--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Italy_Seri" displayName="AveragesTable_Italy_Seri" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN4" t="n">
         <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AQ4" t="n">
         <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.67</v>
+        <v>15.14</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>58.33</v>
+        <v>57.57</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>18.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY4" t="n">
         <v>2.18</v>
@@ -2422,16 +2422,16 @@
         <v>3.27</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="CE4" t="n">
         <v>1.47</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CG4" t="n">
         <v>2.57</v>
@@ -2443,64 +2443,64 @@
         <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL4" t="n">
         <v>2.41</v>
       </c>
       <c r="CM4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO4" t="n">
         <v>1.4</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW4" t="n">
         <v>2.08</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DD4" t="n">
         <v>3.63</v>
@@ -2509,76 +2509,76 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.36</v>
+        <v>93.17</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.45</v>
+        <v>5.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.45</v>
+        <v>39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.73</v>
+        <v>14.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.27</v>
+        <v>15.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>57.09</v>
+        <v>56.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.91</v>
+        <v>12.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.18</v>
+        <v>20.75</v>
       </c>
       <c r="EB4" t="n">
         <v>1.38</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="H5" t="n">
-        <v>74.8</v>
+        <v>68.83</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>30.4</v>
+        <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>16.2</v>
+        <v>17.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="R5" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.2</v>
+        <v>45.83</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.17</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.18</v>
+        <v>9.08</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.84</v>
+        <v>3.69</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="CC5" t="n">
         <v>5.38</v>
@@ -2831,43 +2831,43 @@
         <v>5.66</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN5" t="n">
         <v>1.76</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.86</v>
+        <v>3.98</v>
       </c>
       <c r="CR5" t="n">
         <v>1.49</v>
@@ -2882,28 +2882,28 @@
         <v>1.35</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX5" t="n">
         <v>1.64</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DD5" t="n">
         <v>3.55</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.64</v>
+        <v>70.75</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DM5" t="n">
-        <v>26.91</v>
+        <v>27.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.73</v>
+        <v>16.25</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.73</v>
+        <v>15.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.73</v>
+        <v>9.5</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44</v>
+        <v>44.42</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.55</v>
+        <v>18.84</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="6">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,52 +4290,52 @@
         <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>83.2</v>
+        <v>76.17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AK9" t="n">
         <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.6</v>
+        <v>4.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.6</v>
+        <v>31.33</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.8</v>
+        <v>14.17</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>39.8</v>
+        <v>41.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.4</v>
+        <v>10.83</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.73</v>
+        <v>8.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY9" t="n">
         <v>2.77</v>
@@ -4431,25 +4431,25 @@
         <v>2.84</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.02</v>
+        <v>4.64</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.28</v>
+        <v>4.88</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
@@ -4458,28 +4458,28 @@
         <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK9" t="n">
         <v>1.69</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO9" t="n">
         <v>1.48</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="CR9" t="n">
         <v>1.58</v>
@@ -4506,7 +4506,7 @@
         <v>2.21</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA9" t="n">
         <v>1.67</v>
@@ -4515,52 +4515,52 @@
         <v>1.52</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DD9" t="n">
         <v>3.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>89.91</v>
+        <v>85.84</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.09</v>
+        <v>36.92</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.27</v>
+        <v>15.34</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.73</v>
+        <v>14.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.27</v>
+        <v>6.08</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.27</v>
+        <v>48.5</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.09</v>
+        <v>12.16</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.73</v>
+        <v>4.08</v>
       </c>
       <c r="EA9" t="n">
-        <v>22</v>
+        <v>21.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="10">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -9048,49 +9048,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>102.2</v>
+        <v>98.33</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M21" t="n">
-        <v>45.8</v>
+        <v>45.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P21" t="n">
-        <v>11.8</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>12.67</v>
       </c>
       <c r="R21" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9102,28 +9102,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
         <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.6</v>
+        <v>19.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CC21" t="n">
         <v>5.56</v>
@@ -9279,13 +9279,13 @@
         <v>5.79</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH21" t="n">
         <v>1.37</v>
@@ -9297,61 +9297,61 @@
         <v>1.93</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL21" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CO21" t="n">
         <v>1.34</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="CR21" t="n">
         <v>1.46</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV21" t="n">
         <v>1.88</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD21" t="n">
         <v>3.14</v>
@@ -9360,49 +9360,49 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.45</v>
+        <v>90.42</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.91</v>
+        <v>40.42</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.91</v>
+        <v>13.42</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.18</v>
+        <v>12.5</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
@@ -9414,22 +9414,22 @@
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.82</v>
+        <v>7.92</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.37</v>
+        <v>18.75</v>
       </c>
       <c r="EB21" t="n">
         <v>1.28</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1469,130 +1469,130 @@
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.8</v>
+        <v>82.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>6.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53</v>
+        <v>50.17</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>1.79</v>
@@ -1610,40 +1610,40 @@
         <v>1.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="CE2" t="n">
         <v>1.38</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
         <v>2.28</v>
@@ -1652,19 +1652,19 @@
         <v>1.79</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT2" t="n">
         <v>2.95</v>
@@ -1673,10 +1673,10 @@
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX2" t="n">
         <v>1.62</v>
@@ -1691,88 +1691,88 @@
         <v>1.87</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
         <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>94.91</v>
+        <v>93</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.91</v>
+        <v>43.66</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DP2" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.46</v>
+        <v>12</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.36</v>
+        <v>6.66</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.46</v>
+        <v>50.17</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.63</v>
+        <v>13.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.82</v>
+        <v>8.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.73</v>
+        <v>16.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>88</v>
+        <v>91.83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.2</v>
+        <v>39.17</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>54.6</v>
+        <v>54.67</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.4</v>
+        <v>11.83</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
         <v>1.8</v>
@@ -2013,25 +2013,25 @@
         <v>1.86</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="CH3" t="n">
         <v>1.44</v>
@@ -2043,106 +2043,106 @@
         <v>1.82</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX3" t="n">
         <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>102</v>
+        <v>102.75</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.09</v>
+        <v>5.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>50</v>
+        <v>49.92</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.91</v>
+        <v>10.08</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.91</v>
+        <v>6.58</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.18</v>
+        <v>57</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.27</v>
+        <v>17.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -2419,13 +2419,13 @@
         <v>3.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CC4" t="n">
         <v>2.75</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CE4" t="n">
         <v>1.47</v>
@@ -2467,22 +2467,22 @@
         <v>4.13</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS4" t="n">
         <v>3.29</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CU4" t="n">
         <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX4" t="n">
         <v>1.78</v>
@@ -2497,10 +2497,10 @@
         <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DD4" t="n">
         <v>3.63</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.83</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2816,13 +2816,13 @@
         <v>3.35</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="CA5" t="n">
         <v>3.39</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC5" t="n">
         <v>5.38</v>
@@ -2882,28 +2882,28 @@
         <v>1.35</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="DD5" t="n">
         <v>3.55</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.42</v>
+        <v>44.5</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>97.40000000000001</v>
+        <v>95.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>6.83</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60</v>
+        <v>60.83</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BR6" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>1.94</v>
@@ -3222,136 +3222,136 @@
         <v>2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.16</v>
+        <v>3.01</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
         <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
         <v>3.42</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.91</v>
+        <v>103.42</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.64</v>
+        <v>43.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DO6" t="n">
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.36</v>
+        <v>15.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.27</v>
+        <v>13.58</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.73</v>
+        <v>6.16</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.45</v>
+        <v>60.83</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.27</v>
+        <v>13.42</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.73</v>
+        <v>8.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.09</v>
+        <v>20.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
-        <v>80.8</v>
+        <v>80.33</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>29.2</v>
+        <v>30.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>12.67</v>
       </c>
       <c r="R7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.4</v>
+        <v>47</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.8</v>
+        <v>20.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.94</v>
+        <v>4.24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.66</v>
+        <v>4.83</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="CC7" t="n">
         <v>7.15</v>
@@ -3637,28 +3637,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CK7" t="n">
         <v>1.71</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM7" t="n">
         <v>2.09</v>
@@ -3670,10 +3670,10 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3688,106 +3688,106 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
         <v>1.72</v>
       </c>
       <c r="CY7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CZ7" t="n">
         <v>2.16</v>
       </c>
-      <c r="CZ7" t="n">
-        <v>2.17</v>
-      </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.09</v>
+        <v>81.75</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM7" t="n">
-        <v>29.54</v>
+        <v>30.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.73</v>
+        <v>13</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.63</v>
+        <v>10.42</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46</v>
+        <v>46.34</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.09</v>
+        <v>8.17</v>
       </c>
       <c r="DY7" t="n">
         <v>5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.18</v>
+        <v>19.42</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="H8" t="n">
-        <v>89.59999999999999</v>
+        <v>84.33</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="R8" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.4</v>
+        <v>13.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.6</v>
+        <v>14.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,49 +3968,49 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.36</v>
+        <v>4.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,13 +4019,13 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="CA8" t="n">
         <v>3.28</v>
@@ -4043,13 +4043,13 @@
         <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI8" t="n">
         <v>1.83</v>
@@ -4061,10 +4061,10 @@
         <v>1.81</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN8" t="n">
         <v>1.56</v>
@@ -4082,7 +4082,7 @@
         <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT8" t="n">
         <v>2.75</v>
@@ -4097,16 +4097,16 @@
         <v>1.97</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
@@ -4118,79 +4118,79 @@
         <v>3.33</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>87.36</v>
+        <v>84.92</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.55</v>
+        <v>34.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.45</v>
+        <v>14.16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.36</v>
+        <v>17.42</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.91</v>
+        <v>50.08</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.63</v>
+        <v>11.58</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.64</v>
+        <v>15.34</v>
       </c>
       <c r="EB8" t="n">
         <v>1.18</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="9">
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.67</v>
+        <v>41.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.17</v>
@@ -4434,13 +4434,13 @@
         <v>3.18</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC9" t="n">
         <v>4.64</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="CE9" t="n">
         <v>1.52</v>
@@ -4494,28 +4494,28 @@
         <v>1.32</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DD9" t="n">
         <v>3.34</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.5</v>
+        <v>48.42</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>94.2</v>
+        <v>96.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M10" t="n">
-        <v>36.8</v>
+        <v>38.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>16.4</v>
+        <v>17.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="R10" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>39.2</v>
+        <v>42.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.8</v>
+        <v>13.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,49 +4774,49 @@
         <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.85</v>
+        <v>4.41</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="CC10" t="n">
         <v>5.2</v>
@@ -4849,10 +4849,10 @@
         <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CH10" t="n">
         <v>1.33</v>
@@ -4864,25 +4864,25 @@
         <v>2.05</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CM10" t="n">
         <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
       <c r="CR10" t="n">
         <v>1.49</v>
@@ -4891,7 +4891,7 @@
         <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CU10" t="n">
         <v>1.37</v>
@@ -4900,7 +4900,7 @@
         <v>1.77</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX10" t="n">
         <v>1.73</v>
@@ -4918,7 +4918,7 @@
         <v>1.43</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DD10" t="n">
         <v>3.41</v>
@@ -4927,76 +4927,76 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.91</v>
+        <v>93.25</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.18</v>
+        <v>37.17</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>17</v>
+        <v>17.58</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.91</v>
+        <v>8.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>37.82</v>
+        <v>39.58</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.91</v>
+        <v>4.66</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>21.08</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="H11" t="n">
-        <v>110.5</v>
+        <v>104.29</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="K11" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>59.83</v>
+        <v>63.29</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="P11" t="n">
-        <v>15.33</v>
+        <v>14.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.83</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T11" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.17</v>
+        <v>62.43</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.83</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.33</v>
+        <v>12.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.83</v>
+        <v>18.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0.4</v>
@@ -5177,70 +5177,70 @@
         <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.45</v>
+        <v>10.42</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.63</v>
+        <v>4.51</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="CC11" t="n">
         <v>2.14</v>
@@ -5249,61 +5249,61 @@
         <v>2.04</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
         <v>1.6</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM11" t="n">
         <v>2.22</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX11" t="n">
         <v>1.58</v>
@@ -5321,85 +5321,85 @@
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DF11" t="n">
         <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="DH11" t="n">
-        <v>109.09</v>
+        <v>105.59</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.27</v>
+        <v>7.42</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.82</v>
+        <v>59.09</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.45</v>
+        <v>13.83</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.63</v>
+        <v>11.33</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.27</v>
+        <v>60.58</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>18.09</v>
+        <v>18.25</v>
       </c>
       <c r="DY11" t="n">
-        <v>12.63</v>
+        <v>12.75</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.27</v>
+        <v>18.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5499,52 +5499,52 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>106.2</v>
+        <v>101.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>52.4</v>
+        <v>51.5</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.8</v>
+        <v>20.17</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.36</v>
+        <v>5.67</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
         <v>1.89</v>
@@ -5640,22 +5640,22 @@
         <v>2.02</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CE12" t="n">
         <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
         <v>2.77</v>
@@ -5670,16 +5670,16 @@
         <v>1.96</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5688,16 +5688,16 @@
         <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU12" t="n">
         <v>1.39</v>
@@ -5706,103 +5706,103 @@
         <v>1.88</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
         <v>3.44</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DG12" t="n">
         <v>3</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.18</v>
+        <v>104.66</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.55</v>
+        <v>5.34</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.09</v>
+        <v>57.16</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.45</v>
+        <v>12.92</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.18</v>
+        <v>11.16</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>58.55</v>
+        <v>58.58</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
         <v>17</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.36</v>
+        <v>11.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.18</v>
+        <v>18.58</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>88.8</v>
+        <v>94.17</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M13" t="n">
-        <v>36.2</v>
+        <v>41.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>10.8</v>
+        <v>10.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.6</v>
+        <v>18.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7.8</v>
+        <v>6.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.8</v>
+        <v>54.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
         <v>0.17</v>
@@ -5986,22 +5986,22 @@
         <v>2</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.55</v>
+        <v>7.75</v>
       </c>
       <c r="BI13" t="n">
         <v>2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN13" t="n">
         <v>1</v>
@@ -6010,43 +6010,43 @@
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="CC13" t="n">
         <v>3.83</v>
@@ -6055,28 +6055,28 @@
         <v>4.18</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
         <v>1.54</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM13" t="n">
         <v>2.32</v>
@@ -6088,10 +6088,10 @@
         <v>1.34</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6106,10 +6106,10 @@
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
         <v>1.61</v>
@@ -6124,88 +6124,88 @@
         <v>1.81</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DD13" t="n">
         <v>3.35</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.91</v>
+        <v>88.84</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.91</v>
+        <v>39.42</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DQ13" t="n">
-        <v>18</v>
+        <v>17.58</v>
       </c>
       <c r="DR13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.18</v>
+        <v>10.92</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.55</v>
+        <v>6.84</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.64</v>
+        <v>4.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.45</v>
+        <v>17</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>98.40000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.4</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>42.8</v>
+        <v>41.17</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.17</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>6.83</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BD14" t="n">
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS14" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
         <v>4.15</v>
@@ -6446,25 +6446,25 @@
         <v>4.65</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
@@ -6473,16 +6473,16 @@
         <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CL14" t="n">
         <v>2.05</v>
       </c>
-      <c r="CK14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CM14" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN14" t="n">
         <v>1.88</v>
@@ -6491,10 +6491,10 @@
         <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
@@ -6509,73 +6509,73 @@
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA14" t="n">
         <v>1.9</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DD14" t="n">
         <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.81999999999999</v>
+        <v>93.92</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.27</v>
+        <v>40.58</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.09</v>
+        <v>13.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.18</v>
+        <v>8.42</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.09</v>
+        <v>44.08</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.91</v>
+        <v>9.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.73</v>
+        <v>21.67</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="H15" t="n">
-        <v>107.8</v>
+        <v>105.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M15" t="n">
-        <v>50.8</v>
+        <v>48</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>14.4</v>
+        <v>13.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="R15" t="n">
-        <v>8.6</v>
+        <v>9.67</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.6</v>
+        <v>55.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.4</v>
+        <v>7.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.4</v>
+        <v>19.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6789,70 +6789,70 @@
         <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CC15" t="n">
         <v>2.23</v>
@@ -6864,34 +6864,34 @@
         <v>1.44</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH15" t="n">
         <v>1.34</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM15" t="n">
         <v>2.21</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP15" t="n">
         <v>2.13</v>
@@ -6906,16 +6906,16 @@
         <v>3.22</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CU15" t="n">
         <v>1.36</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CX15" t="n">
         <v>1.69</v>
@@ -6924,7 +6924,7 @@
         <v>2.13</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA15" t="n">
         <v>1.75</v>
@@ -6939,79 +6939,79 @@
         <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.63</v>
+        <v>101.83</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.82</v>
+        <v>5.75</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.63</v>
+        <v>50.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.46</v>
+        <v>13.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.64</v>
+        <v>12.58</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.91</v>
+        <v>8.5</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>58.82</v>
+        <v>57.66</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.18</v>
+        <v>13.92</v>
       </c>
       <c r="DY15" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.82</v>
+        <v>18.58</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI16" t="n">
-        <v>77.59999999999999</v>
+        <v>79.17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>39</v>
+        <v>39.33</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,73 +7168,73 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40.8</v>
+        <v>40.83</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.55</v>
+        <v>7.58</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BR16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>3.74</v>
@@ -7252,55 +7252,55 @@
         <v>4.32</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.09</v>
+        <v>4.82</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.35</v>
+        <v>5.15</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.88</v>
+        <v>3.97</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7309,16 +7309,16 @@
         <v>3.19</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX16" t="n">
         <v>1.61</v>
@@ -7336,85 +7336,85 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD16" t="n">
         <v>3.56</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.36</v>
+        <v>81.83</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DK16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.64</v>
+        <v>37</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="DO16" t="n">
         <v>1</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.91</v>
+        <v>11.42</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.09</v>
+        <v>14</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.82</v>
+        <v>8.58</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>41.55</v>
+        <v>41.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>10</v>
+        <v>10.42</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.27</v>
+        <v>7.34</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.91</v>
+        <v>16.67</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>23.8</v>
+        <v>24.67</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.8</v>
+        <v>13.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>33.4</v>
+        <v>34</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.73</v>
+        <v>8.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="BR17" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS17" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY17" t="n">
         <v>3.25</v>
@@ -7655,31 +7655,31 @@
         <v>3.59</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CC17" t="n">
-        <v>7.45</v>
+        <v>6.89</v>
       </c>
       <c r="CD17" t="n">
-        <v>8.41</v>
+        <v>7.7</v>
       </c>
       <c r="CE17" t="n">
         <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
         <v>2.05</v>
@@ -7688,7 +7688,7 @@
         <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CM17" t="n">
         <v>2.07</v>
@@ -7700,124 +7700,124 @@
         <v>1.35</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU17" t="n">
         <v>1.37</v>
       </c>
       <c r="CV17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CX17" t="n">
         <v>1.78</v>
       </c>
-      <c r="CW17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>1.79</v>
-      </c>
       <c r="CY17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.07</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB17" t="n">
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD17" t="n">
         <v>3.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DH17" t="n">
-        <v>79.18000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.91</v>
+        <v>30.75</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.27</v>
+        <v>13</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.45</v>
+        <v>12.16</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.369999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.64</v>
+        <v>38.5</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.27</v>
+        <v>15.75</v>
       </c>
       <c r="EB17" t="n">
         <v>1.01</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>114.4</v>
+        <v>105</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.2</v>
+        <v>49.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.4</v>
+        <v>16.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.2</v>
+        <v>14.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>59.4</v>
+        <v>57.83</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.2</v>
+        <v>18.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BY18" t="n">
         <v>1.81</v>
@@ -8058,40 +8058,40 @@
         <v>2</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="CE18" t="n">
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH18" t="n">
         <v>1.36</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM18" t="n">
         <v>2.08</v>
@@ -8124,19 +8124,19 @@
         <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB18" t="n">
         <v>1.39</v>
@@ -8145,82 +8145,82 @@
         <v>2.25</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="DH18" t="n">
-        <v>116.82</v>
+        <v>111.92</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.82</v>
+        <v>5.75</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM18" t="n">
-        <v>52.45</v>
+        <v>51.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.37</v>
+        <v>14.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.45</v>
+        <v>7.16</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>59.36</v>
+        <v>58.58</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.36</v>
+        <v>14.16</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>88</v>
+        <v>93.67</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>35.2</v>
+        <v>41.17</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.8</v>
+        <v>14.83</v>
       </c>
       <c r="R19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.4</v>
+        <v>12.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.4</v>
+        <v>8.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.49</v>
+        <v>3.26</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.95</v>
+        <v>3.64</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CB19" t="n">
         <v>3.54</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>3.58</v>
       </c>
       <c r="CC19" t="n">
         <v>4.5</v>
@@ -8473,64 +8473,64 @@
         <v>4.85</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO19" t="n">
         <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="CR19" t="n">
         <v>1.46</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY19" t="n">
         <v>2.17</v>
@@ -8539,91 +8539,91 @@
         <v>2.15</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DD19" t="n">
         <v>3.2</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.81999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM19" t="n">
-        <v>33.45</v>
+        <v>36.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.45</v>
+        <v>13.16</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.73</v>
+        <v>14.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.18</v>
+        <v>8.75</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.27</v>
+        <v>46.75</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.46</v>
+        <v>7.17</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.55</v>
+        <v>16.75</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="20">
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -8645,82 +8645,82 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="G20" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>43.2</v>
+        <v>41.67</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="R20" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>47.6</v>
+        <v>45.5</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.6</v>
+        <v>11.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>20.2</v>
+        <v>19.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8804,70 +8804,70 @@
         <v>2.17</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BP20" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.82</v>
+        <v>5.58</v>
       </c>
       <c r="BR20" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS20" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BX20" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC20" t="n">
         <v>5.48</v>
@@ -8876,13 +8876,13 @@
         <v>6.09</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH20" t="n">
         <v>1.35</v>
@@ -8891,37 +8891,37 @@
         <v>1.79</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8933,22 +8933,22 @@
         <v>2.05</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB20" t="n">
         <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DD20" t="n">
         <v>3.33</v>
@@ -8957,76 +8957,76 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DH20" t="n">
-        <v>85.27</v>
+        <v>86</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.36</v>
+        <v>37.08</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.64</v>
+        <v>13</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.369999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DS20" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT20" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.27</v>
+        <v>42.58</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.37</v>
+        <v>11.25</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.27</v>
+        <v>7.34</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.36</v>
+        <v>17.34</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="21">
@@ -9264,13 +9264,13 @@
         <v>2.96</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CA21" t="n">
         <v>3.59</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC21" t="n">
         <v>5.56</v>
@@ -9324,16 +9324,16 @@
         <v>3.05</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU21" t="n">
         <v>1.4</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW21" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CX21" t="n">
         <v>1.57</v>
@@ -9351,7 +9351,7 @@
         <v>1.39</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DD21" t="n">
         <v>3.14</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -7664,7 +7664,7 @@
         <v>6.89</v>
       </c>
       <c r="CD17" t="n">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
       <c r="CE17" t="n">
         <v>1.45</v>
@@ -7721,7 +7721,7 @@
         <v>1.79</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX17" t="n">
         <v>1.78</v>
@@ -7739,7 +7739,7 @@
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD17" t="n">
         <v>3.4</v>
@@ -8458,13 +8458,13 @@
         <v>3.26</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CA19" t="n">
         <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
         <v>4.5</v>
@@ -8527,7 +8527,7 @@
         <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX19" t="n">
         <v>1.72</v>
@@ -8545,7 +8545,7 @@
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD19" t="n">
         <v>3.2</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>111.17</v>
+        <v>112.14</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>41.5</v>
+        <v>41.57</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="P6" t="n">
-        <v>15.5</v>
+        <v>14.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.17</v>
+        <v>14.86</v>
       </c>
       <c r="R6" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>60.83</v>
+        <v>61.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.83</v>
+        <v>14.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.5</v>
+        <v>6.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>24</v>
+        <v>22.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,64 +3165,64 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BR6" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB6" t="n">
         <v>3.54</v>
@@ -3234,67 +3234,67 @@
         <v>3.01</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CM6" t="n">
         <v>2.01</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX6" t="n">
         <v>1.81</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.03</v>
@@ -3303,55 +3303,55 @@
         <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="DE6" t="n">
         <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DG6" t="n">
         <v>1.92</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.42</v>
+        <v>104.54</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="DK6" t="n">
         <v>3.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.5</v>
+        <v>43.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DO6" t="n">
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.75</v>
+        <v>15.39</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.58</v>
+        <v>13.08</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.16</v>
+        <v>6.15</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.83</v>
+        <v>61</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.42</v>
+        <v>13.77</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.75</v>
+        <v>5.38</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.25</v>
+        <v>19.92</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="7">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.33</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>84</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>31.43</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.33</v>
+        <v>12.43</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.83</v>
+        <v>13.43</v>
       </c>
       <c r="AS19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
         <v>10</v>
       </c>
-      <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.67</v>
-      </c>
       <c r="BB19" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD19" t="n">
-        <v>16</v>
+        <v>15.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.17</v>
+        <v>8.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO19" t="n">
         <v>0.92</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT19" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY19" t="n">
         <v>3.26</v>
@@ -8467,19 +8467,19 @@
         <v>3.55</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
@@ -8488,43 +8488,43 @@
         <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CO19" t="n">
         <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW19" t="n">
         <v>1.93</v>
@@ -8533,64 +8533,64 @@
         <v>1.72</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.84</v>
+        <v>88.31</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.58</v>
+        <v>35.93</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.16</v>
+        <v>12.69</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.33</v>
+        <v>14.08</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.75</v>
+        <v>8.31</v>
       </c>
       <c r="DS19" t="n">
         <v>0.16</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46.75</v>
+        <v>46</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.17</v>
+        <v>7.16</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.75</v>
+        <v>16.23</v>
       </c>
       <c r="EB19" t="n">
         <v>1.24</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H2" t="n">
-        <v>103.33</v>
+        <v>103.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="K2" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>47.83</v>
+        <v>46.43</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>11.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.67</v>
+        <v>13.43</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.17</v>
+        <v>49.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.83</v>
+        <v>15.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.67</v>
+        <v>10.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>18.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF2" t="n">
         <v>0.17</v>
@@ -1550,49 +1550,49 @@
         <v>1.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.92</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.08</v>
+        <v>4.85</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC2" t="n">
         <v>2.34</v>
@@ -1625,112 +1625,112 @@
         <v>1.38</v>
       </c>
       <c r="CF2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG2" t="n">
         <v>2.83</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK2" t="n">
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO2" t="n">
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
         <v>1.99</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DB2" t="n">
         <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DH2" t="n">
-        <v>93</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DK2" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.66</v>
+        <v>43.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DP2" t="n">
         <v>9.92</v>
@@ -1739,40 +1739,40 @@
         <v>12</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.66</v>
+        <v>6.46</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.17</v>
+        <v>49.85</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.08</v>
+        <v>13.31</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.25</v>
+        <v>16.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G3" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>113.67</v>
+        <v>110.29</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>60.67</v>
+        <v>58.86</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>9.83</v>
+        <v>10.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="R3" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.33</v>
+        <v>57.71</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.17</v>
+        <v>17.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>17.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,67 +1953,67 @@
         <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN3" t="n">
         <v>1.08</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="n">
         <v>3.87</v>
@@ -2028,7 +2028,7 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG3" t="n">
         <v>2.95</v>
@@ -2046,31 +2046,31 @@
         <v>1.66</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
@@ -2106,43 +2106,43 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.75</v>
+        <v>101.77</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.84</v>
+        <v>5.69</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.92</v>
+        <v>49.77</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.08</v>
+        <v>10.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.58</v>
+        <v>6.54</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57</v>
+        <v>56.31</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.5</v>
+        <v>10.62</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.33</v>
+        <v>17.07</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,55 +2681,55 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN5" t="n">
         <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.33</v>
+        <v>15.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -2741,76 +2741,76 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.17</v>
+        <v>9.43</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.67</v>
+        <v>16.57</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
         <v>3.35</v>
@@ -2819,136 +2819,136 @@
         <v>3.77</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.38</v>
+        <v>6.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.66</v>
+        <v>6.82</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG5" t="n">
         <v>1.46</v>
       </c>
-      <c r="CF5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>1.16</v>
-      </c>
       <c r="DH5" t="n">
-        <v>70.75</v>
+        <v>70.23</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM5" t="n">
-        <v>27.5</v>
+        <v>27.23</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP5" t="n">
-        <v>16.25</v>
+        <v>16.23</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.75</v>
+        <v>15.77</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.5</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.5</v>
+        <v>44.38</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.67</v>
+        <v>9.31</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.42</v>
+        <v>6.08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.84</v>
+        <v>18.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="6">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3890,127 +3890,127 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>85.5</v>
+        <v>87.14</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.67</v>
+        <v>31.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.83</v>
+        <v>13.29</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.33</v>
+        <v>16.14</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.67</v>
+        <v>51.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.33</v>
+        <v>10.14</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.17</v>
+        <v>7.86</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BH8" t="n">
         <v>9.08</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
         <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO8" t="n">
         <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT8" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY8" t="n">
         <v>2.82</v>
@@ -4028,28 +4028,28 @@
         <v>3.15</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI8" t="n">
         <v>1.83</v>
@@ -4058,40 +4058,40 @@
         <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CM8" t="n">
         <v>1.96</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW8" t="n">
         <v>1.97</v>
@@ -4109,88 +4109,88 @@
         <v>1.58</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>84.92</v>
+        <v>85.84</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM8" t="n">
-        <v>34.08</v>
+        <v>33.69</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.16</v>
+        <v>13.85</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.42</v>
+        <v>17.23</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.08</v>
+        <v>50.23</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.58</v>
+        <v>11.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.83</v>
+        <v>9.08</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.34</v>
+        <v>15.69</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="H9" t="n">
-        <v>95.5</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="K9" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>42.5</v>
+        <v>41.14</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>16.5</v>
+        <v>15.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.83</v>
+        <v>14.57</v>
       </c>
       <c r="R9" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>55.33</v>
+        <v>56</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>13.71</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.33</v>
+        <v>22.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4371,70 +4371,70 @@
         <v>2.83</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.08</v>
+        <v>4.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CC9" t="n">
         <v>4.64</v>
@@ -4443,28 +4443,28 @@
         <v>4.85</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CK9" t="n">
         <v>1.69</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CM9" t="n">
         <v>2.12</v>
@@ -4473,13 +4473,13 @@
         <v>1.67</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="CR9" t="n">
         <v>1.58</v>
@@ -4497,25 +4497,25 @@
         <v>1.67</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DD9" t="n">
         <v>3.34</v>
@@ -4524,40 +4524,40 @@
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.84</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="DL9" t="n">
         <v>0.08</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.92</v>
+        <v>36.61</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.34</v>
+        <v>14.85</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.42</v>
+        <v>14.77</v>
       </c>
       <c r="DR9" t="n">
         <v>6.08</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.42</v>
+        <v>49.31</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.16</v>
+        <v>12.38</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.08</v>
+        <v>8.31</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.67</v>
+        <v>21.23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.67</v>
+        <v>36.43</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.5</v>
+        <v>17.71</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,73 +4750,73 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>36.67</v>
+        <v>37.14</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>23.17</v>
+        <v>22.57</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.17</v>
+        <v>7.92</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN10" t="n">
         <v>1.08</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>4</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>4.17</v>
-      </c>
       <c r="BR10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT10" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY10" t="n">
         <v>3.98</v>
@@ -4834,55 +4834,55 @@
         <v>4.41</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.2</v>
+        <v>5.03</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CK10" t="n">
         <v>1.68</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
         <v>1.71</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="CR10" t="n">
         <v>1.49</v>
@@ -4897,28 +4897,28 @@
         <v>1.37</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="DD10" t="n">
         <v>3.41</v>
@@ -4927,28 +4927,28 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.25</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.17</v>
+        <v>37.46</v>
       </c>
       <c r="DN10" t="n">
         <v>1.08</v>
@@ -4957,13 +4957,13 @@
         <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.58</v>
+        <v>17.69</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.42</v>
+        <v>7.31</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.58</v>
+        <v>39.61</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.08</v>
+        <v>12.16</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.08</v>
+        <v>20.92</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0.29</v>
@@ -5096,139 +5096,139 @@
         <v>1.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.4</v>
+        <v>108.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>53.2</v>
+        <v>53.67</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>5.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>58</v>
+        <v>58.33</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>17.2</v>
+        <v>16.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.42</v>
+        <v>10.38</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY11" t="n">
         <v>1.37</v>
@@ -5237,16 +5237,16 @@
         <v>1.41</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.51</v>
+        <v>4.57</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.78</v>
+        <v>4.91</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5255,16 +5255,16 @@
         <v>2.61</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CK11" t="n">
         <v>1.6</v>
@@ -5276,7 +5276,7 @@
         <v>2.22</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
@@ -5285,121 +5285,121 @@
         <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX11" t="n">
         <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.37</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="DH11" t="n">
-        <v>105.59</v>
+        <v>106.23</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.42</v>
+        <v>7.31</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.09</v>
+        <v>58.85</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.83</v>
+        <v>13.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.83</v>
+        <v>5.08</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.58</v>
+        <v>60.54</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>18.25</v>
+        <v>17.92</v>
       </c>
       <c r="DY11" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.5</v>
+        <v>5.31</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.5</v>
+        <v>18.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12">
@@ -5409,91 +5409,91 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="H12" t="n">
-        <v>108</v>
+        <v>112.71</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5</v>
+        <v>6.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="n">
-        <v>62.83</v>
+        <v>62.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O12" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="P12" t="n">
-        <v>10.83</v>
+        <v>11.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.67</v>
+        <v>58.43</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>19.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>13</v>
+        <v>12.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>16.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -5580,70 +5580,70 @@
         <v>2.17</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.42</v>
+        <v>9.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT12" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.66</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
         <v>1.9</v>
@@ -5652,124 +5652,124 @@
         <v>1.94</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CM12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CZ12" t="n">
         <v>2.24</v>
       </c>
-      <c r="CN12" t="n">
+      <c r="DA12" t="n">
         <v>1.77</v>
       </c>
-      <c r="CO12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.74</v>
-      </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.66</v>
+        <v>107.46</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.16</v>
+        <v>57.23</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.92</v>
+        <v>13.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.16</v>
+        <v>11.54</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.58</v>
+        <v>6.31</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>58.58</v>
+        <v>58.46</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>17</v>
+        <v>16.77</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.5</v>
+        <v>11.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.58</v>
+        <v>18.23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -5902,52 +5902,52 @@
         <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>83.5</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.5</v>
+        <v>37.57</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.67</v>
+        <v>15.71</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.67</v>
+        <v>47.71</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.5</v>
+        <v>16.14</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.75</v>
+        <v>7.54</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BN13" t="n">
         <v>1</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="BR13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT13" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BY13" t="n">
         <v>2.16</v>
@@ -6046,13 +6046,13 @@
         <v>3.45</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.83</v>
+        <v>4.06</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
@@ -6061,7 +6061,7 @@
         <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
         <v>1.37</v>
@@ -6073,13 +6073,13 @@
         <v>1.97</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN13" t="n">
         <v>1.8</v>
@@ -6115,64 +6115,64 @@
         <v>1.61</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB13" t="n">
         <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DH13" t="n">
-        <v>88.84</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.42</v>
+        <v>39.31</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO13" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.58</v>
+        <v>17</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.5</v>
+        <v>50.77</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.92</v>
+        <v>10.77</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.84</v>
+        <v>6.69</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="EA13" t="n">
-        <v>17</v>
+        <v>16.77</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="14">
@@ -6215,25 +6215,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -6242,34 +6242,34 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M14" t="n">
-        <v>41.17</v>
+        <v>39.14</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="P14" t="n">
-        <v>11.5</v>
+        <v>12.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.17</v>
+        <v>15.29</v>
       </c>
       <c r="R14" t="n">
-        <v>7.17</v>
+        <v>7.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,25 +6281,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47</v>
+        <v>47.14</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.33</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -6386,70 +6386,70 @@
         <v>1.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BR14" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.15</v>
+        <v>3.97</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="CC14" t="n">
         <v>5.46</v>
@@ -6458,19 +6458,19 @@
         <v>5.88</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.07</v>
@@ -6479,7 +6479,7 @@
         <v>1.52</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM14" t="n">
         <v>2.4</v>
@@ -6491,19 +6491,19 @@
         <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS14" t="n">
         <v>3.26</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
@@ -6515,22 +6515,22 @@
         <v>2.17</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DD14" t="n">
         <v>3.44</v>
@@ -6539,43 +6539,43 @@
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.92</v>
+        <v>93.77</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.58</v>
+        <v>39.54</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.58</v>
+        <v>12.85</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.58</v>
+        <v>14.23</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.42</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.08</v>
+        <v>44.38</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.58</v>
+        <v>6.69</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.67</v>
+        <v>21</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6708,139 +6708,139 @@
         <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>98.33</v>
+        <v>99.86</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.67</v>
+        <v>5.14</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN15" t="n">
-        <v>52.33</v>
+        <v>49</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>11.86</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.33</v>
+        <v>7.43</v>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>59.83</v>
+        <v>57.57</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.33</v>
+        <v>13.29</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.5</v>
+        <v>8.43</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.5</v>
+        <v>17.86</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.92</v>
+        <v>8.69</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
         <v>1.92</v>
@@ -6849,31 +6849,31 @@
         <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.06</v>
@@ -6885,19 +6885,19 @@
         <v>2.08</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
@@ -6915,25 +6915,25 @@
         <v>1.79</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DD15" t="n">
         <v>3.61</v>
@@ -6942,76 +6942,76 @@
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.83</v>
+        <v>102.38</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.75</v>
+        <v>5.46</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM15" t="n">
-        <v>50.16</v>
+        <v>48.54</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.25</v>
+        <v>13.23</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.58</v>
+        <v>12.7</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.66</v>
+        <v>56.61</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.92</v>
+        <v>13.39</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.67</v>
+        <v>8.15</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.58</v>
+        <v>18.7</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="H16" t="n">
-        <v>84.5</v>
+        <v>87</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="K16" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>34.67</v>
+        <v>36.86</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="P16" t="n">
-        <v>11.83</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.5</v>
+        <v>14.29</v>
       </c>
       <c r="R16" t="n">
-        <v>8.17</v>
+        <v>7.71</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>42.17</v>
+        <v>43.43</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.17</v>
+        <v>11.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.83</v>
+        <v>16.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7195,46 +7195,46 @@
         <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.58</v>
+        <v>8.08</v>
       </c>
       <c r="BI16" t="n">
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.17</v>
+        <v>4.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT16" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CC16" t="n">
         <v>4.82</v>
@@ -7267,10 +7267,10 @@
         <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7279,34 +7279,34 @@
         <v>1.81</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK16" t="n">
         <v>1.58</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO16" t="n">
         <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT16" t="n">
         <v>2.72</v>
@@ -7315,28 +7315,28 @@
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB16" t="n">
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD16" t="n">
         <v>3.56</v>
@@ -7345,43 +7345,43 @@
         <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.83</v>
+        <v>83.39</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DN16" t="n">
         <v>0.92</v>
       </c>
       <c r="DO16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.42</v>
+        <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14</v>
+        <v>14.39</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.58</v>
+        <v>8.31</v>
       </c>
       <c r="DS16" t="n">
         <v>0.08</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>41.5</v>
+        <v>42.23</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.42</v>
+        <v>10.92</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.34</v>
+        <v>7.92</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.67</v>
+        <v>16.85</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>79.83</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="K17" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="L17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M17" t="n">
-        <v>36.83</v>
+        <v>37.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="S17" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="T17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>43</v>
+        <v>42.57</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7499,19 +7499,19 @@
         <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.5</v>
+        <v>17.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7595,70 +7595,70 @@
         <v>1.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="BR17" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS17" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.59</v>
+        <v>4.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="CC17" t="n">
         <v>6.89</v>
@@ -7667,19 +7667,19 @@
         <v>7.75</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ17" t="n">
         <v>2.05</v>
@@ -7688,73 +7688,73 @@
         <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN17" t="n">
         <v>1.67</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV17" t="n">
         <v>1.79</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="DE17" t="n">
         <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DH17" t="n">
-        <v>77.92</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7763,61 +7763,61 @@
         <v>1.92</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="DL17" t="n">
         <v>0.08</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.75</v>
+        <v>31.62</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DP17" t="n">
         <v>13</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.16</v>
+        <v>12.38</v>
       </c>
       <c r="DR17" t="n">
         <v>9.08</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.5</v>
+        <v>38.61</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.75</v>
+        <v>9.77</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.75</v>
+        <v>15.62</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H18" t="n">
+        <v>117.29</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M18" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H18" t="n">
-        <v>118.83</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M18" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.17</v>
-      </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59.33</v>
+        <v>58.86</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.33</v>
+        <v>14.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="AC18" t="n">
-        <v>20</v>
+        <v>20.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,49 +7998,49 @@
         <v>2.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.33</v>
+        <v>9.08</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,19 +8049,19 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="CC18" t="n">
         <v>2.28</v>
@@ -8070,28 +8070,28 @@
         <v>2.4</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI18" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK18" t="n">
         <v>1.7</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM18" t="n">
         <v>2.08</v>
@@ -8100,13 +8100,13 @@
         <v>1.66</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8121,28 +8121,28 @@
         <v>1.36</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DD18" t="n">
         <v>3.59</v>
@@ -8151,43 +8151,43 @@
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="DH18" t="n">
-        <v>111.92</v>
+        <v>111.62</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.5</v>
+        <v>51.54</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.5</v>
+        <v>14.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.67</v>
+        <v>15.46</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.16</v>
+        <v>6.77</v>
       </c>
       <c r="DS18" t="n">
         <v>0.08</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.58</v>
+        <v>58.38</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.16</v>
+        <v>13.69</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.92</v>
+        <v>8.69</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.16</v>
+        <v>19.54</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="19">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8726,49 +8726,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AI20" t="n">
-        <v>73</v>
+        <v>75.86</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>32.5</v>
+        <v>32.86</v>
       </c>
       <c r="AO20" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>14.71</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.33</v>
+        <v>11.86</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>39.67</v>
+        <v>41.43</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.17</v>
+        <v>11.71</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="BD20" t="n">
-        <v>15</v>
+        <v>15.43</v>
       </c>
       <c r="BE20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BN20" t="n">
         <v>1.23</v>
       </c>
-      <c r="BF20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BO20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP20" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.58</v>
+        <v>5.46</v>
       </c>
       <c r="BR20" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS20" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT20" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU20" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV20" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW20" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX20" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY20" t="n">
         <v>3.32</v>
@@ -8864,79 +8864,79 @@
         <v>3.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.48</v>
+        <v>5.07</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.09</v>
+        <v>5.61</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS20" t="n">
         <v>3.19</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.14</v>
@@ -8945,10 +8945,10 @@
         <v>1.7</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DD20" t="n">
         <v>3.33</v>
@@ -8957,43 +8957,43 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="DH20" t="n">
-        <v>86</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="DL20" t="n">
         <v>0.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.08</v>
+        <v>36.93</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="DP20" t="n">
-        <v>13</v>
+        <v>13.69</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.25</v>
+        <v>10.62</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="DS20" t="n">
         <v>0.08</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>42.58</v>
+        <v>43.31</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.25</v>
+        <v>11.53</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.34</v>
+        <v>7.47</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.34</v>
+        <v>17.39</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.5</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN21" t="n">
-        <v>35</v>
+        <v>34.57</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.83</v>
+        <v>14.57</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.33</v>
+        <v>11.29</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>45</v>
+        <v>45.57</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.17</v>
+        <v>10.71</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.17</v>
+        <v>18.71</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.67</v>
+        <v>5.77</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV21" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY21" t="n">
         <v>2.96</v>
@@ -9267,31 +9267,31 @@
         <v>3.33</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.56</v>
+        <v>5.15</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.79</v>
+        <v>5.38</v>
       </c>
       <c r="CE21" t="n">
         <v>1.44</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.93</v>
@@ -9300,28 +9300,28 @@
         <v>1.52</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM21" t="n">
         <v>2.46</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT21" t="n">
         <v>2.8</v>
@@ -9330,28 +9330,28 @@
         <v>1.4</v>
       </c>
       <c r="CV21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA21" t="n">
         <v>1.87</v>
-      </c>
-      <c r="CW21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CX21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CZ21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DA21" t="n">
-        <v>1.89</v>
       </c>
       <c r="DB21" t="n">
         <v>1.39</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD21" t="n">
         <v>3.14</v>
@@ -9363,70 +9363,70 @@
         <v>1.16</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.42</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DJ21" t="n">
         <v>2</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.42</v>
+        <v>39.77</v>
       </c>
       <c r="DN21" t="n">
         <v>0.84</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.42</v>
+        <v>13.85</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.5</v>
+        <v>11.93</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47</v>
+        <v>47.15</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.58</v>
+        <v>11.77</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC21" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>3.67</v>
       </c>
       <c r="H4" t="n">
-        <v>110.2</v>
+        <v>115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>13.2</v>
+        <v>13.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>15.17</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>55.6</v>
+        <v>57.17</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>17.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.8</v>
+        <v>12.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>2.14</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="BL4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO4" t="n">
         <v>0.92</v>
       </c>
-      <c r="BM4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BP4" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.42</v>
+        <v>4.31</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>2.18</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>2.31</v>
-      </c>
       <c r="CA4" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="CC4" t="n">
         <v>2.75</v>
@@ -2428,28 +2428,28 @@
         <v>2.89</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI4" t="n">
         <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK4" t="n">
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CM4" t="n">
         <v>2.01</v>
@@ -2458,13 +2458,13 @@
         <v>1.62</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="CR4" t="n">
         <v>1.52</v>
@@ -2482,16 +2482,16 @@
         <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX4" t="n">
         <v>1.78</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA4" t="n">
         <v>1.65</v>
@@ -2509,76 +2509,76 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.17</v>
+        <v>96.69</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.17</v>
+        <v>5.77</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM4" t="n">
-        <v>39</v>
+        <v>41.85</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.83</v>
+        <v>14.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.5</v>
+        <v>15.15</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>56.75</v>
+        <v>57.39</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.67</v>
+        <v>13.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.75</v>
+        <v>20.84</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="5">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,52 +3484,52 @@
         <v>2.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.17</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>3.29</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>29.83</v>
+        <v>28.43</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.67</v>
+        <v>44.14</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.67</v>
+        <v>19.14</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.25</v>
+        <v>10.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM7" t="n">
         <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>5.77</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY7" t="n">
         <v>4.24</v>
@@ -3625,7 +3625,7 @@
         <v>4.83</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="CB7" t="n">
         <v>4.14</v>
@@ -3634,16 +3634,16 @@
         <v>7.15</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
@@ -3652,13 +3652,13 @@
         <v>1.81</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
         <v>1.71</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CM7" t="n">
         <v>2.09</v>
@@ -3670,10 +3670,10 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3715,37 +3715,37 @@
         <v>3.06</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.75</v>
+        <v>80.31</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.25</v>
+        <v>29.46</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="DP7" t="n">
         <v>11.92</v>
@@ -3754,7 +3754,7 @@
         <v>13</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.34</v>
+        <v>45.46</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.17</v>
+        <v>8.31</v>
       </c>
       <c r="DY7" t="n">
         <v>5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.42</v>
+        <v>19.62</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>91.83</v>
+        <v>92.86</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.17</v>
+        <v>40.29</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>54.67</v>
+        <v>56</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.83</v>
+        <v>11.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.67</v>
+        <v>8.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.33</v>
+        <v>18.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU3" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>1.76</v>
@@ -2013,16 +2013,16 @@
         <v>1.83</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CB3" t="n">
         <v>3.87</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2031,151 +2031,151 @@
         <v>2.75</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK3" t="n">
         <v>1.66</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM3" t="n">
         <v>2.15</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
         <v>1.9</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
         <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.77</v>
+        <v>101.58</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.77</v>
+        <v>49.58</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.46</v>
+        <v>10.22</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.54</v>
+        <v>6.42</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.31</v>
+        <v>56.86</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>14.78</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.62</v>
+        <v>10.36</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.07</v>
+        <v>17.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>81</v>
+        <v>83.38</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>33.88</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.14</v>
+        <v>14.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>57.57</v>
+        <v>57</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="BB4" t="n">
         <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.14</v>
+        <v>17.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>2.07</v>
@@ -2416,22 +2416,22 @@
         <v>2.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
         <v>2.6</v>
@@ -2443,13 +2443,13 @@
         <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM4" t="n">
         <v>2.01</v>
@@ -2464,25 +2464,25 @@
         <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CX4" t="n">
         <v>1.78</v>
@@ -2497,10 +2497,10 @@
         <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DD4" t="n">
         <v>3.63</v>
@@ -2509,76 +2509,76 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.69</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.77</v>
+        <v>5.57</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.85</v>
+        <v>41.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.69</v>
+        <v>14.93</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.15</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>57.39</v>
+        <v>57.07</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.92</v>
+        <v>13.86</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.31</v>
+        <v>4.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.84</v>
+        <v>20.14</v>
       </c>
       <c r="EB4" t="n">
         <v>1.49</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>68.83</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K5" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="L5" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P5" t="n">
-        <v>17.17</v>
+        <v>17.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="R5" t="n">
-        <v>8.17</v>
+        <v>7.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46</v>
+        <v>46.14</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.17</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>19.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="CA5" t="n">
         <v>3.55</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC5" t="n">
         <v>6.33</v>
@@ -2834,28 +2834,28 @@
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN5" t="n">
         <v>1.78</v>
@@ -2867,16 +2867,16 @@
         <v>2.14</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU5" t="n">
         <v>1.38</v>
@@ -2885,22 +2885,22 @@
         <v>1.79</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC5" t="n">
         <v>2.29</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DH5" t="n">
-        <v>70.23</v>
+        <v>71</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>27.23</v>
+        <v>28.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>16.23</v>
+        <v>16.36</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.77</v>
+        <v>15.79</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.38</v>
+        <v>44.57</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.31</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.08</v>
+        <v>6.14</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.23</v>
+        <v>3.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.29</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>95.67</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>45.5</v>
+        <v>45.86</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>15.57</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>11.71</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60.83</v>
+        <v>60.43</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>9.43</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.5</v>
+        <v>16.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.46</v>
+        <v>7.71</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BR6" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY6" t="n">
         <v>1.9</v>
@@ -3222,34 +3222,34 @@
         <v>1.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.91</v>
+        <v>3.32</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
@@ -3258,19 +3258,19 @@
         <v>2.29</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
@@ -3285,10 +3285,10 @@
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX6" t="n">
         <v>1.81</v>
@@ -3297,61 +3297,61 @@
         <v>2.29</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.54</v>
+        <v>104.28</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
         <v>3.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.38</v>
+        <v>43.72</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DO6" t="n">
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.39</v>
+        <v>15.22</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.08</v>
+        <v>13.28</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.15</v>
+        <v>5.93</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61</v>
+        <v>60.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.77</v>
+        <v>13.86</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.390000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.92</v>
+        <v>19.86</v>
       </c>
       <c r="EB6" t="n">
         <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>80.33</v>
+        <v>81</v>
       </c>
       <c r="I7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="L7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>30.67</v>
+        <v>32.71</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>11.83</v>
+        <v>12.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.67</v>
+        <v>12.43</v>
       </c>
       <c r="R7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>9</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>47</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8.67</v>
-      </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.17</v>
+        <v>20.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3565,70 +3565,70 @@
         <v>2.14</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.77</v>
+        <v>5.71</v>
       </c>
       <c r="BR7" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.24</v>
+        <v>3.97</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.83</v>
+        <v>4.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="CC7" t="n">
         <v>7.15</v>
@@ -3637,52 +3637,52 @@
         <v>8.039999999999999</v>
       </c>
       <c r="CE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CH7" t="n">
         <v>1.39</v>
       </c>
-      <c r="CF7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="CI7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS7" t="n">
         <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3706,88 +3706,88 @@
         <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DD7" t="n">
         <v>3.06</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.31</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.31</v>
+        <v>3.43</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM7" t="n">
-        <v>29.46</v>
+        <v>30.57</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.92</v>
+        <v>12.14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.46</v>
+        <v>45.72</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.31</v>
+        <v>8.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.62</v>
+        <v>19.93</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3887,130 +3887,130 @@
         <v>2.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>87.14</v>
+        <v>88.62</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>0.43</v>
       </c>
-      <c r="AN8" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BK8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN8" t="n">
         <v>1.43</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BO8" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY8" t="n">
         <v>2.82</v>
@@ -4028,22 +4028,22 @@
         <v>3.15</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="CE8" t="n">
         <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CG8" t="n">
         <v>2.7</v>
@@ -4052,10 +4052,10 @@
         <v>1.35</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
         <v>1.8</v>
@@ -4067,7 +4067,7 @@
         <v>1.96</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO8" t="n">
         <v>1.35</v>
@@ -4076,7 +4076,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CR8" t="n">
         <v>1.46</v>
@@ -4085,25 +4085,25 @@
         <v>3.16</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU8" t="n">
         <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA8" t="n">
         <v>1.58</v>
@@ -4112,85 +4112,85 @@
         <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD8" t="n">
         <v>3.31</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.84</v>
+        <v>86.78</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.61</v>
+        <v>4.36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.69</v>
+        <v>34.15</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.85</v>
+        <v>13.93</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.23</v>
+        <v>17</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.23</v>
+        <v>50.93</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.84</v>
+        <v>11.64</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.69</v>
+        <v>15.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="9">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="H10" t="n">
-        <v>96.5</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>38.67</v>
+        <v>37.43</v>
       </c>
       <c r="N10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
-        <v>17.67</v>
+        <v>17.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="R10" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.5</v>
+        <v>41.57</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>18.29</v>
       </c>
       <c r="AD10" t="n">
         <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,49 +4774,49 @@
         <v>2.71</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.92</v>
+        <v>8.07</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BR10" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.98</v>
+        <v>4.13</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.41</v>
+        <v>4.63</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CC10" t="n">
         <v>5.03</v>
@@ -4846,28 +4846,28 @@
         <v>5.52</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK10" t="n">
         <v>1.68</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CM10" t="n">
         <v>2.12</v>
@@ -4876,37 +4876,37 @@
         <v>1.71</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX10" t="n">
         <v>1.75</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.12</v>
@@ -4915,88 +4915,88 @@
         <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.84999999999999</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.46</v>
+        <v>36.93</v>
       </c>
       <c r="DN10" t="n">
         <v>1.08</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.69</v>
+        <v>17.42</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.61</v>
+        <v>39.36</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.16</v>
+        <v>12.14</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.46</v>
+        <v>7.28</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.92</v>
+        <v>20.43</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="H11" t="n">
-        <v>104.29</v>
+        <v>98.5</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K11" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="M11" t="n">
-        <v>63.29</v>
+        <v>58.88</v>
       </c>
       <c r="N11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="P11" t="n">
-        <v>14.14</v>
+        <v>14.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="R11" t="n">
-        <v>4.57</v>
+        <v>5.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.43</v>
+        <v>59.88</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.57</v>
+        <v>11.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.29</v>
+        <v>17.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5177,70 +5177,70 @@
         <v>1.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.38</v>
+        <v>10.43</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -5252,40 +5252,40 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
@@ -5300,106 +5300,106 @@
         <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.23</v>
+        <v>102.79</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.85</v>
+        <v>56.65</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.46</v>
+        <v>11.57</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.08</v>
+        <v>5.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.54</v>
+        <v>59.22</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.92</v>
+        <v>17.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>12.62</v>
+        <v>12</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.31</v>
+        <v>5.43</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.62</v>
+        <v>18.21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.14</v>
@@ -5499,52 +5499,52 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AI12" t="n">
-        <v>101.33</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>51.5</v>
+        <v>47.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>12.43</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>58.5</v>
+        <v>57.29</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>12.71</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.17</v>
+        <v>19</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.23</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
         <v>1.8</v>
@@ -5640,73 +5640,73 @@
         <v>1.91</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI12" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CS12" t="n">
         <v>3.03</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX12" t="n">
         <v>1.67</v>
@@ -5721,88 +5721,88 @@
         <v>1.77</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DD12" t="n">
         <v>3.35</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.46</v>
+        <v>104.71</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DK12" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>57.23</v>
+        <v>54.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.15</v>
+        <v>13.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.54</v>
+        <v>11.14</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>58.46</v>
+        <v>57.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.77</v>
+        <v>15.92</v>
       </c>
       <c r="DY12" t="n">
-        <v>11.23</v>
+        <v>10.64</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.54</v>
+        <v>5.29</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.23</v>
+        <v>17.78</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="H13" t="n">
-        <v>94.17</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="K13" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M13" t="n">
-        <v>41.33</v>
+        <v>40.86</v>
       </c>
       <c r="N13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>10.33</v>
+        <v>10.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.5</v>
+        <v>18.43</v>
       </c>
       <c r="R13" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="S13" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54.33</v>
+        <v>53.29</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>13.86</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>5.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.5</v>
+        <v>18.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5983,70 +5983,70 @@
         <v>1.86</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.54</v>
+        <v>7.71</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BN13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1</v>
       </c>
-      <c r="BO13" t="n">
-        <v>0.92</v>
-      </c>
       <c r="BP13" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="BR13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT13" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BZ13" t="n">
         <v>2.3</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CC13" t="n">
         <v>4.06</v>
@@ -6061,151 +6061,151 @@
         <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI13" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CO13" t="n">
         <v>1.34</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD13" t="n">
         <v>3.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.54000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.31</v>
+        <v>39.21</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17</v>
+        <v>17.07</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.46</v>
+        <v>7.57</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.77</v>
+        <v>50.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.77</v>
+        <v>11.14</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.07</v>
+        <v>4.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.77</v>
+        <v>17.22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>97.83</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="AM14" t="n">
         <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>43.14</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP14" t="n">
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.67</v>
+        <v>13.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>41.17</v>
+        <v>42.57</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.83</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>21.43</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="BR14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY14" t="n">
         <v>3.97</v>
@@ -6446,28 +6446,28 @@
         <v>4.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.46</v>
+        <v>5.11</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.88</v>
+        <v>5.54</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI14" t="n">
         <v>1.74</v>
@@ -6476,25 +6476,25 @@
         <v>2.07</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
@@ -6503,31 +6503,31 @@
         <v>3.26</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC14" t="n">
         <v>2.42</v>
@@ -6536,46 +6536,46 @@
         <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.77</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DK14" t="n">
         <v>5.07</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.54</v>
+        <v>41.14</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.85</v>
+        <v>12.78</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.23</v>
+        <v>14.29</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.539999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.38</v>
+        <v>44.86</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.69</v>
+        <v>6.79</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="EA14" t="n">
-        <v>21</v>
+        <v>21.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G15" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="H15" t="n">
-        <v>105.33</v>
+        <v>107.43</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K15" t="n">
-        <v>5.83</v>
+        <v>6.29</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M15" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>13.83</v>
+        <v>12.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.67</v>
+        <v>13.86</v>
       </c>
       <c r="R15" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.5</v>
+        <v>54.71</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>12.86</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.67</v>
+        <v>5.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.67</v>
+        <v>19.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6789,70 +6789,70 @@
         <v>1.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.69</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.31</v>
+        <v>5.14</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="CC15" t="n">
         <v>2.35</v>
@@ -6861,13 +6861,13 @@
         <v>2.5</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
@@ -6876,46 +6876,46 @@
         <v>1.76</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP15" t="n">
         <v>2.2</v>
       </c>
-      <c r="CN15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>2.17</v>
-      </c>
       <c r="CQ15" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CS15" t="n">
         <v>3.22</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CU15" t="n">
         <v>1.36</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX15" t="n">
         <v>1.71</v>
@@ -6930,88 +6930,88 @@
         <v>1.73</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DD15" t="n">
         <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.38</v>
+        <v>103.64</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.46</v>
+        <v>5.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.54</v>
+        <v>48.43</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.23</v>
+        <v>12.71</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.7</v>
+        <v>12.86</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.460000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>56.61</v>
+        <v>56.14</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.39</v>
+        <v>13.08</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.15</v>
+        <v>7.93</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="EB15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="EC15" t="n">
         <v>1.57</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>1.54</v>
       </c>
     </row>
     <row r="16">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7920,127 +7920,127 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>105</v>
+        <v>106.29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>6</v>
+        <v>5.29</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>49.5</v>
+        <v>48.14</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.33</v>
+        <v>16.29</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.67</v>
+        <v>15.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BK18" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BL18" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BT18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BY18" t="n">
         <v>1.93</v>
@@ -8064,16 +8064,16 @@
         <v>3.52</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="CE18" t="n">
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CG18" t="n">
         <v>2.72</v>
@@ -8082,19 +8082,19 @@
         <v>1.35</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CK18" t="n">
         <v>1.7</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN18" t="n">
         <v>1.66</v>
@@ -8106,121 +8106,121 @@
         <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CU18" t="n">
         <v>1.36</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DA18" t="n">
         <v>1.71</v>
       </c>
-      <c r="CY18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>1.72</v>
-      </c>
       <c r="DB18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD18" t="n">
         <v>3.59</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>111.62</v>
+        <v>111.79</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.62</v>
+        <v>5.29</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.54</v>
+        <v>50.72</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.46</v>
+        <v>14.58</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.46</v>
+        <v>15.64</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.38</v>
+        <v>58</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.69</v>
+        <v>13.14</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.69</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.54</v>
+        <v>20.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>93.67</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K19" t="n">
-        <v>3.17</v>
+        <v>3.71</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M19" t="n">
-        <v>41.17</v>
+        <v>40.57</v>
       </c>
       <c r="N19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="R19" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48</v>
+        <v>46.86</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.5</v>
+        <v>17.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
         <v>4.58</v>
@@ -8476,10 +8476,10 @@
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
@@ -8491,19 +8491,19 @@
         <v>1.85</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
         <v>2.1</v>
@@ -8524,19 +8524,19 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DA19" t="n">
         <v>1.69</v>
@@ -8551,79 +8551,79 @@
         <v>3.22</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.31</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>35.93</v>
+        <v>36</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.69</v>
+        <v>12.86</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.08</v>
+        <v>14.14</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.31</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46</v>
+        <v>45.58</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.08</v>
+        <v>11.22</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.16</v>
+        <v>7.22</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.23</v>
+        <v>16.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.29</v>
@@ -1469,139 +1469,139 @@
         <v>1.86</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI2" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>1.77</v>
@@ -1610,25 +1610,25 @@
         <v>1.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB2" t="n">
         <v>3.86</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="CE2" t="n">
         <v>1.38</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
@@ -1640,13 +1640,13 @@
         <v>1.94</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN2" t="n">
         <v>1.78</v>
@@ -1658,13 +1658,13 @@
         <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CR2" t="n">
         <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT2" t="n">
         <v>2.94</v>
@@ -1676,19 +1676,19 @@
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB2" t="n">
         <v>1.35</v>
@@ -1697,82 +1697,82 @@
         <v>2.07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DH2" t="n">
-        <v>93.84999999999999</v>
+        <v>95.78</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.23</v>
+        <v>44.14</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DO2" t="n">
         <v>1.93</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.92</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12</v>
+        <v>12.28</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.46</v>
+        <v>6.21</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.85</v>
+        <v>50.86</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.31</v>
+        <v>13.58</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.69</v>
+        <v>17.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.17</v>
+        <v>76.14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.33</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.33</v>
+        <v>7.29</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.5</v>
+        <v>41.57</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>19.86</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>2.66</v>
@@ -4431,43 +4431,43 @@
         <v>2.74</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.64</v>
+        <v>4.44</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="CE9" t="n">
         <v>1.53</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CM9" t="n">
         <v>2.13</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
         <v>1.67</v>
@@ -4476,7 +4476,7 @@
         <v>1.49</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CQ9" t="n">
         <v>4.81</v>
@@ -4488,7 +4488,7 @@
         <v>3.33</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CU9" t="n">
         <v>1.32</v>
@@ -4515,85 +4515,85 @@
         <v>1.55</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DD9" t="n">
         <v>3.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DH9" t="n">
-        <v>88.45999999999999</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="DK9" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.61</v>
+        <v>35.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.85</v>
+        <v>14.64</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.77</v>
+        <v>14.78</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.08</v>
+        <v>6.58</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.31</v>
+        <v>48.78</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.38</v>
+        <v>12.36</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.31</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.23</v>
+        <v>21.07</v>
       </c>
       <c r="EB9" t="n">
         <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="10">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0.14</v>
@@ -7114,127 +7114,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.17</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN16" t="n">
-        <v>39.33</v>
+        <v>36.14</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>10.43</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40.83</v>
+        <v>40.71</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="BB16" t="n">
         <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.5</v>
+        <v>18.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BG16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.08</v>
+        <v>7.93</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="BR16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU16" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY16" t="n">
         <v>3.6</v>
@@ -7252,25 +7252,25 @@
         <v>4.12</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.82</v>
+        <v>4.6</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.15</v>
+        <v>4.87</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7282,25 +7282,25 @@
         <v>1.97</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7315,22 +7315,22 @@
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB16" t="n">
         <v>1.4</v>
@@ -7342,79 +7342,79 @@
         <v>3.56</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="EB16" t="n">
         <v>1.15</v>
       </c>
-      <c r="DG16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>83.39</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>38</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>11</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>42.23</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>3</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="EC16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>78.70999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="K17" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="L17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>37.57</v>
+        <v>40.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>12.86</v>
+        <v>13.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>13.12</v>
       </c>
       <c r="R17" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="S17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>42.57</v>
+        <v>44.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.71</v>
+        <v>8.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.86</v>
+        <v>18.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7595,70 +7595,70 @@
         <v>1.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.69</v>
+        <v>8.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO17" t="n">
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="BR17" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.79</v>
+        <v>4.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
         <v>6.89</v>
@@ -7667,16 +7667,16 @@
         <v>7.75</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI17" t="n">
         <v>1.76</v>
@@ -7688,7 +7688,7 @@
         <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM17" t="n">
         <v>2.08</v>
@@ -7697,13 +7697,13 @@
         <v>1.67</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="CR17" t="n">
         <v>1.46</v>
@@ -7718,16 +7718,16 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX17" t="n">
         <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.11</v>
@@ -7745,79 +7745,79 @@
         <v>3.23</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="DH17" t="n">
-        <v>77.45999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>31.62</v>
+        <v>33.86</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DP17" t="n">
-        <v>13</v>
+        <v>13.14</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.61</v>
+        <v>40.14</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.77</v>
+        <v>10.07</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.3</v>
+        <v>7.64</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.62</v>
+        <v>16.29</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="18">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>99</v>
+        <v>95.86</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>41.67</v>
+        <v>39.86</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U20" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V20" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>45.5</v>
+        <v>44.14</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.67</v>
+        <v>18.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8804,70 +8804,70 @@
         <v>2.29</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.539999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.46</v>
+        <v>5.21</v>
       </c>
       <c r="BR20" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV20" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW20" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX20" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="BZ20" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CB20" t="n">
         <v>3.5</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CB20" t="n">
-        <v>3.47</v>
       </c>
       <c r="CC20" t="n">
         <v>5.07</v>
@@ -8879,16 +8879,16 @@
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.99</v>
@@ -8897,31 +8897,31 @@
         <v>1.7</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CM20" t="n">
         <v>2.1</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8948,85 +8948,85 @@
         <v>1.42</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="DH20" t="n">
-        <v>86.54000000000001</v>
+        <v>85.86</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM20" t="n">
-        <v>36.93</v>
+        <v>36.36</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.69</v>
+        <v>13.86</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.62</v>
+        <v>10.28</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.31</v>
+        <v>42.78</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.53</v>
+        <v>11.28</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.47</v>
+        <v>7.21</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.39</v>
+        <v>16.78</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -9051,43 +9051,43 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H21" t="n">
-        <v>98.33</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K21" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M21" t="n">
-        <v>45.83</v>
+        <v>46.43</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O21" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>13.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.67</v>
+        <v>12.57</v>
       </c>
       <c r="R21" t="n">
-        <v>6.67</v>
+        <v>6.14</v>
       </c>
       <c r="S21" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -9102,28 +9102,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49</v>
+        <v>50.29</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>14.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>10.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>19.33</v>
+        <v>19.57</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.85</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.77</v>
+        <v>5.64</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="CC21" t="n">
         <v>5.15</v>
@@ -9279,22 +9279,22 @@
         <v>5.38</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CH21" t="n">
         <v>1.36</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK21" t="n">
         <v>1.52</v>
@@ -9303,37 +9303,37 @@
         <v>2.02</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CN21" t="n">
         <v>1.9</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS21" t="n">
         <v>3.07</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CU21" t="n">
         <v>1.4</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CX21" t="n">
         <v>1.59</v>
@@ -9348,10 +9348,10 @@
         <v>1.87</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="DD21" t="n">
         <v>3.14</v>
@@ -9360,76 +9360,76 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.84999999999999</v>
+        <v>91</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.77</v>
+        <v>40.5</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.85</v>
+        <v>14</v>
       </c>
       <c r="DQ21" t="n">
         <v>11.93</v>
       </c>
       <c r="DR21" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.15</v>
+        <v>47.93</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.77</v>
+        <v>12.57</v>
       </c>
       <c r="DY21" t="n">
-        <v>8</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="EA21" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="EC21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
-        <v>103.43</v>
+        <v>103.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>46.43</v>
+        <v>47.62</v>
       </c>
       <c r="N2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="R2" t="n">
-        <v>6.14</v>
+        <v>5.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.57</v>
+        <v>50.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.86</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.14</v>
+        <v>18.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,70 +1550,70 @@
         <v>1.29</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.43</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA2" t="n">
         <v>3.79</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>92.86</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3.76</v>
-      </c>
       <c r="CB2" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="CC2" t="n">
         <v>2.23</v>
@@ -1625,16 +1625,16 @@
         <v>1.38</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.94</v>
@@ -1655,10 +1655,10 @@
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CR2" t="n">
         <v>1.42</v>
@@ -1673,106 +1673,106 @@
         <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY2" t="n">
         <v>2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA2" t="n">
         <v>1.84</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.78</v>
+        <v>96.27</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.14</v>
+        <v>44.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.28</v>
+        <v>12.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.86</v>
+        <v>51.4</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.859999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.07</v>
+        <v>17.47</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="H3" t="n">
-        <v>110.29</v>
+        <v>111.62</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K3" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>58.86</v>
+        <v>57.62</v>
       </c>
       <c r="N3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>10.57</v>
+        <v>10.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.57</v>
+        <v>10.25</v>
       </c>
       <c r="R3" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.71</v>
+        <v>57.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.71</v>
+        <v>17.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.43</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CC3" t="n">
         <v>2.38</v>
@@ -2025,43 +2025,43 @@
         <v>2.36</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,22 +2076,22 @@
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
@@ -2100,49 +2100,49 @@
         <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.58</v>
+        <v>102.87</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.58</v>
+        <v>49.53</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.720000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.86</v>
+        <v>56.93</v>
       </c>
       <c r="DW3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.78</v>
+        <v>14.93</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.36</v>
+        <v>10.27</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.43</v>
+        <v>4.67</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.92</v>
+        <v>18</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="n">
-        <v>115</v>
+        <v>110.57</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J4" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="K4" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>49.14</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="P4" t="n">
-        <v>13.17</v>
+        <v>12.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.17</v>
+        <v>14.57</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>4.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>57.17</v>
+        <v>56.29</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.33</v>
+        <v>16.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>24</v>
+        <v>22.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.29</v>
+        <v>5.07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB4" t="n">
         <v>3.31</v>
@@ -2431,7 +2431,7 @@
         <v>1.47</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CG4" t="n">
         <v>2.6</v>
@@ -2440,145 +2440,145 @@
         <v>1.33</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
         <v>2.43</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CU4" t="n">
         <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.93000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>41</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="EC4" t="n">
         <v>1.93</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>1.86</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2684,133 +2684,133 @@
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>71.43000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>25.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.43</v>
+        <v>15.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.29</v>
+        <v>14.12</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>43</v>
+        <v>42.88</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.57</v>
+        <v>16.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY5" t="n">
         <v>3.6</v>
@@ -2819,28 +2819,28 @@
         <v>4.14</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.33</v>
+        <v>6.57</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.82</v>
+        <v>7.17</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI5" t="n">
         <v>1.77</v>
@@ -2849,10 +2849,10 @@
         <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM5" t="n">
         <v>2.28</v>
@@ -2861,13 +2861,13 @@
         <v>1.78</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
@@ -2882,19 +2882,19 @@
         <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX5" t="n">
         <v>1.66</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
         <v>1.78</v>
@@ -2903,10 +2903,10 @@
         <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2915,73 +2915,73 @@
         <v>1.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="DH5" t="n">
-        <v>71</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.5</v>
+        <v>28.87</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP5" t="n">
-        <v>16.36</v>
+        <v>16.27</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.79</v>
+        <v>15.6</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.220000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.57</v>
+        <v>44.4</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.14</v>
+        <v>18.06</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3484,52 +3484,52 @@
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>80.29000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.43</v>
+        <v>31.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.29</v>
+        <v>14.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>44.14</v>
+        <v>45.38</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>3.97</v>
@@ -3625,40 +3625,40 @@
         <v>4.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.15</v>
+        <v>6.74</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.039999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CM7" t="n">
         <v>2.1</v>
@@ -3667,37 +3667,37 @@
         <v>1.66</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CR7" t="n">
         <v>1.46</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX7" t="n">
         <v>1.72</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.16</v>
@@ -3706,55 +3706,55 @@
         <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
         <v>2.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.65000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.57</v>
+        <v>32.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.14</v>
+        <v>12.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.86</v>
+        <v>13.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.5</v>
+        <v>10.27</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.72</v>
+        <v>46.27</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.93</v>
+        <v>19.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G8" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="H8" t="n">
-        <v>84.33</v>
+        <v>89.86</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="K8" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="L8" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>36.5</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="P8" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="S8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.83</v>
+        <v>14.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.5</v>
+        <v>11.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.17</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,49 +3968,49 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
         <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO8" t="n">
         <v>1.07</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.07</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,19 +4019,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC8" t="n">
         <v>3.72</v>
@@ -4046,52 +4046,52 @@
         <v>3.01</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
         <v>1.35</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO8" t="n">
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW8" t="n">
         <v>1.96</v>
@@ -4112,85 +4112,85 @@
         <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD8" t="n">
         <v>3.31</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.78</v>
+        <v>89.2</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.36</v>
+        <v>4.67</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DM8" t="n">
-        <v>34.15</v>
+        <v>36.4</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.93</v>
+        <v>13.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17</v>
+        <v>17.34</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.93</v>
+        <v>51.93</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.64</v>
+        <v>12.2</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>95.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K9" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>41.14</v>
+        <v>40.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>15.43</v>
+        <v>14.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.57</v>
+        <v>15.25</v>
       </c>
       <c r="R9" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56</v>
+        <v>53.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.71</v>
+        <v>12.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>22.29</v>
+        <v>22.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4371,70 +4371,70 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="CC9" t="n">
         <v>4.44</v>
@@ -4443,13 +4443,13 @@
         <v>4.65</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CH9" t="n">
         <v>1.28</v>
@@ -4467,100 +4467,100 @@
         <v>2.25</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV9" t="n">
         <v>1.67</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="DE9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DH9" t="n">
-        <v>87.56999999999999</v>
+        <v>86.47</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.86</v>
+        <v>3.67</v>
       </c>
       <c r="DL9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.57</v>
+        <v>35.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.64</v>
+        <v>14.33</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.78</v>
+        <v>15.13</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.58</v>
+        <v>6.54</v>
       </c>
       <c r="DS9" t="n">
         <v>0.07000000000000001</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.78</v>
+        <v>47.93</v>
       </c>
       <c r="DW9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.36</v>
+        <v>11.86</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.140000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.07</v>
+        <v>21.13</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>91.56999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.43</v>
+        <v>34.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.71</v>
+        <v>18.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,73 +4750,73 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>37.14</v>
+        <v>36.75</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.14</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>22.57</v>
+        <v>21.38</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.07</v>
+        <v>8.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="BR10" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>4.13</v>
@@ -4837,19 +4837,19 @@
         <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.52</v>
+        <v>5.39</v>
       </c>
       <c r="CE10" t="n">
         <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CG10" t="n">
         <v>2.58</v>
@@ -4873,52 +4873,52 @@
         <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO10" t="n">
         <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV10" t="n">
         <v>1.77</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DD10" t="n">
         <v>3.42</v>
@@ -4927,43 +4927,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.93</v>
+        <v>36</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.42</v>
+        <v>17.73</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.57</v>
+        <v>8.66</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.14</v>
+        <v>7.4</v>
       </c>
       <c r="DS10" t="n">
         <v>0.07000000000000001</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.36</v>
+        <v>39</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.14</v>
+        <v>12.2</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.28</v>
+        <v>7.47</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.43</v>
+        <v>19.94</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>108.5</v>
+        <v>109.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN11" t="n">
-        <v>53.67</v>
+        <v>54.43</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.67</v>
+        <v>14.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="AT11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
         <v>1.39</v>
@@ -5237,79 +5237,79 @@
         <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="CC11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK11" t="n">
         <v>1.62</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN11" t="n">
         <v>1.77</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.33</v>
@@ -5321,85 +5321,85 @@
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.79</v>
+        <v>103.67</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.29</v>
+        <v>7.2</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.65</v>
+        <v>56.8</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.08</v>
+        <v>14.47</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.57</v>
+        <v>11.47</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.22</v>
+        <v>59.53</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.43</v>
+        <v>17.47</v>
       </c>
       <c r="DY11" t="n">
-        <v>12</v>
+        <v>11.87</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.43</v>
+        <v>5.6</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.21</v>
+        <v>18.53</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.14</v>
@@ -5499,52 +5499,52 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>96.70999999999999</v>
+        <v>98</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.43</v>
+        <v>46.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.43</v>
+        <v>12.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>57.29</v>
+        <v>56.25</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.71</v>
+        <v>12.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="BR12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY12" t="n">
         <v>1.8</v>
@@ -5640,43 +5640,43 @@
         <v>1.91</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
         <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN12" t="n">
         <v>1.78</v>
@@ -5688,10 +5688,10 @@
         <v>2.09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS12" t="n">
         <v>3.03</v>
@@ -5703,73 +5703,73 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX12" t="n">
         <v>1.67</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.24</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.71</v>
+        <v>104.86</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.78</v>
+        <v>53.93</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.28</v>
+        <v>13.13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.14</v>
+        <v>11.07</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
       <c r="DS12" t="n">
         <v>0.14</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.86</v>
+        <v>57.27</v>
       </c>
       <c r="DW12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.92</v>
+        <v>15.73</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.29</v>
+        <v>5.13</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.78</v>
+        <v>17.73</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.43</v>
@@ -5902,52 +5902,52 @@
         <v>1.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.56999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.57</v>
+        <v>36</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.71</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.71</v>
+        <v>48.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.43</v>
+        <v>9.25</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.14</v>
+        <v>15.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BN13" t="n">
         <v>0.93</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BR13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BY13" t="n">
         <v>2.18</v>
@@ -6043,22 +6043,22 @@
         <v>2.3</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.06</v>
+        <v>3.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.4</v>
+        <v>4.12</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CG13" t="n">
         <v>2.71</v>
@@ -6067,46 +6067,46 @@
         <v>1.36</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CR13" t="n">
         <v>1.44</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
         <v>2.03</v>
@@ -6124,55 +6124,55 @@
         <v>1.79</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD13" t="n">
         <v>3.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.56999999999999</v>
+        <v>89.27</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>39.21</v>
+        <v>38.27</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.07</v>
+        <v>16.87</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.57</v>
+        <v>7.87</v>
       </c>
       <c r="DS13" t="n">
         <v>0.07000000000000001</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.5</v>
+        <v>50.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.14</v>
+        <v>11.4</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.71</v>
+        <v>6.93</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.22</v>
+        <v>16.8</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -6215,25 +6215,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="H14" t="n">
-        <v>90.29000000000001</v>
+        <v>88.38</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -6242,34 +6242,34 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.71</v>
+        <v>5.62</v>
       </c>
       <c r="L14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>39.14</v>
+        <v>39.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>12.14</v>
+        <v>12.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.29</v>
+        <v>14.12</v>
       </c>
       <c r="R14" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,25 +6281,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.14</v>
+        <v>47.62</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.859999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.57</v>
+        <v>8</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AC14" t="n">
         <v>21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -6386,70 +6386,70 @@
         <v>1.57</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.97</v>
+        <v>3.78</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="CC14" t="n">
         <v>5.11</v>
@@ -6458,13 +6458,13 @@
         <v>5.54</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH14" t="n">
         <v>1.31</v>
@@ -6473,28 +6473,28 @@
         <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.26</v>
+        <v>4.38</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
@@ -6509,73 +6509,73 @@
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DD14" t="n">
         <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.65000000000001</v>
+        <v>93.34</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.07</v>
+        <v>5.53</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.14</v>
+        <v>41.2</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.78</v>
+        <v>13.07</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.29</v>
+        <v>13.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.86</v>
+        <v>45.26</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.5</v>
+        <v>10.27</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.79</v>
+        <v>7.53</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.22</v>
+        <v>21.2</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,139 +6708,139 @@
         <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AI15" t="n">
-        <v>99.86</v>
+        <v>99.12</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>49</v>
+        <v>48.88</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AP15" t="n">
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.71</v>
+        <v>12.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.86</v>
+        <v>12.38</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>57.57</v>
+        <v>58.12</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.29</v>
+        <v>12.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.86</v>
+        <v>4.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.86</v>
+        <v>17.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.710000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.01</v>
@@ -6849,31 +6849,31 @@
         <v>2.13</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.07</v>
@@ -6882,13 +6882,13 @@
         <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM15" t="n">
         <v>2.19</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO15" t="n">
         <v>1.38</v>
@@ -6897,16 +6897,16 @@
         <v>2.2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU15" t="n">
         <v>1.36</v>
@@ -6939,79 +6939,79 @@
         <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.64</v>
+        <v>103</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.71</v>
+        <v>5.54</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.43</v>
+        <v>48.4</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.71</v>
+        <v>12.46</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.86</v>
+        <v>13.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>56.14</v>
+        <v>56.53</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.08</v>
+        <v>12.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.93</v>
+        <v>7.87</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.14</v>
+        <v>4.8</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>87</v>
+        <v>87.75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>36.86</v>
+        <v>38.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.29</v>
+        <v>13.5</v>
       </c>
       <c r="R16" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.43</v>
+        <v>43.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.14</v>
+        <v>12.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.29</v>
+        <v>16.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,49 +7192,49 @@
         <v>2.29</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BH16" t="n">
         <v>7.93</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BR16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC16" t="n">
         <v>4.6</v>
@@ -7267,46 +7267,46 @@
         <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CG16" t="n">
         <v>2.69</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO16" t="n">
         <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT16" t="n">
         <v>2.72</v>
@@ -7336,85 +7336,85 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD16" t="n">
         <v>3.56</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.84999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
         <v>2.14</v>
       </c>
       <c r="DK16" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM16" t="n">
-        <v>36.5</v>
+        <v>37.27</v>
       </c>
       <c r="DN16" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DO16" t="n">
         <v>0.93</v>
       </c>
-      <c r="DO16" t="n">
-        <v>1</v>
-      </c>
       <c r="DP16" t="n">
-        <v>10.72</v>
+        <v>10.94</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.36</v>
+        <v>13.93</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.279999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.07</v>
+        <v>42.4</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.78</v>
+        <v>11.33</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.86</v>
+        <v>8.27</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.29</v>
+        <v>17.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AI17" t="n">
-        <v>76</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>24.67</v>
+        <v>26.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.17</v>
+        <v>12.14</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>11.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>34</v>
+        <v>36.14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.83</v>
+        <v>6.57</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="BD17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
         <v>1.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS17" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
         <v>3.74</v>
@@ -7655,34 +7655,34 @@
         <v>4.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.89</v>
+        <v>6.39</v>
       </c>
       <c r="CD17" t="n">
-        <v>7.75</v>
+        <v>7.14</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
         <v>1.71</v>
@@ -7697,13 +7697,13 @@
         <v>1.67</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="CR17" t="n">
         <v>1.46</v>
@@ -7718,16 +7718,16 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CX17" t="n">
         <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.11</v>
@@ -7736,10 +7736,10 @@
         <v>1.68</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DD17" t="n">
         <v>3.23</v>
@@ -7748,76 +7748,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="DH17" t="n">
-        <v>80.5</v>
+        <v>79.94</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM17" t="n">
-        <v>33.86</v>
+        <v>34.07</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.14</v>
+        <v>12.66</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.14</v>
+        <v>40.73</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.07</v>
+        <v>9.73</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.64</v>
+        <v>7.47</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.29</v>
+        <v>16.53</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="18">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.29</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>83.70999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.43</v>
+        <v>32.62</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.14</v>
       </c>
-      <c r="AU19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BF19" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY19" t="n">
         <v>3.21</v>
@@ -8461,55 +8461,55 @@
         <v>3.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.58</v>
+        <v>4.93</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.87</v>
+        <v>5.16</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG19" t="n">
         <v>2.8</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL19" t="n">
         <v>2.19</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO19" t="n">
         <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
@@ -8524,106 +8524,106 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE19" t="n">
         <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.06999999999999</v>
+        <v>85.87</v>
       </c>
       <c r="DI19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM19" t="n">
-        <v>36</v>
+        <v>36.33</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.86</v>
+        <v>12.8</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.58</v>
+        <v>45.27</v>
       </c>
       <c r="DW19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.22</v>
+        <v>7.07</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.28</v>
+        <v>16.13</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>95.86</v>
+        <v>98.25</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K20" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>39.86</v>
+        <v>41.38</v>
       </c>
       <c r="N20" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>13.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="R20" t="n">
-        <v>9.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>44.14</v>
+        <v>44.38</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.86</v>
+        <v>11.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.14</v>
+        <v>7.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.14</v>
+        <v>18.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8804,70 +8804,70 @@
         <v>2.29</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.359999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.93</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="BR20" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS20" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT20" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.83</v>
+        <v>3.61</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC20" t="n">
         <v>5.07</v>
@@ -8879,7 +8879,7 @@
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CG20" t="n">
         <v>2.63</v>
@@ -8888,16 +8888,16 @@
         <v>1.35</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM20" t="n">
         <v>2.1</v>
@@ -8909,124 +8909,124 @@
         <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA20" t="n">
         <v>1.7</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF20" t="n">
         <v>1.14</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DH20" t="n">
-        <v>85.86</v>
+        <v>87.8</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="DL20" t="n">
         <v>0.14</v>
       </c>
       <c r="DM20" t="n">
-        <v>36.36</v>
+        <v>37.4</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.86</v>
+        <v>14.27</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.28</v>
+        <v>10.47</v>
       </c>
       <c r="DR20" t="n">
-        <v>9.140000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>42.78</v>
+        <v>43</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.28</v>
+        <v>11.73</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.21</v>
+        <v>7.54</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.78</v>
+        <v>17.2</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -9048,46 +9048,46 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G21" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
-        <v>97.56999999999999</v>
+        <v>96.12</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M21" t="n">
-        <v>46.43</v>
+        <v>45.12</v>
       </c>
       <c r="N21" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="P21" t="n">
-        <v>13.43</v>
+        <v>13.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.57</v>
+        <v>12.12</v>
       </c>
       <c r="R21" t="n">
-        <v>6.14</v>
+        <v>6.88</v>
       </c>
       <c r="S21" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -9102,28 +9102,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>50.29</v>
+        <v>48.75</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>19.57</v>
+        <v>18.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.710000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.07</v>
+        <v>3.93</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU21" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC21" t="n">
         <v>5.15</v>
@@ -9282,76 +9282,76 @@
         <v>1.45</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.94</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP21" t="n">
         <v>2.18</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CR21" t="n">
         <v>1.48</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DB21" t="n">
         <v>1.41</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD21" t="n">
         <v>3.14</v>
@@ -9360,43 +9360,43 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="DH21" t="n">
-        <v>91</v>
+        <v>90.66</v>
       </c>
       <c r="DI21" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.93</v>
+        <v>4.67</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.5</v>
+        <v>40.2</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="DP21" t="n">
-        <v>14</v>
+        <v>14.13</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.93</v>
+        <v>11.73</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.64</v>
+        <v>7.93</v>
       </c>
       <c r="DS21" t="n">
         <v>0.14</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.93</v>
+        <v>47.27</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.57</v>
+        <v>12.93</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.640000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.14</v>
+        <v>18.53</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.75</v>
+        <v>57.88</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.93</v>
+        <v>57</v>
       </c>
       <c r="DW3" t="n">
         <v>0.07000000000000001</v>
@@ -2257,10 +2257,10 @@
         <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.57</v>
+        <v>16.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="AB4" t="n">
         <v>4.57</v>
@@ -2269,7 +2269,7 @@
         <v>22.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="n">
         <v>1.57</v>
@@ -2413,13 +2413,13 @@
         <v>2.22</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CA4" t="n">
         <v>3.23</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC4" t="n">
         <v>2.8</v>
@@ -2467,7 +2467,7 @@
         <v>4.02</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS4" t="n">
         <v>3.26</v>
@@ -2482,7 +2482,7 @@
         <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX4" t="n">
         <v>1.77</v>
@@ -2503,7 +2503,7 @@
         <v>2.39</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
@@ -2563,10 +2563,10 @@
         <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.73</v>
+        <v>13.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.33</v>
+        <v>9.27</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.4</v>
@@ -2575,7 +2575,7 @@
         <v>19.87</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC4" t="n">
         <v>1.93</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.88</v>
+        <v>42.75</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.4</v>
+        <v>44.33</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.29</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>96.43000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>45.86</v>
+        <v>44.38</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.57</v>
+        <v>14.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.71</v>
+        <v>12.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.29</v>
+        <v>6.88</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60.43</v>
+        <v>58.75</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.29</v>
+        <v>13.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.43</v>
+        <v>9.75</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.86</v>
+        <v>17.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.71</v>
+        <v>7.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>1.9</v>
@@ -3222,28 +3222,28 @@
         <v>1.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
         <v>1.89</v>
@@ -3255,31 +3255,31 @@
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO6" t="n">
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
@@ -3291,22 +3291,22 @@
         <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD6" t="n">
         <v>3.34</v>
@@ -3315,43 +3315,43 @@
         <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="DG6" t="n">
         <v>1.93</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.28</v>
+        <v>102.13</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.72</v>
+        <v>43.07</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.22</v>
+        <v>14.73</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.28</v>
+        <v>13.47</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.93</v>
+        <v>6.27</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.78</v>
+        <v>59.87</v>
       </c>
       <c r="DW6" t="n">
         <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.86</v>
+        <v>13.8</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.22</v>
+        <v>4.93</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.86</v>
+        <v>20.13</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="7">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51</v>
+        <v>50.86</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.93</v>
+        <v>51.87</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
         <v>2.38</v>
@@ -4224,7 +4224,7 @@
         <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.5</v>
@@ -4281,13 +4281,13 @@
         <v>3.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>22.25</v>
+        <v>22.38</v>
       </c>
       <c r="AD9" t="n">
         <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4524,7 +4524,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DG9" t="n">
         <v>2.4</v>
@@ -4536,7 +4536,7 @@
         <v>0.26</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DK9" t="n">
         <v>3.67</v>
@@ -4587,13 +4587,13 @@
         <v>4.13</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.13</v>
+        <v>21.2</v>
       </c>
       <c r="EB9" t="n">
         <v>1.3</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>36.75</v>
+        <v>36.88</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39</v>
+        <v>39.07</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
@@ -5643,13 +5643,13 @@
         <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC12" t="n">
         <v>2.08</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
@@ -5694,16 +5694,16 @@
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW12" t="n">
         <v>2.04</v>
@@ -5724,10 +5724,10 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="DE12" t="n">
         <v>0.13</v>
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>117.29</v>
+        <v>116.12</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="L18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>53.29</v>
+        <v>53.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>12.86</v>
+        <v>13.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.14</v>
+        <v>15.12</v>
       </c>
       <c r="R18" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>58.86</v>
+        <v>58.12</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.57</v>
+        <v>21.38</v>
       </c>
       <c r="AD18" t="n">
         <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,49 +7998,49 @@
         <v>2.14</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.789999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,19 +8049,19 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC18" t="n">
         <v>2.2</v>
@@ -8073,154 +8073,154 @@
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU18" t="n">
         <v>1.36</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD18" t="n">
         <v>3.59</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DH18" t="n">
-        <v>111.79</v>
+        <v>111.53</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.29</v>
+        <v>5.34</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM18" t="n">
-        <v>50.72</v>
+        <v>51.13</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.58</v>
+        <v>14.67</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.64</v>
+        <v>15.13</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58</v>
+        <v>57.66</v>
       </c>
       <c r="DW18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.14</v>
+        <v>13.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.359999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.78</v>
+        <v>4.73</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.14</v>
+        <v>20.6</v>
       </c>
       <c r="EB18" t="n">
         <v>1.54</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="n">
-        <v>70.56999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="K5" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>33</v>
+        <v>33.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O5" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
-        <v>17.29</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="R5" t="n">
-        <v>7.86</v>
+        <v>8.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46.14</v>
+        <v>47.75</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.71</v>
+        <v>20.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>6.57</v>
@@ -2831,16 +2831,16 @@
         <v>7.17</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI5" t="n">
         <v>1.77</v>
@@ -2852,34 +2852,34 @@
         <v>1.6</v>
       </c>
       <c r="CL5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CP5" t="n">
         <v>2.12</v>
       </c>
-      <c r="CM5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>2.11</v>
-      </c>
       <c r="CQ5" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV5" t="n">
         <v>1.78</v>
@@ -2891,10 +2891,10 @@
         <v>1.66</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA5" t="n">
         <v>1.78</v>
@@ -2903,7 +2903,7 @@
         <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD5" t="n">
         <v>3.34</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DH5" t="n">
-        <v>71.93000000000001</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.87</v>
+        <v>29.25</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="DP5" t="n">
-        <v>16.27</v>
+        <v>16.19</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.6</v>
+        <v>15.87</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.27</v>
+        <v>9.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.33</v>
+        <v>45.25</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.6</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.2</v>
+        <v>6.38</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.06</v>
+        <v>18.37</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3484,52 +3484,52 @@
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.38</v>
+        <v>79.89</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.75</v>
+        <v>29.78</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.12</v>
+        <v>13.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.12</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.12</v>
+        <v>10.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.38</v>
+        <v>45.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>19</v>
+        <v>19.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.27</v>
+        <v>9.81</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY7" t="n">
         <v>3.97</v>
@@ -3625,22 +3625,22 @@
         <v>4.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
         <v>4.02</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.74</v>
+        <v>6.69</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.52</v>
+        <v>7.47</v>
       </c>
       <c r="CE7" t="n">
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
         <v>2.8</v>
@@ -3655,16 +3655,16 @@
         <v>1.96</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
@@ -3673,13 +3673,13 @@
         <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT7" t="n">
         <v>2.8</v>
@@ -3691,103 +3691,103 @@
         <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="DE7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="DS7" t="n">
         <v>0.13</v>
       </c>
-      <c r="DF7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="DL7" t="n">
+      <c r="DT7" t="n">
         <v>0.13</v>
       </c>
-      <c r="DM7" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.27</v>
+        <v>46.06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.6</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.27</v>
+        <v>5.37</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.8</v>
+        <v>19.87</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="8">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H12" t="n">
-        <v>112.71</v>
+        <v>109.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="K12" t="n">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M12" t="n">
-        <v>62.14</v>
+        <v>61.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O12" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>11.57</v>
+        <v>11.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="R12" t="n">
         <v>6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.43</v>
+        <v>56.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.14</v>
+        <v>18.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.29</v>
+        <v>11.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.86</v>
+        <v>7.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.57</v>
+        <v>18.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0.12</v>
@@ -5580,70 +5580,70 @@
         <v>1.88</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.07</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="BR12" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="CC12" t="n">
         <v>2.08</v>
@@ -5652,34 +5652,34 @@
         <v>2.16</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL12" t="n">
         <v>2.08</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5688,37 +5688,37 @@
         <v>2.09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW12" t="n">
         <v>2.04</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
@@ -5730,79 +5730,79 @@
         <v>3.39</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.86</v>
+        <v>103.75</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM12" t="n">
-        <v>53.93</v>
+        <v>53.94</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.13</v>
+        <v>13.19</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.07</v>
+        <v>11.18</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.27</v>
+        <v>56.25</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.73</v>
+        <v>15.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.6</v>
+        <v>10.18</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.13</v>
+        <v>5.37</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.73</v>
+        <v>18.44</v>
       </c>
       <c r="EB12" t="n">
         <v>1.75</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H13" t="n">
-        <v>93.56999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="K13" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>40.86</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.43</v>
+        <v>18.75</v>
       </c>
       <c r="R13" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.29</v>
+        <v>53.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.86</v>
+        <v>13.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.29</v>
+        <v>17.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5983,70 +5983,70 @@
         <v>1.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.73</v>
+        <v>7.44</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="BR13" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT13" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BU13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CC13" t="n">
         <v>3.82</v>
@@ -6055,7 +6055,7 @@
         <v>4.12</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
         <v>3.03</v>
@@ -6070,28 +6070,28 @@
         <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK13" t="n">
         <v>1.57</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP13" t="n">
         <v>2.16</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CR13" t="n">
         <v>1.44</v>
@@ -6109,13 +6109,13 @@
         <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.28</v>
@@ -6124,88 +6124,88 @@
         <v>1.79</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.27</v>
+        <v>90.56</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.27</v>
+        <v>38</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.8</v>
+        <v>10.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.87</v>
+        <v>17.12</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.87</v>
+        <v>7.88</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.67</v>
+        <v>51.06</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.93</v>
+        <v>6.88</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.8</v>
+        <v>16.62</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>75.43000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.43</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.14</v>
+        <v>13.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.71</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>36.14</v>
+        <v>36.75</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.57</v>
+        <v>7.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BD17" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BG17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="BR17" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS17" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY17" t="n">
         <v>3.74</v>
@@ -7655,25 +7655,25 @@
         <v>4.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.39</v>
+        <v>6.01</v>
       </c>
       <c r="CD17" t="n">
-        <v>7.14</v>
+        <v>6.73</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7682,19 +7682,19 @@
         <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL17" t="n">
         <v>2.24</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO17" t="n">
         <v>1.37</v>
@@ -7703,58 +7703,58 @@
         <v>2.2</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CU17" t="n">
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
         <v>2.13</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DA17" t="n">
         <v>1.68</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD17" t="n">
         <v>3.23</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>79.94</v>
+        <v>80.19</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7763,61 +7763,61 @@
         <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DM17" t="n">
-        <v>34.07</v>
+        <v>34.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.66</v>
+        <v>13.12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.73</v>
+        <v>40.75</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.73</v>
+        <v>10.06</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.47</v>
+        <v>7.75</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>106.29</v>
+        <v>109</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>48.14</v>
+        <v>49.75</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.29</v>
+        <v>15.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.140000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>57.14</v>
+        <v>57.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.86</v>
+        <v>7.12</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.71</v>
+        <v>20.12</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BY18" t="n">
         <v>1.95</v>
@@ -8058,40 +8058,40 @@
         <v>2.13</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH18" t="n">
         <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK18" t="n">
         <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM18" t="n">
         <v>2.08</v>
@@ -8106,13 +8106,13 @@
         <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT18" t="n">
         <v>2.76</v>
@@ -8121,22 +8121,22 @@
         <v>1.36</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX18" t="n">
         <v>1.75</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
@@ -8151,43 +8151,43 @@
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>111.53</v>
+        <v>112.56</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.34</v>
+        <v>5.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.13</v>
+        <v>51.75</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.67</v>
+        <v>14.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.13</v>
+        <v>15.06</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.8</v>
+        <v>6.62</v>
       </c>
       <c r="DS18" t="n">
         <v>0.06</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.66</v>
+        <v>57.75</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.2</v>
+        <v>13.25</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.6</v>
+        <v>20.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>90.43000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>40.57</v>
+        <v>39.62</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="O19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.86</v>
+        <v>15.12</v>
       </c>
       <c r="R19" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>46.86</v>
+        <v>47.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.43</v>
+        <v>11.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.57</v>
+        <v>8.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.43</v>
+        <v>18</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.27</v>
+        <v>8.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC19" t="n">
         <v>4.93</v>
@@ -8476,10 +8476,10 @@
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH19" t="n">
         <v>1.39</v>
@@ -8500,7 +8500,7 @@
         <v>2.21</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
         <v>1.34</v>
@@ -8509,19 +8509,19 @@
         <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
         <v>1.95</v>
@@ -8536,94 +8536,94 @@
         <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA19" t="n">
         <v>1.7</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
         <v>3.23</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.87</v>
+        <v>87.19</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.33</v>
+        <v>36.12</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.8</v>
+        <v>12.94</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14</v>
+        <v>14.18</v>
       </c>
       <c r="DR19" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.27</v>
+        <v>45.75</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.07</v>
+        <v>7</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.13</v>
+        <v>16.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0.12</v>
@@ -8726,136 +8726,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>75.86</v>
+        <v>79.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN20" t="n">
-        <v>32.86</v>
+        <v>32.12</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.71</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.86</v>
+        <v>12.12</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>41.43</v>
+        <v>42.12</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>15.43</v>
+        <v>15.88</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="BR20" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS20" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU20" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV20" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY20" t="n">
         <v>3.39</v>
@@ -8864,43 +8864,43 @@
         <v>3.61</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC20" t="n">
-        <v>5.07</v>
+        <v>4.84</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.61</v>
+        <v>5.32</v>
       </c>
       <c r="CE20" t="n">
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH20" t="n">
         <v>1.35</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN20" t="n">
         <v>1.69</v>
@@ -8909,7 +8909,7 @@
         <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ20" t="n">
         <v>3.96</v>
@@ -8918,7 +8918,7 @@
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT20" t="n">
         <v>2.74</v>
@@ -8927,7 +8927,7 @@
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW20" t="n">
         <v>2.04</v>
@@ -8942,7 +8942,7 @@
         <v>2.15</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB20" t="n">
         <v>1.41</v>
@@ -8957,76 +8957,76 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DH20" t="n">
-        <v>87.8</v>
+        <v>88.75</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.4</v>
+        <v>36.75</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.27</v>
+        <v>14.44</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.47</v>
+        <v>10.68</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43</v>
+        <v>43.25</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.73</v>
+        <v>11.62</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.54</v>
+        <v>7.38</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.2</v>
+        <v>17.32</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>92.86</v>
+        <v>96.38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.29</v>
+        <v>46.88</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.859999999999999</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56</v>
+        <v>57.88</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.86</v>
+        <v>12.38</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.14</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.81</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.47</v>
+        <v>4.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY3" t="n">
         <v>1.7</v>
@@ -2013,55 +2013,55 @@
         <v>1.77</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM3" t="n">
         <v>2.16</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,7 +2076,7 @@
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW3" t="n">
         <v>1.88</v>
@@ -2085,97 +2085,97 @@
         <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.87</v>
+        <v>104</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.6</v>
+        <v>5.88</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.53</v>
+        <v>52.25</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.4</v>
+        <v>10.94</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.07</v>
+        <v>10.12</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57</v>
+        <v>57.88</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.93</v>
+        <v>15</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.27</v>
+        <v>10.38</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="EA3" t="n">
-        <v>18</v>
+        <v>17.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="4">
@@ -2816,13 +2816,13 @@
         <v>3.42</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CA5" t="n">
         <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC5" t="n">
         <v>6.57</v>
@@ -2885,25 +2885,25 @@
         <v>1.78</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX5" t="n">
         <v>1.66</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB5" t="n">
         <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD5" t="n">
         <v>3.34</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>89.86</v>
+        <v>89.62</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>41.38</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>13.86</v>
+        <v>13.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>17.62</v>
       </c>
       <c r="R8" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.86</v>
+        <v>52.38</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.71</v>
+        <v>15.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>15.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.07</v>
+        <v>3.88</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC8" t="n">
         <v>3.72</v>
@@ -4043,31 +4043,31 @@
         <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH8" t="n">
         <v>1.35</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CO8" t="n">
         <v>1.35</v>
@@ -4076,16 +4076,16 @@
         <v>2.14</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CR8" t="n">
         <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
@@ -4097,16 +4097,16 @@
         <v>1.96</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB8" t="n">
         <v>1.4</v>
@@ -4115,82 +4115,82 @@
         <v>2.24</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.2</v>
+        <v>89.12</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.67</v>
+        <v>4.44</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM8" t="n">
-        <v>36.4</v>
+        <v>36.88</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.67</v>
+        <v>13.44</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.34</v>
+        <v>16.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.87</v>
+        <v>52.56</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.2</v>
+        <v>12.69</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.8</v>
+        <v>15.88</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
-        <v>95.5</v>
+        <v>92.67</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>40.25</v>
+        <v>39.22</v>
       </c>
       <c r="N9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>14.75</v>
+        <v>14.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.25</v>
+        <v>15.67</v>
       </c>
       <c r="R9" t="n">
-        <v>5.88</v>
+        <v>7.22</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>53.5</v>
+        <v>50.78</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.62</v>
+        <v>11.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>8.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>22.38</v>
+        <v>21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4371,70 +4371,70 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.27</v>
+        <v>8.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="CA9" t="n">
         <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CC9" t="n">
         <v>4.44</v>
@@ -4446,7 +4446,7 @@
         <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CG9" t="n">
         <v>2.45</v>
@@ -4455,16 +4455,16 @@
         <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CM9" t="n">
         <v>2.12</v>
@@ -4479,7 +4479,7 @@
         <v>2.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="CR9" t="n">
         <v>1.57</v>
@@ -4494,16 +4494,16 @@
         <v>1.33</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.08</v>
@@ -4512,88 +4512,88 @@
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.47</v>
+        <v>85.44</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.67</v>
+        <v>3.81</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.47</v>
+        <v>35.19</v>
       </c>
       <c r="DN9" t="n">
         <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.33</v>
+        <v>14.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.13</v>
+        <v>15.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.54</v>
+        <v>7.25</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.93</v>
+        <v>46.75</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.86</v>
+        <v>11.5</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.74</v>
+        <v>7.44</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10">
@@ -7658,13 +7658,13 @@
         <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CC17" t="n">
         <v>6.01</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
       <c r="CE17" t="n">
         <v>1.47</v>
@@ -7718,28 +7718,28 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW17" t="n">
         <v>2.13</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD17" t="n">
         <v>3.23</v>
@@ -7950,7 +7950,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.75</v>
+        <v>15.88</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
@@ -8181,7 +8181,7 @@
         <v>1.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.5</v>
+        <v>14.57</v>
       </c>
       <c r="DQ18" t="n">
         <v>15.06</v>
@@ -8515,13 +8515,13 @@
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV19" t="n">
         <v>1.95</v>
@@ -8536,16 +8536,16 @@
         <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA19" t="n">
         <v>1.7</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD19" t="n">
         <v>3.23</v>
@@ -8873,7 +8873,7 @@
         <v>4.84</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="CE20" t="n">
         <v>1.46</v>
@@ -8921,7 +8921,7 @@
         <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8930,7 +8930,7 @@
         <v>1.85</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX20" t="n">
         <v>1.72</v>
@@ -8942,7 +8942,7 @@
         <v>2.15</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB20" t="n">
         <v>1.41</v>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AI21" t="n">
-        <v>84.43000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN21" t="n">
-        <v>34.57</v>
+        <v>33.75</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.57</v>
+        <v>13.75</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.29</v>
+        <v>11.12</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>45.57</v>
+        <v>44.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.71</v>
+        <v>10.75</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.71</v>
+        <v>18</v>
       </c>
       <c r="BE21" t="n">
         <v>1.18</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.33</v>
+        <v>9.06</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY21" t="n">
         <v>3.06</v>
@@ -9267,16 +9267,16 @@
         <v>3.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.15</v>
+        <v>4.97</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.38</v>
+        <v>5.19</v>
       </c>
       <c r="CE21" t="n">
         <v>1.45</v>
@@ -9285,7 +9285,7 @@
         <v>3.09</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH21" t="n">
         <v>1.35</v>
@@ -9297,13 +9297,13 @@
         <v>1.94</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN21" t="n">
         <v>1.89</v>
@@ -9321,10 +9321,10 @@
         <v>1.48</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU21" t="n">
         <v>1.39</v>
@@ -9342,7 +9342,7 @@
         <v>1.99</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA21" t="n">
         <v>1.85</v>
@@ -9354,82 +9354,82 @@
         <v>2.25</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.66</v>
+        <v>89.81</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM21" t="n">
-        <v>40.2</v>
+        <v>39.44</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.13</v>
+        <v>13.75</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.73</v>
+        <v>11.62</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.27</v>
+        <v>46.62</v>
       </c>
       <c r="DW21" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.93</v>
+        <v>12.82</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.93</v>
+        <v>8.81</v>
       </c>
       <c r="DZ21" t="n">
         <v>4</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.53</v>
+        <v>18.19</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.12</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.25</v>
+        <v>24.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.75</v>
+        <v>42.89</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.62</v>
+        <v>16.11</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ5" t="n">
         <v>4.12</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
         <v>3.42</v>
@@ -2819,16 +2819,16 @@
         <v>3.87</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.57</v>
+        <v>6.28</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.17</v>
+        <v>6.96</v>
       </c>
       <c r="CE5" t="n">
         <v>1.45</v>
@@ -2849,16 +2849,16 @@
         <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO5" t="n">
         <v>1.36</v>
@@ -2867,7 +2867,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
@@ -2888,16 +2888,16 @@
         <v>2.14</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB5" t="n">
         <v>1.42</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.18000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM5" t="n">
-        <v>29.25</v>
+        <v>28.59</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP5" t="n">
-        <v>16.19</v>
+        <v>16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.87</v>
+        <v>15.76</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.25</v>
+        <v>45.18</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.37</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
         <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.29</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>93.38</v>
+        <v>92.89</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.38</v>
+        <v>43.44</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.62</v>
+        <v>15.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.75</v>
+        <v>59.11</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.25</v>
+        <v>13.11</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.75</v>
+        <v>9.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="BE6" t="n">
         <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.8</v>
+        <v>7.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT6" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
         <v>1.9</v>
@@ -3225,31 +3225,31 @@
         <v>3.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.49</v>
+        <v>3.31</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
@@ -3258,37 +3258,37 @@
         <v>2.32</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
         <v>1.82</v>
@@ -3303,55 +3303,55 @@
         <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
         <v>3.34</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.13</v>
+        <v>101.31</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.07</v>
+        <v>42.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.73</v>
+        <v>15.32</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.47</v>
+        <v>13.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.27</v>
+        <v>6.31</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>59.87</v>
+        <v>60</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.8</v>
+        <v>13.69</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.869999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
         <v>20.13</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3887,139 +3887,139 @@
         <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>88.62</v>
+        <v>90.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>32.38</v>
+        <v>37.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.88</v>
+        <v>15.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>52.75</v>
+        <v>53.33</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>11.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.88</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.12</v>
+        <v>5.18</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.61</v>
@@ -4031,22 +4031,22 @@
         <v>3.3</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.11</v>
+        <v>3.89</v>
       </c>
       <c r="CE8" t="n">
         <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
         <v>1.35</v>
@@ -4055,13 +4055,13 @@
         <v>1.84</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK8" t="n">
         <v>1.78</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM8" t="n">
         <v>2</v>
@@ -4073,28 +4073,28 @@
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS8" t="n">
         <v>3.19</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
@@ -4112,85 +4112,85 @@
         <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.12</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DM8" t="n">
-        <v>36.88</v>
+        <v>39.53</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.44</v>
+        <v>13.53</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.75</v>
+        <v>16.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.12</v>
+        <v>7.3</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.56</v>
+        <v>52.88</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.69</v>
+        <v>13.29</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.69</v>
+        <v>10.23</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.88</v>
+        <v>16.18</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="9">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5499,53 +5499,53 @@
         <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>98</v>
+        <v>97.89</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.75</v>
+        <v>49.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.5</v>
+        <v>14.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.12</v>
+        <v>11.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="AT12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU12" t="n">
         <v>1</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>56.25</v>
+        <v>56.56</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.75</v>
+        <v>12.89</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.75</v>
+        <v>19.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY12" t="n">
         <v>1.83</v>
@@ -5640,22 +5640,22 @@
         <v>1.92</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CC12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CD12" t="n">
         <v>2.08</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>2.16</v>
       </c>
       <c r="CE12" t="n">
         <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG12" t="n">
         <v>2.76</v>
@@ -5664,31 +5664,31 @@
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CR12" t="n">
         <v>1.45</v>
@@ -5703,19 +5703,19 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA12" t="n">
         <v>1.75</v>
@@ -5724,52 +5724,52 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="DH12" t="n">
-        <v>103.75</v>
+        <v>103.35</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.44</v>
+        <v>4.64</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM12" t="n">
-        <v>53.94</v>
+        <v>54.88</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.19</v>
+        <v>13.12</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.18</v>
+        <v>11.12</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="DS12" t="n">
         <v>0.12</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.25</v>
+        <v>56.41</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.56</v>
+        <v>15.47</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.18</v>
+        <v>10.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.37</v>
+        <v>5.41</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.44</v>
+        <v>18.82</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5902,52 +5902,52 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.5</v>
+        <v>84.33</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>36</v>
+        <v>34.44</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.88</v>
+        <v>11.22</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.5</v>
+        <v>15.89</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.38</v>
+        <v>49</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.38</v>
+        <v>6.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.44</v>
+        <v>7.65</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT13" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BY13" t="n">
         <v>2.11</v>
@@ -6043,25 +6043,25 @@
         <v>2.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH13" t="n">
         <v>1.36</v>
@@ -6073,103 +6073,103 @@
         <v>1.96</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS13" t="n">
         <v>3.15</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CZ13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DC13" t="n">
         <v>2.28</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>2.24</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.56</v>
+        <v>89.64</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>38</v>
+        <v>37.06</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.94</v>
+        <v>11.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.12</v>
+        <v>17.24</v>
       </c>
       <c r="DR13" t="n">
         <v>7.88</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.06</v>
+        <v>51.24</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.18</v>
+        <v>11.35</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.88</v>
+        <v>7.18</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.31</v>
+        <v>4.18</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.62</v>
+        <v>16.35</v>
       </c>
       <c r="EB13" t="n">
         <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14">
@@ -6215,25 +6215,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G14" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="H14" t="n">
-        <v>88.38</v>
+        <v>87.67</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -6242,34 +6242,34 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>39.5</v>
+        <v>40.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>12.75</v>
+        <v>12.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.12</v>
+        <v>15.11</v>
       </c>
       <c r="R14" t="n">
-        <v>7.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,25 +6281,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.62</v>
+        <v>46.56</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.25</v>
+        <v>11.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>21</v>
+        <v>20.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -6386,67 +6386,67 @@
         <v>1.57</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.53</v>
+        <v>5.31</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="BR14" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS14" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CB14" t="n">
         <v>3.36</v>
@@ -6467,7 +6467,7 @@
         <v>2.54</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI14" t="n">
         <v>1.74</v>
@@ -6476,37 +6476,37 @@
         <v>2.08</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CT14" t="n">
         <v>2.63</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV14" t="n">
         <v>1.75</v>
@@ -6515,22 +6515,22 @@
         <v>2.17</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB14" t="n">
         <v>1.46</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DD14" t="n">
         <v>3.44</v>
@@ -6539,43 +6539,43 @@
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.34</v>
+        <v>92.63</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.2</v>
+        <v>41.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.07</v>
+        <v>12.87</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.73</v>
+        <v>14.31</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.470000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.26</v>
+        <v>44.81</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.27</v>
+        <v>10.31</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.2</v>
+        <v>20.75</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="15">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
-        <v>87.75</v>
+        <v>85.56</v>
       </c>
       <c r="I16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M16" t="n">
-        <v>38.25</v>
+        <v>39.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="R16" t="n">
-        <v>7.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.88</v>
+        <v>43.67</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.25</v>
+        <v>16.44</v>
       </c>
       <c r="AD16" t="n">
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,49 +7192,49 @@
         <v>2.29</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.93</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY16" t="n">
         <v>3.62</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC16" t="n">
         <v>4.6</v>
@@ -7264,31 +7264,31 @@
         <v>4.87</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF16" t="n">
         <v>3.09</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN16" t="n">
         <v>1.77</v>
@@ -7297,124 +7297,124 @@
         <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CY16" t="n">
         <v>2.06</v>
       </c>
-      <c r="CX16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>2.04</v>
-      </c>
       <c r="CZ16" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB16" t="n">
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>2.13</v>
       </c>
-      <c r="DH16" t="n">
-        <v>83.53</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DK16" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.27</v>
+        <v>37.93</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.94</v>
+        <v>10.87</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.93</v>
+        <v>14</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.130000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.4</v>
+        <v>42.38</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.33</v>
+        <v>11.44</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.27</v>
+        <v>8.44</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.2</v>
+        <v>17.25</v>
       </c>
       <c r="EB16" t="n">
         <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
-        <v>83.88</v>
+        <v>85.78</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>40.75</v>
+        <v>43.44</v>
       </c>
       <c r="N17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P17" t="n">
-        <v>13.12</v>
+        <v>12.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="T17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.75</v>
+        <v>44.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.75</v>
+        <v>19.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7598,67 +7598,67 @@
         <v>2.12</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="BI17" t="n">
         <v>2.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="BR17" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.74</v>
+        <v>4.22</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.52</v>
+        <v>4.87</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="CC17" t="n">
         <v>6.01</v>
@@ -7667,13 +7667,13 @@
         <v>6.8</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7685,10 +7685,10 @@
         <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CM17" t="n">
         <v>2.07</v>
@@ -7700,10 +7700,10 @@
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
@@ -7718,10 +7718,10 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CX17" t="n">
         <v>1.75</v>
@@ -7739,85 +7739,85 @@
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DH17" t="n">
-        <v>80.19</v>
+        <v>81.41</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM17" t="n">
-        <v>34.38</v>
+        <v>36.17</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.12</v>
+        <v>12.94</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.43</v>
+        <v>12.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.75</v>
+        <v>40.76</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.75</v>
+        <v>7.76</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.43</v>
+        <v>16.82</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="18">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="H20" t="n">
-        <v>98.25</v>
+        <v>101.22</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J20" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="K20" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>41.38</v>
+        <v>43.22</v>
       </c>
       <c r="N20" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P20" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="R20" t="n">
-        <v>8.619999999999999</v>
+        <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>44.38</v>
+        <v>45.67</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.75</v>
+        <v>12.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.75</v>
+        <v>19.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8804,67 +8804,67 @@
         <v>2.12</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.380000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.88</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="BR20" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT20" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU20" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV20" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW20" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX20" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.61</v>
+        <v>3.41</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
         <v>3.47</v>
@@ -8879,7 +8879,7 @@
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CG20" t="n">
         <v>2.62</v>
@@ -8897,13 +8897,13 @@
         <v>1.68</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CM20" t="n">
         <v>2.11</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO20" t="n">
         <v>1.37</v>
@@ -8930,16 +8930,16 @@
         <v>1.85</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA20" t="n">
         <v>1.7</v>
@@ -8957,76 +8957,76 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DH20" t="n">
-        <v>88.75</v>
+        <v>90.88</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="DL20" t="n">
         <v>0.12</v>
       </c>
       <c r="DM20" t="n">
-        <v>36.75</v>
+        <v>38</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.68</v>
+        <v>10.82</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.75</v>
+        <v>8.41</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>43.25</v>
+        <v>44</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.62</v>
+        <v>12.06</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.25</v>
+        <v>4.59</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.32</v>
+        <v>17.71</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -9048,46 +9048,46 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H21" t="n">
-        <v>96.12</v>
+        <v>94.33</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M21" t="n">
-        <v>45.12</v>
+        <v>46.33</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="P21" t="n">
-        <v>13.75</v>
+        <v>14.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="R21" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -9102,28 +9102,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48.75</v>
+        <v>48.44</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.88</v>
+        <v>14.89</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.38</v>
+        <v>17.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.25</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.06</v>
+        <v>9.18</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV21" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX21" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY21" t="n">
         <v>3.06</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC21" t="n">
         <v>4.97</v>
@@ -9282,76 +9282,76 @@
         <v>1.45</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI21" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CO21" t="n">
         <v>1.37</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS21" t="n">
         <v>3.12</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY21" t="n">
         <v>2.03</v>
       </c>
-      <c r="CX21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>1.99</v>
-      </c>
       <c r="CZ21" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DD21" t="n">
         <v>3.21</v>
@@ -9360,43 +9360,43 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="DH21" t="n">
-        <v>89.81</v>
+        <v>89.23</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.44</v>
+        <v>40.41</v>
       </c>
       <c r="DN21" t="n">
         <v>0.88</v>
       </c>
       <c r="DO21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.75</v>
+        <v>14.06</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.62</v>
+        <v>11.76</v>
       </c>
       <c r="DR21" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="DS21" t="n">
         <v>0.12</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.62</v>
+        <v>46.59</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.82</v>
+        <v>12.94</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.81</v>
+        <v>8.94</v>
       </c>
       <c r="DZ21" t="n">
         <v>4</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.19</v>
+        <v>17.88</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>103.38</v>
+        <v>102.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K2" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>47.62</v>
+        <v>45.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>11.38</v>
+        <v>10.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.25</v>
+        <v>13.33</v>
       </c>
       <c r="R2" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.75</v>
+        <v>50.89</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,70 +1550,70 @@
         <v>1.29</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.86</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.89</v>
+        <v>3.96</v>
       </c>
       <c r="CC2" t="n">
         <v>2.23</v>
@@ -1634,10 +1634,10 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
         <v>1.58</v>
@@ -1661,28 +1661,28 @@
         <v>3.35</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CX2" t="n">
         <v>1.63</v>
       </c>
       <c r="CY2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.27</v>
@@ -1694,85 +1694,85 @@
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG2" t="n">
         <v>2</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.27</v>
+        <v>96.06</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DK2" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.93</v>
+        <v>44</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.27</v>
+        <v>12.37</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.4</v>
+        <v>51.44</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.54</v>
+        <v>13.38</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.47</v>
+        <v>17.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="H3" t="n">
-        <v>111.62</v>
+        <v>109.11</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>57.62</v>
+        <v>55.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="P3" t="n">
-        <v>10.88</v>
+        <v>10.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="R3" t="n">
-        <v>6.12</v>
+        <v>6.78</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.88</v>
+        <v>56.44</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.62</v>
+        <v>16.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.88</v>
+        <v>11.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.75</v>
+        <v>5.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.88</v>
+        <v>17.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CC3" t="n">
         <v>2.35</v>
@@ -2028,25 +2028,25 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM3" t="n">
         <v>2.16</v>
@@ -2058,10 +2058,10 @@
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,10 +2076,10 @@
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX3" t="n">
         <v>1.68</v>
@@ -2097,10 +2097,10 @@
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2109,40 +2109,40 @@
         <v>1.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="DH3" t="n">
-        <v>104</v>
+        <v>103.12</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.88</v>
+        <v>5.77</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.25</v>
+        <v>51.24</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.94</v>
+        <v>10.77</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.12</v>
+        <v>10.23</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.88</v>
+        <v>57.12</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>14.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.38</v>
+        <v>10.18</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.94</v>
+        <v>17.65</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G4" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H4" t="n">
-        <v>110.57</v>
+        <v>113.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K4" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>49.14</v>
+        <v>48.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="P4" t="n">
-        <v>12.71</v>
+        <v>13.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.57</v>
+        <v>15.12</v>
       </c>
       <c r="R4" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.29</v>
+        <v>56.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.43</v>
+        <v>16.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.86</v>
+        <v>22.25</v>
       </c>
       <c r="AD4" t="n">
         <v>1.72</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB4" t="n">
         <v>3.3</v>
@@ -2428,7 +2428,7 @@
         <v>2.98</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
         <v>3.15</v>
@@ -2437,61 +2437,61 @@
         <v>2.6</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.96</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL4" t="n">
         <v>2.43</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO4" t="n">
         <v>1.38</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CU4" t="n">
         <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA4" t="n">
         <v>1.66</v>
@@ -2500,85 +2500,85 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.06999999999999</v>
+        <v>98.25</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>41</v>
+        <v>41.32</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.6</v>
+        <v>14.82</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.74</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.4</v>
+        <v>5.32</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>56.67</v>
+        <v>56.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.67</v>
+        <v>13.82</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.27</v>
+        <v>9.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.87</v>
+        <v>19.75</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="5">
@@ -3394,91 +3394,91 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
-        <v>81</v>
+        <v>81.88</v>
       </c>
       <c r="I7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>32.71</v>
+        <v>33.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="R7" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.29</v>
+        <v>47.25</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.71</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,70 +3565,70 @@
         <v>2.22</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.81</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BR7" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.97</v>
+        <v>4.18</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.49</v>
+        <v>4.82</v>
       </c>
       <c r="CA7" t="n">
         <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
         <v>6.69</v>
@@ -3643,13 +3643,13 @@
         <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.96</v>
@@ -3658,7 +3658,7 @@
         <v>1.68</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM7" t="n">
         <v>2.12</v>
@@ -3676,22 +3676,22 @@
         <v>3.63</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX7" t="n">
         <v>1.71</v>
@@ -3700,91 +3700,91 @@
         <v>2.15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DE7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="DS7" t="n">
         <v>0.12</v>
       </c>
-      <c r="DF7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>80.38</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="DL7" t="n">
+      <c r="DT7" t="n">
         <v>0.12</v>
       </c>
-      <c r="DM7" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.13</v>
-      </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.06</v>
+        <v>46.12</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.37</v>
+        <v>5.29</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.87</v>
+        <v>19.59</v>
       </c>
       <c r="EB7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
         <v>2.12</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.14</v>
+        <v>79.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>30.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.86</v>
+        <v>13.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.29</v>
+        <v>7.62</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.57</v>
+        <v>41.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.86</v>
+        <v>20.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BQ9" t="n">
         <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY9" t="n">
         <v>3.2</v>
@@ -4431,28 +4431,28 @@
         <v>3.43</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.44</v>
+        <v>4.63</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.65</v>
+        <v>4.89</v>
       </c>
       <c r="CE9" t="n">
         <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI9" t="n">
         <v>1.68</v>
@@ -4464,31 +4464,31 @@
         <v>1.69</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN9" t="n">
         <v>1.68</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CU9" t="n">
         <v>1.33</v>
@@ -4509,13 +4509,13 @@
         <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="DD9" t="n">
         <v>3.47</v>
@@ -4524,43 +4524,43 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.44</v>
+        <v>86.53</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.19</v>
+        <v>34.94</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.12</v>
+        <v>14.06</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.38</v>
+        <v>15.24</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.25</v>
+        <v>7.41</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.75</v>
+        <v>46.3</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.5</v>
+        <v>11.41</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.5</v>
+        <v>20.88</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,127 +4696,127 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>88.5</v>
+        <v>88.56</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.38</v>
       </c>
-      <c r="AN10" t="n">
-        <v>34.75</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="BL10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.12</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>36.88</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BP10" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BR10" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY10" t="n">
         <v>4.13</v>
@@ -4834,25 +4834,25 @@
         <v>4.63</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.39</v>
+        <v>5.86</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CH10" t="n">
         <v>1.33</v>
@@ -4861,142 +4861,142 @@
         <v>1.73</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL10" t="n">
         <v>2.24</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO10" t="n">
         <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV10" t="n">
         <v>1.77</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.67</v>
+        <v>91.5</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM10" t="n">
-        <v>36</v>
+        <v>36.12</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.73</v>
+        <v>17.56</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.66</v>
+        <v>8.44</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.07</v>
+        <v>39.62</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.94</v>
+        <v>19.88</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>109.57</v>
+        <v>109</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.43</v>
+        <v>54</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.57</v>
+        <v>14.25</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59.14</v>
+        <v>58.62</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.86</v>
+        <v>16.62</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.29</v>
+        <v>12.12</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.57</v>
+        <v>19.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.2</v>
+        <v>10.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY11" t="n">
         <v>1.39</v>
@@ -5237,34 +5237,34 @@
         <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.84</v>
+        <v>4.76</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CK11" t="n">
         <v>1.62</v>
@@ -5282,7 +5282,7 @@
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.9</v>
@@ -5300,10 +5300,10 @@
         <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX11" t="n">
         <v>1.61</v>
@@ -5312,13 +5312,13 @@
         <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
         <v>1.83</v>
@@ -5327,79 +5327,79 @@
         <v>2.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.67</v>
+        <v>103.75</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.8</v>
+        <v>56.44</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.47</v>
+        <v>14.32</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.47</v>
+        <v>11.25</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.53</v>
+        <v>59.25</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.47</v>
+        <v>17.31</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.87</v>
+        <v>11.81</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.53</v>
+        <v>18.44</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -5562,19 +5562,19 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
         <v>19.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF12" t="n">
         <v>1.78</v>
@@ -5787,13 +5787,13 @@
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.47</v>
+        <v>15.53</v>
       </c>
       <c r="DY12" t="n">
         <v>10.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
       <c r="EA12" t="n">
         <v>18.82</v>
@@ -5968,16 +5968,16 @@
         <v>9.779999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.11</v>
+        <v>6.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="BD13" t="n">
         <v>15.11</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
         <v>2</v>
@@ -6193,16 +6193,16 @@
         <v>11.35</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="EA13" t="n">
         <v>16.35</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
         <v>1.88</v>
@@ -6260,7 +6260,7 @@
         <v>12.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.11</v>
+        <v>15.22</v>
       </c>
       <c r="R14" t="n">
         <v>8.109999999999999</v>
@@ -6572,7 +6572,7 @@
         <v>12.87</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.31</v>
+        <v>14.38</v>
       </c>
       <c r="DR14" t="n">
         <v>8.630000000000001</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,139 +6708,139 @@
         <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO15" t="n">
         <v>1</v>
       </c>
-      <c r="AH15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>99.12</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>58.12</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BP15" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY15" t="n">
         <v>2.01</v>
@@ -6849,25 +6849,25 @@
         <v>2.13</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
@@ -6888,46 +6888,46 @@
         <v>2.19</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO15" t="n">
         <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT15" t="n">
         <v>2.75</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW15" t="n">
         <v>2.17</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY15" t="n">
         <v>2.16</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB15" t="n">
         <v>1.42</v>
@@ -6936,82 +6936,82 @@
         <v>2.34</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="DH15" t="n">
-        <v>103</v>
+        <v>102.44</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.54</v>
+        <v>5.81</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.4</v>
+        <v>48.75</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.46</v>
+        <v>12.19</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.07</v>
+        <v>13.06</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>56.53</v>
+        <v>56.31</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.67</v>
+        <v>13.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.87</v>
+        <v>8.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.4</v>
+        <v>18.56</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="H18" t="n">
-        <v>116.12</v>
+        <v>114</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K18" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M18" t="n">
-        <v>53.75</v>
+        <v>53.89</v>
       </c>
       <c r="N18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P18" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.12</v>
+        <v>14.89</v>
       </c>
       <c r="R18" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="U18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>58.12</v>
+        <v>58.44</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.25</v>
+        <v>14.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.38</v>
+        <v>4.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.38</v>
+        <v>21.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,49 +7998,49 @@
         <v>2.25</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.619999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BN18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,19 +8049,19 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="CA18" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CB18" t="n">
         <v>3.5</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>3.48</v>
       </c>
       <c r="CC18" t="n">
         <v>2.41</v>
@@ -8073,7 +8073,7 @@
         <v>1.44</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG18" t="n">
         <v>2.68</v>
@@ -8082,31 +8082,31 @@
         <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK18" t="n">
         <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8118,25 +8118,25 @@
         <v>2.76</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX18" t="n">
         <v>1.75</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.12</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
@@ -8151,43 +8151,43 @@
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="DH18" t="n">
-        <v>112.56</v>
+        <v>111.65</v>
       </c>
       <c r="DI18" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.75</v>
+        <v>51.94</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO18" t="n">
         <v>1.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.57</v>
+        <v>14.47</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.06</v>
+        <v>14.94</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.62</v>
+        <v>6.47</v>
       </c>
       <c r="DS18" t="n">
         <v>0.06</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.75</v>
+        <v>57.94</v>
       </c>
       <c r="DW18" t="n">
         <v>0.06</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.25</v>
+        <v>13.41</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.75</v>
+        <v>4.94</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.75</v>
+        <v>20.7</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>81.88</v>
+        <v>79.44</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN19" t="n">
-        <v>32.62</v>
+        <v>31.56</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.38</v>
+        <v>13.11</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.25</v>
+        <v>13.78</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.619999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.88</v>
+        <v>43.67</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BD19" t="n">
-        <v>15</v>
+        <v>15.44</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.06</v>
+        <v>7.88</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
         <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS19" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT19" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY19" t="n">
         <v>3.1</v>
@@ -8461,16 +8461,16 @@
         <v>3.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.93</v>
+        <v>4.81</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
@@ -8485,7 +8485,7 @@
         <v>1.39</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.86</v>
@@ -8494,7 +8494,7 @@
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CM19" t="n">
         <v>2.21</v>
@@ -8509,7 +8509,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
@@ -8527,7 +8527,7 @@
         <v>1.95</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX19" t="n">
         <v>1.72</v>
@@ -8536,7 +8536,7 @@
         <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA19" t="n">
         <v>1.7</v>
@@ -8548,49 +8548,49 @@
         <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="DE19" t="n">
         <v>0.12</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.19</v>
+        <v>85.59</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DL19" t="n">
         <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.12</v>
+        <v>35.35</v>
       </c>
       <c r="DN19" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.94</v>
+        <v>13.29</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.18</v>
+        <v>14.41</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.94</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.12</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.75</v>
+        <v>45.53</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.75</v>
+        <v>10.59</v>
       </c>
       <c r="DY19" t="n">
-        <v>7</v>
+        <v>6.76</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.5</v>
+        <v>16.64</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.22</v>
@@ -1469,139 +1469,139 @@
         <v>1.56</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>88.14</v>
+        <v>92.38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>41.86</v>
+        <v>43.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52.14</v>
+        <v>52.38</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.29</v>
+        <v>11.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BD2" t="n">
-        <v>16</v>
+        <v>16.88</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY2" t="n">
         <v>1.69</v>
@@ -1616,10 +1616,10 @@
         <v>3.96</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="CE2" t="n">
         <v>1.38</v>
@@ -1628,7 +1628,7 @@
         <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
@@ -1637,28 +1637,28 @@
         <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO2" t="n">
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
@@ -1673,106 +1673,106 @@
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB2" t="n">
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DG2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.06</v>
+        <v>97.59</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM2" t="n">
-        <v>44</v>
+        <v>44.77</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.37</v>
+        <v>12.23</v>
       </c>
       <c r="DR2" t="n">
         <v>6</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.44</v>
+        <v>51.59</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.38</v>
+        <v>13.24</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.630000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.69</v>
+        <v>18</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>109.11</v>
+        <v>109.4</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>55.11</v>
+        <v>54.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>10.56</v>
+        <v>11.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.44</v>
+        <v>10.9</v>
       </c>
       <c r="R3" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.44</v>
+        <v>55.3</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.44</v>
+        <v>16.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.33</v>
+        <v>17.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.12</v>
+        <v>5.28</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC3" t="n">
         <v>2.35</v>
@@ -2028,10 +2028,10 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
@@ -2040,55 +2040,55 @@
         <v>1.94</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL3" t="n">
         <v>2.21</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW3" t="n">
         <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
         <v>1.74</v>
@@ -2097,85 +2097,85 @@
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.12</v>
+        <v>103.61</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.24</v>
+        <v>51.11</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DO3" t="n">
         <v>2.89</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.77</v>
+        <v>11.06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.23</v>
+        <v>10.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.53</v>
+        <v>6.33</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.12</v>
+        <v>56.45</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.53</v>
+        <v>14.45</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.18</v>
+        <v>10.22</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.65</v>
+        <v>17.89</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="4">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2603,46 +2603,46 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="H5" t="n">
-        <v>73.25</v>
+        <v>73.56</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>33.25</v>
+        <v>33.11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>16.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.62</v>
+        <v>16.56</v>
       </c>
       <c r="R5" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>47.75</v>
+        <v>47.56</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.12</v>
+        <v>19.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.59</v>
+        <v>8.83</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.87</v>
+        <v>4.19</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>6.28</v>
@@ -2834,10 +2834,10 @@
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2846,19 +2846,19 @@
         <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO5" t="n">
         <v>1.36</v>
@@ -2867,7 +2867,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
@@ -2885,70 +2885,70 @@
         <v>1.78</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA5" t="n">
         <v>1.76</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC5" t="n">
         <v>2.27</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.12</v>
+        <v>73.28</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.59</v>
+        <v>28.78</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>16</v>
+        <v>15.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.76</v>
+        <v>15.34</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.470000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.18</v>
+        <v>45.22</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.82</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.3</v>
+        <v>6.22</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>17.78</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>112.14</v>
+        <v>109.38</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>41.57</v>
+        <v>43.62</v>
       </c>
       <c r="N6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P6" t="n">
-        <v>14.86</v>
+        <v>14.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="R6" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61.14</v>
+        <v>61.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.86</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.86</v>
+        <v>22.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,64 +3162,64 @@
         <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.94</v>
+        <v>7.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CA6" t="n">
         <v>3.5</v>
@@ -3237,7 +3237,7 @@
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG6" t="n">
         <v>2.76</v>
@@ -3246,16 +3246,16 @@
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CM6" t="n">
         <v>2.02</v>
@@ -3270,13 +3270,13 @@
         <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT6" t="n">
         <v>2.88</v>
@@ -3285,7 +3285,7 @@
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW6" t="n">
         <v>1.94</v>
@@ -3309,82 +3309,82 @@
         <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DG6" t="n">
         <v>2.06</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.31</v>
+        <v>100.65</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.62</v>
+        <v>43.52</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.32</v>
+        <v>15.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.25</v>
+        <v>13.29</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.31</v>
+        <v>6.18</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60</v>
+        <v>60.12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.69</v>
+        <v>13.76</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.69</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.13</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
         <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="7">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>92.67</v>
+        <v>93.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>39.22</v>
+        <v>40.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>14.33</v>
+        <v>13.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.67</v>
+        <v>15.8</v>
       </c>
       <c r="R9" t="n">
-        <v>7.22</v>
+        <v>7.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.78</v>
+        <v>51.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC9" t="n">
         <v>4.63</v>
@@ -4455,10 +4455,10 @@
         <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK9" t="n">
         <v>1.69</v>
@@ -4467,7 +4467,7 @@
         <v>2.26</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
         <v>1.68</v>
@@ -4476,10 +4476,10 @@
         <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4521,79 +4521,79 @@
         <v>3.47</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.53</v>
+        <v>87.22</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.94</v>
+        <v>35.72</v>
       </c>
       <c r="DN9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.06</v>
+        <v>13.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.24</v>
+        <v>15.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.3</v>
+        <v>47.17</v>
       </c>
       <c r="DW9" t="n">
         <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.41</v>
+        <v>11.45</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.95</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.88</v>
+        <v>21.06</v>
       </c>
       <c r="EB9" t="n">
         <v>1.26</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="10">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>109.5</v>
+        <v>114.56</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="L12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="M12" t="n">
-        <v>61.12</v>
+        <v>67.56</v>
       </c>
       <c r="N12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>11.88</v>
+        <v>11.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>56.25</v>
+        <v>58</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>18.38</v>
+        <v>19.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.25</v>
+        <v>12.22</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.12</v>
+        <v>19.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5580,70 +5580,70 @@
         <v>1.78</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
         <v>2.02</v>
@@ -5652,157 +5652,157 @@
         <v>2.08</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL12" t="n">
         <v>2.1</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="DE12" t="n">
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DH12" t="n">
-        <v>103.35</v>
+        <v>106.22</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.64</v>
+        <v>4.94</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.88</v>
+        <v>58.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.12</v>
+        <v>10.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.3</v>
+        <v>6.17</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.41</v>
+        <v>57.28</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.53</v>
+        <v>16.06</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.06</v>
+        <v>10.61</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.82</v>
+        <v>19.56</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>99</v>
+        <v>94.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AN14" t="n">
-        <v>43.14</v>
+        <v>39.88</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.43</v>
+        <v>12.62</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.29</v>
+        <v>12.38</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.289999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>42.57</v>
+        <v>40.75</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.43</v>
+        <v>20.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BG14" t="n">
         <v>2.06</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="BI14" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BR14" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY14" t="n">
         <v>3.87</v>
@@ -6446,136 +6446,136 @@
         <v>4.3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.11</v>
+        <v>6.22</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.54</v>
+        <v>6.39</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL14" t="n">
         <v>2.08</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.63</v>
+        <v>91</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.44</v>
+        <v>5.18</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.69</v>
+        <v>40.24</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.87</v>
+        <v>12.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.38</v>
+        <v>13.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.630000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.81</v>
+        <v>43.83</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.31</v>
+        <v>10.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.75</v>
+        <v>20.35</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="15">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7114,127 +7114,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.70999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>36.14</v>
+        <v>37</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.43</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.43</v>
+        <v>14.12</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40.71</v>
+        <v>41.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.43</v>
+        <v>11.12</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.29</v>
+        <v>18.12</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.119999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY16" t="n">
         <v>3.62</v>
@@ -7255,13 +7255,13 @@
         <v>3.3</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.87</v>
+        <v>4.81</v>
       </c>
       <c r="CE16" t="n">
         <v>1.44</v>
@@ -7270,37 +7270,37 @@
         <v>3.09</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO16" t="n">
         <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7309,19 +7309,19 @@
         <v>3.21</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW16" t="n">
         <v>2.04</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY16" t="n">
         <v>2.06</v>
@@ -7330,7 +7330,7 @@
         <v>2.28</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB16" t="n">
         <v>1.4</v>
@@ -7339,82 +7339,82 @@
         <v>2.28</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>2.06</v>
       </c>
-      <c r="DH16" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.13</v>
-      </c>
       <c r="DK16" t="n">
-        <v>3.19</v>
+        <v>3.41</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.93</v>
+        <v>38.23</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.87</v>
+        <v>10.65</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.44</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.38</v>
+        <v>42.65</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.44</v>
+        <v>8.59</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.25</v>
+        <v>17.23</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>76.5</v>
+        <v>78.11</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>30.78</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.12</v>
+        <v>13.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.75</v>
+        <v>11.44</v>
       </c>
       <c r="AS17" t="n">
         <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>36.75</v>
+        <v>36.89</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.12</v>
+        <v>14.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="BR17" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT17" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY17" t="n">
         <v>4.22</v>
@@ -7655,34 +7655,34 @@
         <v>4.87</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.01</v>
+        <v>5.87</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.8</v>
+        <v>6.59</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
         <v>1.71</v>
@@ -7691,7 +7691,7 @@
         <v>2.26</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN17" t="n">
         <v>1.66</v>
@@ -7700,10 +7700,10 @@
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
@@ -7718,10 +7718,10 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX17" t="n">
         <v>1.75</v>
@@ -7736,10 +7736,10 @@
         <v>1.67</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD17" t="n">
         <v>3.28</v>
@@ -7748,55 +7748,55 @@
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="DH17" t="n">
-        <v>81.41</v>
+        <v>81.94</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="DL17" t="n">
         <v>0.11</v>
       </c>
       <c r="DM17" t="n">
-        <v>36.17</v>
+        <v>37.11</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.94</v>
+        <v>13.17</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.41</v>
+        <v>12.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.76</v>
+        <v>40.61</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
@@ -7805,19 +7805,19 @@
         <v>9.94</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.76</v>
+        <v>7.78</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.82</v>
+        <v>16.77</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>109</v>
+        <v>107.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>49.75</v>
+        <v>48.89</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.62</v>
+        <v>7.78</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>57.38</v>
+        <v>57.11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.12</v>
+        <v>19.44</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.529999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.29</v>
+        <v>5.44</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY18" t="n">
         <v>1.89</v>
@@ -8058,22 +8058,22 @@
         <v>2.08</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="CE18" t="n">
         <v>1.44</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG18" t="n">
         <v>2.68</v>
@@ -8088,55 +8088,55 @@
         <v>2.03</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL18" t="n">
         <v>2.22</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU18" t="n">
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX18" t="n">
         <v>1.75</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.12</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
@@ -8145,49 +8145,49 @@
         <v>2.31</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="DH18" t="n">
-        <v>111.65</v>
+        <v>110.84</v>
       </c>
       <c r="DI18" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.94</v>
+        <v>51.39</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.47</v>
+        <v>14.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.94</v>
+        <v>15</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.47</v>
+        <v>6.61</v>
       </c>
       <c r="DS18" t="n">
         <v>0.06</v>
@@ -8199,25 +8199,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.94</v>
+        <v>57.78</v>
       </c>
       <c r="DW18" t="n">
         <v>0.06</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.41</v>
+        <v>13.22</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.470000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.7</v>
+        <v>20.33</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC18" t="n">
         <v>2</v>
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>92.5</v>
+        <v>95.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M19" t="n">
-        <v>39.62</v>
+        <v>42.67</v>
       </c>
       <c r="N19" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.12</v>
+        <v>14.22</v>
       </c>
       <c r="R19" t="n">
-        <v>7.25</v>
+        <v>6.89</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.62</v>
+        <v>48.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.75</v>
+        <v>11.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.88</v>
+        <v>8.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS19" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC19" t="n">
         <v>4.81</v>
@@ -8476,16 +8476,16 @@
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.86</v>
@@ -8494,10 +8494,10 @@
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CM19" t="n">
         <v>2.2</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>2.21</v>
       </c>
       <c r="CN19" t="n">
         <v>1.75</v>
@@ -8521,7 +8521,7 @@
         <v>2.82</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
         <v>1.95</v>
@@ -8530,7 +8530,7 @@
         <v>1.92</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY19" t="n">
         <v>2.17</v>
@@ -8548,82 +8548,82 @@
         <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.59</v>
+        <v>87.33</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM19" t="n">
-        <v>35.35</v>
+        <v>37.11</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.29</v>
+        <v>13.22</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.41</v>
+        <v>14</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.53</v>
+        <v>45.94</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.59</v>
+        <v>10.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.76</v>
+        <v>6.83</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.64</v>
+        <v>16.88</v>
       </c>
       <c r="EB19" t="n">
         <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="20">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>83.5</v>
+        <v>82.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN21" t="n">
-        <v>33.75</v>
+        <v>32.33</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.5</v>
+        <v>43.78</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="BD21" t="n">
-        <v>18</v>
+        <v>18.11</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.18</v>
+        <v>8.94</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX21" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY21" t="n">
         <v>3.06</v>
@@ -9267,13 +9267,13 @@
         <v>3.41</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC21" t="n">
-        <v>4.97</v>
+        <v>4.95</v>
       </c>
       <c r="CD21" t="n">
         <v>5.19</v>
@@ -9285,10 +9285,10 @@
         <v>3.12</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI21" t="n">
         <v>1.8</v>
@@ -9300,22 +9300,22 @@
         <v>1.56</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO21" t="n">
         <v>1.37</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
@@ -9324,13 +9324,13 @@
         <v>3.12</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU21" t="n">
         <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW21" t="n">
         <v>2.04</v>
@@ -9351,85 +9351,85 @@
         <v>1.42</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DH21" t="n">
-        <v>89.23</v>
+        <v>88.5</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DO21" t="n">
         <v>2</v>
       </c>
-      <c r="DK21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="DL21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DM21" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="DN21" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DO21" t="n">
-        <v>2.06</v>
-      </c>
       <c r="DP21" t="n">
-        <v>14.06</v>
+        <v>14.11</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.76</v>
+        <v>11.77</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.59</v>
+        <v>46.11</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.94</v>
+        <v>12.39</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.94</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.88</v>
+        <v>17.94</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2076,28 +2076,28 @@
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW3" t="n">
         <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY3" t="n">
         <v>2.13</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
         <v>3.2</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>83.38</v>
+        <v>82.89</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>33.88</v>
+        <v>32.33</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16.25</v>
+        <v>16.78</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.88</v>
+        <v>15.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>57</v>
+        <v>55.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.25</v>
+        <v>10.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.25</v>
+        <v>17.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.19</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BO4" t="n">
         <v>0.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.94</v>
+        <v>4.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY4" t="n">
         <v>2.19</v>
@@ -2416,34 +2416,34 @@
         <v>2.32</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.8</v>
+        <v>3.37</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.98</v>
+        <v>3.51</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI4" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK4" t="n">
         <v>1.72</v>
@@ -2458,25 +2458,25 @@
         <v>1.64</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV4" t="n">
         <v>1.86</v>
@@ -2485,67 +2485,67 @@
         <v>2.04</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>98.25</v>
+        <v>97.12</v>
       </c>
       <c r="DI4" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.19</v>
+        <v>4.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.32</v>
+        <v>40.06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.82</v>
+        <v>15.18</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.32</v>
+        <v>5.41</v>
       </c>
       <c r="DS4" t="n">
         <v>0.18</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>56.75</v>
+        <v>55.88</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.82</v>
+        <v>13.36</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.31</v>
+        <v>9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.75</v>
+        <v>19.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3096,7 +3096,7 @@
         <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL6" t="n">
         <v>3.89</v>
@@ -3108,7 +3108,7 @@
         <v>43.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP6" t="n">
         <v>1.67</v>
@@ -3159,7 +3159,7 @@
         <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="BG6" t="n">
         <v>2.06</v>
@@ -3219,7 +3219,7 @@
         <v>1.88</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CA6" t="n">
         <v>3.5</v>
@@ -3276,10 +3276,10 @@
         <v>1.44</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
@@ -3306,10 +3306,10 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
@@ -3327,7 +3327,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="DK6" t="n">
         <v>3.94</v>
@@ -3339,7 +3339,7 @@
         <v>43.52</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
         <v>1.88</v>
@@ -3384,7 +3384,7 @@
         <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3484,52 +3484,52 @@
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.89</v>
+        <v>78.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>29.78</v>
+        <v>28.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.11</v>
+        <v>13.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.33</v>
+        <v>10.3</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>45.11</v>
+        <v>44.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.22</v>
+        <v>18.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BR7" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>4.18</v>
@@ -3625,25 +3625,25 @@
         <v>4.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.69</v>
+        <v>6.5</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.47</v>
+        <v>7.24</v>
       </c>
       <c r="CE7" t="n">
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
@@ -3664,7 +3664,7 @@
         <v>2.12</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
@@ -3673,7 +3673,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CR7" t="n">
         <v>1.46</v>
@@ -3691,7 +3691,7 @@
         <v>1.86</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
         <v>1.71</v>
@@ -3706,88 +3706,88 @@
         <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.83</v>
+        <v>79.89</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DL7" t="n">
         <v>0.11</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.41</v>
+        <v>30.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.77</v>
+        <v>13.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13</v>
+        <v>12.84</v>
       </c>
       <c r="DR7" t="n">
         <v>9.94</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.12</v>
+        <v>45.5</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.59</v>
+        <v>19.33</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="H8" t="n">
-        <v>89.62</v>
+        <v>92.56</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K8" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>41.38</v>
+        <v>45.22</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P8" t="n">
-        <v>13.38</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.62</v>
+        <v>17.78</v>
       </c>
       <c r="R8" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.38</v>
+        <v>53.78</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.38</v>
+        <v>16.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.5</v>
+        <v>11.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.25</v>
+        <v>16.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP8" t="n">
         <v>3.94</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT8" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CC8" t="n">
         <v>3.53</v>
@@ -4040,13 +4040,13 @@
         <v>3.89</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH8" t="n">
         <v>1.35</v>
@@ -4058,7 +4058,7 @@
         <v>1.9</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL8" t="n">
         <v>2.28</v>
@@ -4076,7 +4076,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CR8" t="n">
         <v>1.46</v>
@@ -4097,100 +4097,100 @@
         <v>1.95</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB8" t="n">
         <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DE8" t="n">
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.18000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.53</v>
+        <v>4.66</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.53</v>
+        <v>41.56</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.53</v>
+        <v>13.34</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.88</v>
+        <v>53.56</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.29</v>
+        <v>13.77</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.23</v>
+        <v>10.44</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.06</v>
+        <v>3.33</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.18</v>
+        <v>16.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4293,7 +4293,7 @@
         <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
         <v>2.25</v>
@@ -4302,7 +4302,7 @@
         <v>79.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
         <v>2.38</v>
@@ -4317,7 +4317,7 @@
         <v>30.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AP9" t="n">
         <v>1.25</v>
@@ -4515,7 +4515,7 @@
         <v>1.52</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="DD9" t="n">
         <v>3.47</v>
@@ -4524,7 +4524,7 @@
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DG9" t="n">
         <v>2.22</v>
@@ -4533,7 +4533,7 @@
         <v>87.22</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="DJ9" t="n">
         <v>2.28</v>
@@ -4548,7 +4548,7 @@
         <v>35.72</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
         <v>1.33</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -4615,88 +4615,88 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
-        <v>95.29000000000001</v>
+        <v>99</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="L10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>37.43</v>
+        <v>38.88</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P10" t="n">
-        <v>17.14</v>
+        <v>16.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.57</v>
+        <v>42.38</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>12.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.43</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.29</v>
+        <v>18.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
         <v>1.56</v>
@@ -4720,7 +4720,7 @@
         <v>35.11</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AP10" t="n">
         <v>1.33</v>
@@ -4774,49 +4774,49 @@
         <v>2.78</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO10" t="n">
         <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR10" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.13</v>
+        <v>3.96</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CC10" t="n">
         <v>5.4</v>
@@ -4846,43 +4846,43 @@
         <v>5.86</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CH10" t="n">
         <v>1.33</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.07</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL10" t="n">
         <v>2.24</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.11</v>
+        <v>4.17</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
@@ -4891,7 +4891,7 @@
         <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4909,16 +4909,16 @@
         <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA10" t="n">
         <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DD10" t="n">
         <v>3.4</v>
@@ -4927,43 +4927,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>91.5</v>
+        <v>93.47</v>
       </c>
       <c r="DI10" t="n">
         <v>-0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.12</v>
+        <v>36.88</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.56</v>
+        <v>17.29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.44</v>
+        <v>8.35</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.62</v>
+        <v>40.12</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.88</v>
+        <v>19.94</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G11" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="H11" t="n">
-        <v>98.5</v>
+        <v>98.11</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="K11" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="M11" t="n">
-        <v>58.88</v>
+        <v>58.44</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>14.38</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.25</v>
+        <v>10.56</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>59.88</v>
+        <v>59.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>18.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.5</v>
+        <v>11.22</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.62</v>
+        <v>17.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
         <v>0.38</v>
@@ -5177,58 +5177,58 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.25</v>
+        <v>10.12</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.44</v>
+        <v>4.24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.81</v>
+        <v>5.88</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY11" t="n">
         <v>1.39</v>
@@ -5237,10 +5237,10 @@
         <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="CC11" t="n">
         <v>1.95</v>
@@ -5252,10 +5252,10 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
@@ -5270,22 +5270,22 @@
         <v>1.62</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN11" t="n">
         <v>1.77</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
         <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
@@ -5294,7 +5294,7 @@
         <v>2.74</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU11" t="n">
         <v>1.48</v>
@@ -5306,7 +5306,7 @@
         <v>2.02</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
         <v>2.02</v>
@@ -5327,79 +5327,79 @@
         <v>2.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF11" t="n">
         <v>1.06</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.75</v>
+        <v>103.23</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.44</v>
+        <v>56.35</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.32</v>
+        <v>14.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.25</v>
+        <v>11.83</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.25</v>
+        <v>59.18</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.31</v>
+        <v>17.41</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.81</v>
+        <v>11.64</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.44</v>
+        <v>18.47</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
@@ -5643,7 +5643,7 @@
         <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
         <v>2.02</v>
@@ -5691,22 +5691,22 @@
         <v>3.62</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX12" t="n">
         <v>1.67</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="G13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="H13" t="n">
-        <v>95.62</v>
+        <v>91.11</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="K13" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>40</v>
+        <v>37.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0.11</v>
@@ -5983,70 +5983,70 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="BR13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT13" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC13" t="n">
         <v>3.65</v>
@@ -6055,43 +6055,43 @@
         <v>3.94</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CO13" t="n">
         <v>1.36</v>
       </c>
-      <c r="CI13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP13" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
@@ -6106,73 +6106,73 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.64</v>
+        <v>87.72</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.06</v>
+        <v>36.16</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.12</v>
+        <v>11.06</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.24</v>
+        <v>17</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.88</v>
+        <v>8.06</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.24</v>
+        <v>50.34</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.35</v>
+        <v>11</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.24</v>
+        <v>7.11</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.35</v>
+        <v>15.94</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6449,13 +6449,13 @@
         <v>3.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>6.22</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.39</v>
+        <v>6.66</v>
       </c>
       <c r="CE14" t="n">
         <v>1.5</v>
@@ -6497,22 +6497,22 @@
         <v>4.3</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV14" t="n">
         <v>1.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CX14" t="n">
         <v>1.61</v>
@@ -6521,10 +6521,10 @@
         <v>2.01</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
         <v>1.44</v>
@@ -6533,7 +6533,7 @@
         <v>2.42</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
@@ -6618,19 +6618,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
         <v>3.57</v>
@@ -6654,7 +6654,7 @@
         <v>47.86</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O15" t="n">
         <v>2.71</v>
@@ -6708,139 +6708,139 @@
         <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>98.56</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>49.44</v>
+        <v>50.3</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.11</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>57.56</v>
+        <v>58.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.890000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.11</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
         <v>1.54</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.56</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY15" t="n">
         <v>2.01</v>
@@ -6849,55 +6849,55 @@
         <v>2.13</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CD15" t="n">
         <v>2.33</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.07</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6921,19 +6921,19 @@
         <v>1.72</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DD15" t="n">
         <v>3.62</v>
@@ -6942,43 +6942,43 @@
         <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.44</v>
+        <v>101.94</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.81</v>
+        <v>5.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.75</v>
+        <v>49.3</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.19</v>
+        <v>12.23</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.06</v>
+        <v>12.88</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.94</v>
+        <v>7.59</v>
       </c>
       <c r="DS15" t="n">
         <v>0.18</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>56.31</v>
+        <v>56.82</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.25</v>
+        <v>13.3</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.25</v>
+        <v>8.41</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.56</v>
+        <v>18.47</v>
       </c>
       <c r="EB15" t="n">
         <v>1.54</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7045,7 @@
         <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="K16" t="n">
         <v>3.44</v>
@@ -7057,7 +7057,7 @@
         <v>39.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -7108,7 +7108,7 @@
         <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>4.52</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="CE16" t="n">
         <v>1.44</v>
@@ -7318,7 +7318,7 @@
         <v>1.87</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX16" t="n">
         <v>1.65</v>
@@ -7357,7 +7357,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
         <v>3.41</v>
@@ -7369,7 +7369,7 @@
         <v>38.23</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
         <v>1.35</v>
@@ -7414,7 +7414,7 @@
         <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -7658,13 +7658,13 @@
         <v>3.64</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CC17" t="n">
         <v>5.87</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.59</v>
+        <v>6.61</v>
       </c>
       <c r="CE17" t="n">
         <v>1.47</v>
@@ -7712,16 +7712,16 @@
         <v>3.14</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU17" t="n">
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX17" t="n">
         <v>1.75</v>
@@ -7739,7 +7739,7 @@
         <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD17" t="n">
         <v>3.28</v>
@@ -7839,7 +7839,7 @@
         <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
         <v>3.11</v>
@@ -7851,7 +7851,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="K18" t="n">
         <v>5.44</v>
@@ -7914,7 +7914,7 @@
         <v>1.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -8127,13 +8127,13 @@
         <v>2.09</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA18" t="n">
         <v>1.68</v>
@@ -8142,7 +8142,7 @@
         <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD18" t="n">
         <v>3.6</v>
@@ -8151,7 +8151,7 @@
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG18" t="n">
         <v>3.39</v>
@@ -8163,7 +8163,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="DK18" t="n">
         <v>5.28</v>
@@ -8220,7 +8220,7 @@
         <v>1.56</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="19">
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
         <v>1.56</v>
@@ -8347,7 +8347,7 @@
         <v>31.56</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
         <v>1.89</v>
@@ -8458,7 +8458,7 @@
         <v>2.99</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CA19" t="n">
         <v>3.48</v>
@@ -8521,7 +8521,7 @@
         <v>2.82</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV19" t="n">
         <v>1.95</v>
@@ -8530,7 +8530,7 @@
         <v>1.92</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY19" t="n">
         <v>2.17</v>
@@ -8554,7 +8554,7 @@
         <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DG19" t="n">
         <v>1.78</v>
@@ -8578,7 +8578,7 @@
         <v>37.11</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
         <v>1.72</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0.11</v>
@@ -8723,139 +8723,139 @@
         <v>1.44</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.25</v>
+        <v>83.56</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>32.12</v>
+        <v>31.44</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>14.11</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>42.12</v>
+        <v>43.22</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>12.56</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="BD20" t="n">
-        <v>15.88</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.35</v>
+        <v>8.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="BR20" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS20" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT20" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU20" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV20" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW20" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX20" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY20" t="n">
         <v>3.23</v>
@@ -8864,55 +8864,55 @@
         <v>3.41</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.84</v>
+        <v>4.61</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.34</v>
+        <v>5.09</v>
       </c>
       <c r="CE20" t="n">
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL20" t="n">
         <v>2.23</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN20" t="n">
         <v>1.68</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
@@ -8921,13 +8921,13 @@
         <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW20" t="n">
         <v>2.04</v>
@@ -8945,88 +8945,88 @@
         <v>1.7</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DD20" t="n">
         <v>3.42</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="DH20" t="n">
-        <v>90.88</v>
+        <v>92.39</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>38</v>
+        <v>37.33</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.41</v>
+        <v>14</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.82</v>
+        <v>10.94</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.41</v>
+        <v>8.34</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44</v>
+        <v>44.44</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.06</v>
+        <v>12.56</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.47</v>
+        <v>7.94</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.71</v>
+        <v>17.66</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="21">
@@ -9270,7 +9270,7 @@
         <v>3.45</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC21" t="n">
         <v>4.95</v>
@@ -9321,7 +9321,7 @@
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT21" t="n">
         <v>2.72</v>
@@ -9330,7 +9330,7 @@
         <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW21" t="n">
         <v>2.04</v>
@@ -9354,7 +9354,7 @@
         <v>2.28</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -1875,103 +1875,103 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.38</v>
+        <v>97.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.88</v>
+        <v>46.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.88</v>
+        <v>56.67</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>18.78</v>
       </c>
       <c r="BE3" t="n">
         <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
         <v>1.11</v>
@@ -1980,31 +1980,31 @@
         <v>1.11</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY3" t="n">
         <v>1.95</v>
@@ -2013,40 +2013,40 @@
         <v>2.01</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CD3" t="n">
         <v>2.35</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>2.33</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK3" t="n">
         <v>1.66</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM3" t="n">
         <v>2.15</v>
@@ -2058,10 +2058,10 @@
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2079,7 +2079,7 @@
         <v>2.03</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX3" t="n">
         <v>1.7</v>
@@ -2100,49 +2100,49 @@
         <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.61</v>
+        <v>103.79</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.11</v>
+        <v>-0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="DK3" t="n">
         <v>5.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.11</v>
+        <v>50.74</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.06</v>
+        <v>11.26</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.5</v>
+        <v>10.79</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.45</v>
+        <v>55.95</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.45</v>
+        <v>14.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.22</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.89</v>
+        <v>18.26</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="n">
-        <v>113.12</v>
+        <v>111</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="K4" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>48.75</v>
+        <v>49.11</v>
       </c>
       <c r="N4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>13.38</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="R4" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.5</v>
+        <v>56.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.38</v>
+        <v>15.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.25</v>
+        <v>21.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,49 +2356,49 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CA4" t="n">
         <v>3.32</v>
@@ -2431,7 +2431,7 @@
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CG4" t="n">
         <v>2.65</v>
@@ -2440,49 +2440,49 @@
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK4" t="n">
         <v>1.72</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CU4" t="n">
         <v>1.37</v>
       </c>
-      <c r="CP4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="CV4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
         <v>1.75</v>
@@ -2497,88 +2497,88 @@
         <v>1.67</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="DH4" t="n">
-        <v>97.12</v>
+        <v>96.94</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.06</v>
+        <v>40.72</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.18</v>
+        <v>15.23</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.29</v>
+        <v>15.28</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.88</v>
+        <v>55.72</v>
       </c>
       <c r="DW4" t="n">
         <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.36</v>
+        <v>13.22</v>
       </c>
       <c r="DY4" t="n">
         <v>9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.65</v>
+        <v>19.56</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>92.89</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.44</v>
+        <v>45.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.67</v>
+        <v>15.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>59.11</v>
+        <v>60.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.11</v>
+        <v>13.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.76</v>
+        <v>7.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="BQ6" t="n">
         <v>4</v>
       </c>
       <c r="BR6" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>1.88</v>
@@ -3228,19 +3228,19 @@
         <v>3.56</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3252,10 +3252,10 @@
         <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM6" t="n">
         <v>2.02</v>
@@ -3270,7 +3270,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3294,10 +3294,10 @@
         <v>1.82</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA6" t="n">
         <v>1.62</v>
@@ -3312,79 +3312,79 @@
         <v>3.37</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DH6" t="n">
-        <v>100.65</v>
+        <v>102.28</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.52</v>
+        <v>44.78</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.12</v>
+        <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.12</v>
+        <v>60.83</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.76</v>
+        <v>13.83</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>19.72</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,139 +3887,139 @@
         <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.67</v>
+        <v>90.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.89</v>
+        <v>37.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.67</v>
+        <v>13.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.22</v>
+        <v>14.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>53.33</v>
+        <v>53.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="BE8" t="n">
         <v>1.16</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.17</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1</v>
       </c>
-      <c r="BM8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BP8" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.22</v>
+        <v>5.11</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY8" t="n">
         <v>2.51</v>
@@ -4028,22 +4028,22 @@
         <v>2.76</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CE8" t="n">
         <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG8" t="n">
         <v>2.7</v>
@@ -4061,7 +4061,7 @@
         <v>1.77</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM8" t="n">
         <v>2</v>
@@ -4073,10 +4073,10 @@
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CR8" t="n">
         <v>1.46</v>
@@ -4109,7 +4109,7 @@
         <v>1.61</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC8" t="n">
         <v>2.22</v>
@@ -4118,79 +4118,79 @@
         <v>3.42</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.62</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.66</v>
+        <v>4.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.56</v>
+        <v>41</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.34</v>
+        <v>13.42</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.5</v>
+        <v>16.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.28</v>
+        <v>7.16</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.56</v>
+        <v>53.42</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.77</v>
+        <v>13.47</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.44</v>
+        <v>10.05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.84</v>
+        <v>16.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,127 +4696,127 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>88.56</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.11</v>
+        <v>34.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.89</v>
+        <v>17.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38.11</v>
+        <v>37.3</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.11</v>
+        <v>19.8</v>
       </c>
       <c r="BE10" t="n">
         <v>1.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
         <v>3.96</v>
@@ -4834,34 +4834,34 @@
         <v>4.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.4</v>
+        <v>6.02</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.86</v>
+        <v>6.06</v>
       </c>
       <c r="CE10" t="n">
         <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH10" t="n">
         <v>1.33</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CK10" t="n">
         <v>1.68</v>
@@ -4870,19 +4870,19 @@
         <v>2.24</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
         <v>2.28</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
@@ -4897,10 +4897,10 @@
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4915,10 +4915,10 @@
         <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DD10" t="n">
         <v>3.4</v>
@@ -4927,76 +4927,76 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.47</v>
+        <v>92.94</v>
       </c>
       <c r="DI10" t="n">
         <v>-0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.83</v>
+        <v>3.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.88</v>
+        <v>36.22</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.29</v>
+        <v>17.16</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.29</v>
+        <v>7.56</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.12</v>
+        <v>39.56</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.7</v>
+        <v>11.67</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.94</v>
+        <v>19.28</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.22</v>
@@ -5096,139 +5096,139 @@
         <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>109</v>
+        <v>114.22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN11" t="n">
-        <v>54</v>
+        <v>57.89</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.25</v>
+        <v>14.89</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.25</v>
+        <v>12.22</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>58.62</v>
+        <v>59.11</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.62</v>
+        <v>17.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.12</v>
+        <v>12.78</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.25</v>
+        <v>18.89</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.12</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY11" t="n">
         <v>1.39</v>
@@ -5237,40 +5237,40 @@
         <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="CB11" t="n">
         <v>4.77</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
         <v>1.62</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM11" t="n">
         <v>2.19</v>
@@ -5282,28 +5282,28 @@
         <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CT11" t="n">
         <v>3.1</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
         <v>1.89</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5321,52 +5321,52 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.23</v>
+        <v>106.16</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="DK11" t="n">
-        <v>7.17</v>
+        <v>6.94</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DM11" t="n">
-        <v>56.35</v>
+        <v>58.16</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.65</v>
+        <v>14.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.83</v>
+        <v>11.39</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.18</v>
+        <v>59.39</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.41</v>
+        <v>17.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.77</v>
+        <v>5.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.47</v>
+        <v>18.33</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5499,52 +5499,52 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>97.89</v>
+        <v>102.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>49.33</v>
+        <v>52.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.89</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>56.56</v>
+        <v>56.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.44</v>
+        <v>19.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.83</v>
+        <v>3.74</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.22</v>
+        <v>5.37</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX12" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY12" t="n">
         <v>1.77</v>
@@ -5643,19 +5643,19 @@
         <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
         <v>2.78</v>
@@ -5664,19 +5664,19 @@
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK12" t="n">
         <v>1.61</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN12" t="n">
         <v>1.77</v>
@@ -5688,10 +5688,10 @@
         <v>2.07</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS12" t="n">
         <v>3.05</v>
@@ -5703,10 +5703,10 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CX12" t="n">
         <v>1.67</v>
@@ -5724,85 +5724,85 @@
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.22</v>
+        <v>108.05</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.44</v>
+        <v>59.69</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.72</v>
+        <v>12.68</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.84</v>
+        <v>10.42</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.28</v>
+        <v>57.21</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.06</v>
+        <v>16.1</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.61</v>
+        <v>10.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.44</v>
+        <v>5.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.56</v>
+        <v>19.42</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>91.11</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>37.89</v>
+        <v>39</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.11</v>
+        <v>17.7</v>
       </c>
       <c r="R13" t="n">
-        <v>7.67</v>
+        <v>7.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.67</v>
+        <v>51.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.22</v>
+        <v>12.7</v>
       </c>
       <c r="AA13" t="n">
         <v>8</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.78</v>
+        <v>16.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
         <v>0.11</v>
@@ -5983,70 +5983,70 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.67</v>
+        <v>7.79</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="BR13" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT13" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC13" t="n">
         <v>3.65</v>
@@ -6058,10 +6058,10 @@
         <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
         <v>1.35</v>
@@ -6073,25 +6073,25 @@
         <v>1.97</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO13" t="n">
         <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
@@ -6100,7 +6100,7 @@
         <v>3.15</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6109,7 +6109,7 @@
         <v>1.85</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
         <v>1.65</v>
@@ -6133,79 +6133,79 @@
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.72</v>
+        <v>88.16</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.73</v>
+        <v>3.95</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.16</v>
+        <v>36.84</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17</v>
+        <v>16.84</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.06</v>
+        <v>7.79</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.34</v>
+        <v>50.26</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DX13" t="n">
-        <v>11</v>
+        <v>11.32</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.11</v>
+        <v>7.16</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.89</v>
+        <v>4.16</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.94</v>
+        <v>15.89</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>87.67</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K14" t="n">
-        <v>5.44</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M14" t="n">
-        <v>40.56</v>
+        <v>41.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.22</v>
+        <v>15.7</v>
       </c>
       <c r="R14" t="n">
-        <v>8.109999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.56</v>
+        <v>47</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.22</v>
+        <v>10.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.22</v>
+        <v>20.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6389,64 +6389,64 @@
         <v>2.06</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.53</v>
+        <v>10.17</v>
       </c>
       <c r="BI14" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.47</v>
+        <v>5.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="BR14" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT14" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CB14" t="n">
         <v>3.51</v>
@@ -6458,13 +6458,13 @@
         <v>6.66</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF14" t="n">
         <v>3.24</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CH14" t="n">
         <v>1.31</v>
@@ -6473,13 +6473,13 @@
         <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK14" t="n">
         <v>1.54</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM14" t="n">
         <v>2.36</v>
@@ -6491,10 +6491,10 @@
         <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
@@ -6509,16 +6509,16 @@
         <v>1.35</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW14" t="n">
         <v>2.21</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.34</v>
@@ -6530,7 +6530,7 @@
         <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD14" t="n">
         <v>3.4</v>
@@ -6539,43 +6539,43 @@
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="DH14" t="n">
-        <v>91</v>
+        <v>92.06</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.24</v>
+        <v>40.61</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.52</v>
+        <v>12.39</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.88</v>
+        <v>14.22</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.83</v>
+        <v>44.22</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.06</v>
+        <v>9.83</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.3</v>
+        <v>7.17</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.35</v>
+        <v>20.67</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="H15" t="n">
-        <v>107.43</v>
+        <v>110.88</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>47.86</v>
+        <v>49.12</v>
       </c>
       <c r="N15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>12.71</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="S15" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>54.71</v>
+        <v>56.62</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.86</v>
+        <v>13.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.43</v>
+        <v>7.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.14</v>
+        <v>19.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6789,70 +6789,70 @@
         <v>1.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.529999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
         <v>2.22</v>
@@ -6861,43 +6861,43 @@
         <v>2.33</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CK15" t="n">
         <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN15" t="n">
         <v>1.73</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6912,10 +6912,10 @@
         <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CX15" t="n">
         <v>1.72</v>
@@ -6924,7 +6924,7 @@
         <v>2.17</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA15" t="n">
         <v>1.71</v>
@@ -6933,85 +6933,85 @@
         <v>1.43</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD15" t="n">
         <v>3.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.94</v>
+        <v>103.78</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DK15" t="n">
         <v>5.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.3</v>
+        <v>49.78</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.23</v>
+        <v>11.94</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.59</v>
+        <v>7.56</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>56.82</v>
+        <v>57.55</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.3</v>
+        <v>13.39</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.41</v>
+        <v>8.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.47</v>
+        <v>18.72</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
-        <v>85.56</v>
+        <v>85.8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M16" t="n">
-        <v>39.33</v>
+        <v>38.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P16" t="n">
-        <v>11.22</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.67</v>
+        <v>14.3</v>
       </c>
       <c r="R16" t="n">
-        <v>8.109999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.67</v>
+        <v>43</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.22</v>
+        <v>11.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.56</v>
+        <v>9</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.44</v>
+        <v>16.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,49 +7192,49 @@
         <v>2.12</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.289999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
         <v>1.06</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="BR16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.07</v>
+        <v>4.38</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.39</v>
+        <v>3.47</v>
       </c>
       <c r="CC16" t="n">
         <v>4.52</v>
@@ -7264,28 +7264,28 @@
         <v>4.78</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK16" t="n">
         <v>1.62</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM16" t="n">
         <v>2.23</v>
@@ -7294,25 +7294,25 @@
         <v>1.76</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CT16" t="n">
         <v>2.74</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV16" t="n">
         <v>1.87</v>
@@ -7336,52 +7336,52 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.94</v>
+        <v>84.16</v>
       </c>
       <c r="DI16" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.23</v>
+        <v>37.67</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.65</v>
+        <v>10.28</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.88</v>
+        <v>14.22</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.529999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="DS16" t="n">
         <v>0.11</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.65</v>
+        <v>42.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.7</v>
+        <v>11.28</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.59</v>
+        <v>8.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.23</v>
+        <v>17</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>85.78</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M17" t="n">
-        <v>43.44</v>
+        <v>42.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="R17" t="n">
-        <v>8.220000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.33</v>
+        <v>42.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.220000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.22</v>
+        <v>18.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7595,70 +7595,70 @@
         <v>1.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.83</v>
+        <v>8.68</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BR17" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC17" t="n">
         <v>5.87</v>
@@ -7673,34 +7673,34 @@
         <v>3.12</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM17" t="n">
         <v>2.06</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO17" t="n">
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ17" t="n">
         <v>4.1</v>
@@ -7721,103 +7721,103 @@
         <v>1.78</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD17" t="n">
         <v>3.28</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DH17" t="n">
-        <v>81.94</v>
+        <v>81.42</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.11</v>
+        <v>36.95</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.17</v>
+        <v>12.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.22</v>
+        <v>12.21</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.61</v>
+        <v>39.9</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.78</v>
+        <v>7.68</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.77</v>
+        <v>16.74</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>107.67</v>
+        <v>107.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>48.89</v>
+        <v>48.9</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.78</v>
+        <v>16.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.11</v>
+        <v>14.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.78</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,49 +7974,49 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>57.11</v>
+        <v>56.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="BB18" t="n">
         <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.44</v>
+        <v>20.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.720000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BN18" t="n">
         <v>0.89</v>
@@ -8025,22 +8025,22 @@
         <v>0.89</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.44</v>
+        <v>5.21</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BT18" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BU18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BY18" t="n">
         <v>1.89</v>
@@ -8058,16 +8058,16 @@
         <v>2.08</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB18" t="n">
         <v>3.48</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="CE18" t="n">
         <v>1.44</v>
@@ -8088,16 +8088,16 @@
         <v>2.03</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
@@ -8106,7 +8106,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8121,106 +8121,106 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW18" t="n">
         <v>2.09</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD18" t="n">
         <v>3.6</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="DH18" t="n">
-        <v>110.84</v>
+        <v>110.74</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.28</v>
+        <v>5.1</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.39</v>
+        <v>51.26</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.5</v>
+        <v>14.79</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15</v>
+        <v>14.74</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.61</v>
+        <v>6.79</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.78</v>
+        <v>57.31</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.22</v>
+        <v>13.05</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.34</v>
+        <v>8.26</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.33</v>
+        <v>20.74</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>95.22</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M19" t="n">
-        <v>42.67</v>
+        <v>41.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>13.33</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48.22</v>
+        <v>47.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.67</v>
+        <v>11.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.220000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.33</v>
+        <v>17.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.06</v>
+        <v>8.16</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.44</v>
+        <v>4.63</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.23</v>
+        <v>3.37</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
         <v>4.81</v>
@@ -8476,7 +8476,7 @@
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG19" t="n">
         <v>2.77</v>
@@ -8500,25 +8500,25 @@
         <v>2.2</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO19" t="n">
         <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
@@ -8530,100 +8530,100 @@
         <v>1.92</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.15</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB19" t="n">
         <v>1.37</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.33</v>
+        <v>86.52</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.11</v>
+        <v>37</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.22</v>
+        <v>12.68</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.89</v>
+        <v>7.84</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.94</v>
+        <v>45.84</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.62</v>
+        <v>10.37</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.83</v>
+        <v>6.68</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.88</v>
+        <v>16.68</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>101.22</v>
+        <v>102.3</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M20" t="n">
-        <v>43.22</v>
+        <v>44.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>13.89</v>
+        <v>14.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="S20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>45.67</v>
+        <v>46.5</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.89</v>
+        <v>7.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.33</v>
+        <v>18.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8804,70 +8804,70 @@
         <v>2.11</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.5</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BR20" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT20" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV20" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW20" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX20" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BZ20" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="CB20" t="n">
         <v>3.41</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CB20" t="n">
-        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>4.61</v>
@@ -8876,7 +8876,7 @@
         <v>5.09</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF20" t="n">
         <v>3.16</v>
@@ -8900,34 +8900,34 @@
         <v>2.23</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO20" t="n">
         <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW20" t="n">
         <v>2.04</v>
@@ -8954,46 +8954,46 @@
         <v>3.42</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DH20" t="n">
-        <v>92.39</v>
+        <v>93.42</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.33</v>
+        <v>38.21</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DP20" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.94</v>
+        <v>10.79</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.34</v>
+        <v>8.16</v>
       </c>
       <c r="DS20" t="n">
         <v>0.16</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.44</v>
+        <v>44.95</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.56</v>
+        <v>12.42</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.94</v>
+        <v>7.84</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.66</v>
+        <v>17.42</v>
       </c>
       <c r="EB20" t="n">
         <v>1.39</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,112 +9129,112 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.67</v>
+        <v>82.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.33</v>
+        <v>33</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.89</v>
+        <v>13.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.22</v>
+        <v>11.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43.78</v>
+        <v>44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.11</v>
+        <v>18.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.94</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="BQ21" t="n">
         <v>5.11</v>
@@ -9243,22 +9243,22 @@
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT21" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU21" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX21" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY21" t="n">
         <v>3.06</v>
@@ -9267,19 +9267,19 @@
         <v>3.41</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CC21" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.19</v>
+        <v>5.01</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF21" t="n">
         <v>3.12</v>
@@ -9288,40 +9288,40 @@
         <v>2.67</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI21" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO21" t="n">
         <v>1.37</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT21" t="n">
         <v>2.72</v>
@@ -9330,10 +9330,10 @@
         <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX21" t="n">
         <v>1.62</v>
@@ -9351,7 +9351,7 @@
         <v>1.42</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD21" t="n">
         <v>3.26</v>
@@ -9363,40 +9363,40 @@
         <v>1.11</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.5</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="DI21" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.33</v>
+        <v>39.31</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DP21" t="n">
-        <v>14.11</v>
+        <v>13.79</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.77</v>
+        <v>12</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DS21" t="n">
         <v>0.11</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.11</v>
+        <v>46.1</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.39</v>
+        <v>12.21</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.619999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.94</v>
+        <v>18.26</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>102.22</v>
+        <v>106.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.11</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>45.67</v>
+        <v>52.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>10.67</v>
+        <v>10.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.33</v>
+        <v>12.8</v>
       </c>
       <c r="R2" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.89</v>
+        <v>51.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,28 +1550,28 @@
         <v>1.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
         <v>1.06</v>
@@ -1580,37 +1580,37 @@
         <v>4.06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CB2" t="n">
         <v>3.96</v>
@@ -1622,7 +1622,7 @@
         <v>2.26</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
         <v>2.85</v>
@@ -1634,16 +1634,16 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
         <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM2" t="n">
         <v>2.25</v>
@@ -1652,13 +1652,13 @@
         <v>1.77</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
@@ -1673,10 +1673,10 @@
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX2" t="n">
         <v>1.65</v>
@@ -1691,88 +1691,88 @@
         <v>1.82</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD2" t="n">
         <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.59</v>
+        <v>100.22</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.77</v>
+        <v>48.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.23</v>
+        <v>12</v>
       </c>
       <c r="DR2" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.59</v>
+        <v>52.11</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.24</v>
+        <v>14.28</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.529999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.71</v>
+        <v>4.89</v>
       </c>
       <c r="EA2" t="n">
         <v>18</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -2016,13 +2016,13 @@
         <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC3" t="n">
         <v>2.34</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2067,10 +2067,10 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
         <v>1.43</v>
@@ -2079,16 +2079,16 @@
         <v>2.03</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
         <v>2.13</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
         <v>1.73</v>
@@ -2097,10 +2097,10 @@
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,127 +2278,127 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>82.89</v>
+        <v>80.7</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.33</v>
+        <v>31.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16.78</v>
+        <v>15.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.44</v>
+        <v>15.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.33</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>55.33</v>
+        <v>53.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.67</v>
+        <v>10.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.33</v>
+        <v>17.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.279999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2407,25 +2407,25 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY4" t="n">
         <v>2.27</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.51</v>
+        <v>3.67</v>
       </c>
       <c r="CE4" t="n">
         <v>1.45</v>
@@ -2446,25 +2446,25 @@
         <v>1.94</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
         <v>2.42</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO4" t="n">
         <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CR4" t="n">
         <v>1.48</v>
@@ -2479,19 +2479,19 @@
         <v>1.37</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA4" t="n">
         <v>1.67</v>
@@ -2500,52 +2500,52 @@
         <v>1.41</v>
       </c>
       <c r="DC4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DG4" t="n">
         <v>2.31</v>
       </c>
-      <c r="DD4" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.44</v>
-      </c>
       <c r="DH4" t="n">
-        <v>96.94</v>
+        <v>95.05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="DK4" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.72</v>
+        <v>39.74</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.23</v>
+        <v>14.58</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.28</v>
+        <v>15.21</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.33</v>
+        <v>5.84</v>
       </c>
       <c r="DS4" t="n">
         <v>0.16</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.72</v>
+        <v>54.95</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.22</v>
+        <v>12.9</v>
       </c>
       <c r="DY4" t="n">
-        <v>9</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.56</v>
+        <v>19.58</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>73</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.44</v>
+        <v>27.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.11</v>
+        <v>14.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.11</v>
+        <v>14.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.89</v>
+        <v>44.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.220000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.22</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.11</v>
+        <v>16.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.83</v>
+        <v>8.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY5" t="n">
         <v>3.72</v>
@@ -2819,34 +2819,34 @@
         <v>4.19</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.28</v>
+        <v>5.97</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.96</v>
+        <v>6.61</v>
       </c>
       <c r="CE5" t="n">
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
@@ -2855,28 +2855,28 @@
         <v>2.17</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN5" t="n">
         <v>1.75</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
@@ -2894,16 +2894,16 @@
         <v>2.12</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DD5" t="n">
         <v>3.38</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.28</v>
+        <v>75.16</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.78</v>
+        <v>30.37</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO5" t="n">
         <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.66</v>
+        <v>15.47</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.34</v>
+        <v>15.37</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.22</v>
+        <v>45.79</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.609999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.22</v>
+        <v>6.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.39</v>
+        <v>3.47</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.78</v>
+        <v>17.89</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="n">
-        <v>109.38</v>
+        <v>108.33</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>43.62</v>
+        <v>43.44</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.75</v>
+        <v>13.44</v>
       </c>
       <c r="R6" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="S6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61.25</v>
+        <v>61</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>14.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.25</v>
+        <v>23.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,82 +3165,82 @@
         <v>2.11</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.67</v>
+        <v>7.58</v>
       </c>
       <c r="BI6" t="n">
         <v>2.11</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
         <v>3.02</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3252,16 +3252,16 @@
         <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CL6" t="n">
         <v>2.34</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
@@ -3291,16 +3291,16 @@
         <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.02</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
@@ -3312,31 +3312,31 @@
         <v>3.37</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="DG6" t="n">
         <v>2.11</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.28</v>
+        <v>102.16</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="DK6" t="n">
         <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.78</v>
+        <v>44.63</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
@@ -3345,46 +3345,46 @@
         <v>1.89</v>
       </c>
       <c r="DP6" t="n">
-        <v>15</v>
+        <v>14.95</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13</v>
+        <v>12.47</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.83</v>
+        <v>60.74</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.83</v>
+        <v>13.74</v>
       </c>
       <c r="DY6" t="n">
         <v>8.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.72</v>
+        <v>20.26</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="7">
@@ -3394,91 +3394,91 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
-        <v>81.88</v>
+        <v>82.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>12.38</v>
+        <v>12.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="R7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.25</v>
+        <v>46.89</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>20</v>
+        <v>19.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -3565,88 +3565,88 @@
         <v>2.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.890000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.56</v>
+        <v>5.42</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.18</v>
+        <v>3.98</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.82</v>
+        <v>4.57</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="CC7" t="n">
         <v>6.5</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="CE7" t="n">
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
         <v>1.81</v>
@@ -3658,7 +3658,7 @@
         <v>1.68</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CM7" t="n">
         <v>2.12</v>
@@ -3667,22 +3667,22 @@
         <v>1.67</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
@@ -3694,97 +3694,97 @@
         <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.89</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.56</v>
+        <v>30.58</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.11</v>
+        <v>13.26</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.84</v>
+        <v>12.79</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.94</v>
+        <v>10.16</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.5</v>
+        <v>45.42</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.33</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.33</v>
+        <v>19.1</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
         <v>2.11</v>
@@ -4037,7 +4037,7 @@
         <v>3.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CE8" t="n">
         <v>1.44</v>
@@ -4082,10 +4082,10 @@
         <v>1.46</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
@@ -4097,16 +4097,16 @@
         <v>1.95</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB8" t="n">
         <v>1.39</v>
@@ -4115,7 +4115,7 @@
         <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="DE8" t="n">
         <v>0.1</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.62</v>
+        <v>79.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.12</v>
+        <v>28.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.75</v>
+        <v>13.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.75</v>
+        <v>14.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.25</v>
+        <v>41</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.88</v>
+        <v>10.44</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.75</v>
+        <v>20.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.89</v>
+        <v>5.11</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY9" t="n">
         <v>3.08</v>
@@ -4431,25 +4431,25 @@
         <v>3.28</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.63</v>
+        <v>5.06</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.89</v>
+        <v>5.3</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
@@ -4458,7 +4458,7 @@
         <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CK9" t="n">
         <v>1.69</v>
@@ -4467,19 +4467,19 @@
         <v>2.26</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO9" t="n">
         <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4512,55 +4512,55 @@
         <v>1.67</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="DH9" t="n">
-        <v>87.22</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="DL9" t="n">
         <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.72</v>
+        <v>34.63</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.78</v>
+        <v>13.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.33</v>
+        <v>15.1</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.5</v>
+        <v>7.68</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.17</v>
+        <v>46.74</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.45</v>
+        <v>11.21</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.5</v>
+        <v>7.37</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.06</v>
+        <v>20.84</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="10">
@@ -4717,7 +4717,7 @@
         <v>0.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="AO10" t="n">
         <v>1.2</v>
@@ -4831,19 +4831,19 @@
         <v>3.96</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="CA10" t="n">
         <v>3.57</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
         <v>6.02</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.06</v>
+        <v>6.51</v>
       </c>
       <c r="CE10" t="n">
         <v>1.46</v>
@@ -4891,13 +4891,13 @@
         <v>3.1</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW10" t="n">
         <v>2.17</v>
@@ -4909,10 +4909,10 @@
         <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB10" t="n">
         <v>1.43</v>
@@ -4921,7 +4921,7 @@
         <v>2.37</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.22</v>
+        <v>36.28</v>
       </c>
       <c r="DN10" t="n">
         <v>1.16</v>
@@ -5240,13 +5240,13 @@
         <v>4.48</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="CC11" t="n">
         <v>1.87</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5291,7 +5291,7 @@
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT11" t="n">
         <v>3.1</v>
@@ -5303,7 +5303,7 @@
         <v>1.89</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5321,10 +5321,10 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DE11" t="n">
         <v>0.28</v>
@@ -5643,13 +5643,13 @@
         <v>3.74</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
         <v>1.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
@@ -5703,13 +5703,13 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
         <v>2.1</v>
@@ -5724,7 +5724,7 @@
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
         <v>3.4</v>
@@ -6040,7 +6040,7 @@
         <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="CA13" t="n">
         <v>3.36</v>
@@ -6094,13 +6094,13 @@
         <v>3.85</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6109,25 +6109,25 @@
         <v>1.85</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DB13" t="n">
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
@@ -6443,7 +6443,7 @@
         <v>4.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="CA14" t="n">
         <v>3.37</v>
@@ -6500,19 +6500,19 @@
         <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CU14" t="n">
         <v>1.35</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CX14" t="n">
         <v>1.6</v>
@@ -6846,19 +6846,19 @@
         <v>1.93</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CA15" t="n">
         <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CC15" t="n">
         <v>2.22</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
@@ -6915,7 +6915,7 @@
         <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CX15" t="n">
         <v>1.72</v>
@@ -6927,16 +6927,16 @@
         <v>2.16</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC15" t="n">
         <v>2.34</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
@@ -7249,13 +7249,13 @@
         <v>4.06</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="CA16" t="n">
         <v>3.4</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="CC16" t="n">
         <v>4.52</v>
@@ -7306,19 +7306,19 @@
         <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CT16" t="n">
         <v>2.74</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV16" t="n">
         <v>1.87</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX16" t="n">
         <v>1.65</v>
@@ -7327,7 +7327,7 @@
         <v>2.06</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA16" t="n">
         <v>1.79</v>
@@ -7336,10 +7336,10 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,166 +7514,166 @@
         <v>2.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.11</v>
+        <v>80.7</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>30.78</v>
+        <v>31.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>36.89</v>
+        <v>37.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.67</v>
+        <v>10.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.33</v>
+        <v>14.6</v>
       </c>
       <c r="BE17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1</v>
       </c>
-      <c r="BF17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BP17" t="n">
-        <v>4.11</v>
+        <v>3.85</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.58</v>
+        <v>4.3</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY17" t="n">
         <v>4.29</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.87</v>
+        <v>5.73</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.61</v>
+        <v>6.44</v>
       </c>
       <c r="CE17" t="n">
         <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7691,7 +7691,7 @@
         <v>2.27</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CN17" t="n">
         <v>1.65</v>
@@ -7703,13 +7703,13 @@
         <v>2.2</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT17" t="n">
         <v>2.76</v>
@@ -7724,13 +7724,13 @@
         <v>2.13</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA17" t="n">
         <v>1.66</v>
@@ -7739,7 +7739,7 @@
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD17" t="n">
         <v>3.28</v>
@@ -7748,76 +7748,76 @@
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>81.42</v>
+        <v>82.55</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="DM17" t="n">
-        <v>36.95</v>
+        <v>37.15</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.95</v>
+        <v>13.1</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.21</v>
+        <v>12.25</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.369999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="DW17" t="n">
         <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.949999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.74</v>
+        <v>16.75</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>114</v>
+        <v>117.2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M18" t="n">
-        <v>53.89</v>
+        <v>57.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.89</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>58.44</v>
+        <v>59.1</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.44</v>
+        <v>15.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.67</v>
+        <v>10.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.22</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,49 +7998,49 @@
         <v>2.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.470000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BT18" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,19 +8049,19 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC18" t="n">
         <v>2.45</v>
@@ -8091,7 +8091,7 @@
         <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CM18" t="n">
         <v>2.1</v>
@@ -8106,7 +8106,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8115,13 +8115,13 @@
         <v>3.26</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU18" t="n">
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW18" t="n">
         <v>2.09</v>
@@ -8130,7 +8130,7 @@
         <v>1.74</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.13</v>
@@ -8142,7 +8142,7 @@
         <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD18" t="n">
         <v>3.6</v>
@@ -8151,13 +8151,13 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DH18" t="n">
-        <v>110.74</v>
+        <v>112.5</v>
       </c>
       <c r="DI18" t="n">
         <v>0.05</v>
@@ -8169,25 +8169,25 @@
         <v>5.1</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>51.26</v>
+        <v>53</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.79</v>
+        <v>14.8</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.74</v>
+        <v>14.8</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="DS18" t="n">
         <v>0.05</v>
@@ -8199,25 +8199,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.31</v>
+        <v>57.7</v>
       </c>
       <c r="DW18" t="n">
         <v>0.05</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.05</v>
+        <v>13.7</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.26</v>
+        <v>8.85</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.74</v>
+        <v>20.65</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="EC18" t="n">
         <v>1.9</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8323,163 +8323,163 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.44</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.56</v>
+        <v>30.7</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.11</v>
+        <v>13.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.78</v>
+        <v>13.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.890000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.67</v>
+        <v>42.8</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.56</v>
+        <v>9.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.44</v>
+        <v>5.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.44</v>
+        <v>15.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.16</v>
+        <v>8.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>3.19</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.37</v>
+        <v>3.49</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CB19" t="n">
         <v>3.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.81</v>
+        <v>4.84</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.07</v>
+        <v>5.17</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
@@ -8488,25 +8488,25 @@
         <v>1.88</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK19" t="n">
         <v>1.64</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN19" t="n">
         <v>1.74</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.58</v>
@@ -8524,10 +8524,10 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX19" t="n">
         <v>1.71</v>
@@ -8545,52 +8545,52 @@
         <v>1.37</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD19" t="n">
         <v>3.31</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.52</v>
+        <v>86.45</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM19" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.68</v>
+        <v>12.85</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.9</v>
+        <v>13.95</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.84</v>
+        <v>8.1</v>
       </c>
       <c r="DS19" t="n">
         <v>0.1</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.84</v>
+        <v>45.3</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.37</v>
+        <v>10.1</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.68</v>
+        <v>6.45</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.68</v>
+        <v>16.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -8861,13 +8861,13 @@
         <v>3.14</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CA20" t="n">
         <v>3.32</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC20" t="n">
         <v>4.61</v>
@@ -8915,7 +8915,7 @@
         <v>4.05</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS20" t="n">
         <v>3.19</v>
@@ -8933,16 +8933,16 @@
         <v>2.04</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DB20" t="n">
         <v>1.42</v>
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -9051,79 +9051,79 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>94.33</v>
+        <v>93.5</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>46.33</v>
+        <v>45.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="P21" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.33</v>
+        <v>12.6</v>
       </c>
       <c r="R21" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48.44</v>
+        <v>49</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.89</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.78</v>
+        <v>17.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,64 +9207,64 @@
         <v>2.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX21" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="CA21" t="n">
         <v>3.42</v>
@@ -9276,16 +9276,16 @@
         <v>4.8</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.01</v>
+        <v>5.05</v>
       </c>
       <c r="CE21" t="n">
         <v>1.46</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH21" t="n">
         <v>1.34</v>
@@ -9294,40 +9294,40 @@
         <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK21" t="n">
         <v>1.57</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO21" t="n">
         <v>1.37</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV21" t="n">
         <v>1.86</v>
@@ -9336,16 +9336,16 @@
         <v>2.03</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DB21" t="n">
         <v>1.42</v>
@@ -9360,76 +9360,76 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.26000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.31</v>
+        <v>39.4</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.79</v>
+        <v>13.75</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12</v>
+        <v>12.15</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="DW21" t="n">
         <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.21</v>
+        <v>12.15</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.26</v>
+        <v>18</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,139 +1469,139 @@
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>92.38</v>
+        <v>91.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>43.75</v>
+        <v>42.78</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52.38</v>
+        <v>51.89</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.25</v>
+        <v>11.44</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.88</v>
+        <v>7.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.88</v>
+        <v>16.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.109999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.06</v>
+        <v>5.32</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY2" t="n">
         <v>1.67</v>
@@ -1610,10 +1610,10 @@
         <v>1.65</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CC2" t="n">
         <v>2.13</v>
@@ -1625,7 +1625,7 @@
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG2" t="n">
         <v>2.82</v>
@@ -1634,10 +1634,10 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
         <v>1.59</v>
@@ -1646,16 +1646,16 @@
         <v>2.19</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN2" t="n">
         <v>1.77</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.4</v>
@@ -1667,16 +1667,16 @@
         <v>3.02</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU2" t="n">
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX2" t="n">
         <v>1.65</v>
@@ -1688,13 +1688,13 @@
         <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
         <v>3.47</v>
@@ -1703,43 +1703,43 @@
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.22</v>
+        <v>99.42</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.39</v>
+        <v>47.69</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.94</v>
+        <v>6.05</v>
       </c>
       <c r="DS2" t="n">
         <v>0.16</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.11</v>
+        <v>51.9</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.28</v>
+        <v>14.21</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="EA2" t="n">
-        <v>18</v>
+        <v>17.63</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>109.4</v>
+        <v>109.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>54.5</v>
+        <v>54.45</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>11.1</v>
+        <v>11.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.9</v>
+        <v>11.45</v>
       </c>
       <c r="R3" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55.3</v>
+        <v>55.36</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.1</v>
+        <v>16.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.3</v>
+        <v>11.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.8</v>
+        <v>18.09</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,67 +1953,67 @@
         <v>1.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CB3" t="n">
         <v>3.82</v>
@@ -2025,22 +2025,22 @@
         <v>2.34</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK3" t="n">
         <v>1.66</v>
@@ -2052,7 +2052,7 @@
         <v>2.15</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2067,7 +2067,7 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CT3" t="n">
         <v>3.07</v>
@@ -2076,7 +2076,7 @@
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW3" t="n">
         <v>1.87</v>
@@ -2091,7 +2091,7 @@
         <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,7 +2100,7 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
@@ -2109,40 +2109,40 @@
         <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.79</v>
+        <v>104.35</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.74</v>
+        <v>50.9</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.26</v>
+        <v>11.4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.79</v>
+        <v>11.1</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2160,22 +2160,22 @@
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.26</v>
+        <v>14.45</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.26</v>
+        <v>18.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>76.59999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.8</v>
+        <v>15.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.3</v>
+        <v>14.55</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44.2</v>
+        <v>45.27</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.4</v>
+        <v>10.82</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>7.64</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.5</v>
+        <v>17.27</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.68</v>
+        <v>8.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
         <v>3.72</v>
@@ -2819,55 +2819,55 @@
         <v>4.19</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.97</v>
+        <v>5.81</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.61</v>
+        <v>6.39</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI5" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO5" t="n">
         <v>1.37</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CR5" t="n">
         <v>1.5</v>
@@ -2882,28 +2882,28 @@
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW5" t="n">
         <v>2.15</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DD5" t="n">
         <v>3.38</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DH5" t="n">
-        <v>75.16</v>
+        <v>76.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.37</v>
+        <v>30.85</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.47</v>
+        <v>15.7</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.37</v>
+        <v>15.45</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.210000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.79</v>
+        <v>46.3</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.21</v>
+        <v>10.45</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.74</v>
+        <v>7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.89</v>
+        <v>18.25</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.22</v>
@@ -3484,139 +3484,139 @@
         <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.3</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BG7" t="n">
         <v>2.4</v>
       </c>
-      <c r="AL7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="BH7" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.58</v>
-      </c>
       <c r="BK7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>3.98</v>
@@ -3625,136 +3625,136 @@
         <v>4.57</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.93</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.5</v>
+        <v>7.04</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.23</v>
+        <v>7.66</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="CR7" t="n">
         <v>1.47</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="CT7" t="n">
         <v>2.78</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.58</v>
+        <v>30.9</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.26</v>
+        <v>13</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.79</v>
+        <v>12.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.16</v>
+        <v>9.9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.42</v>
+        <v>45.25</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.31</v>
+        <v>5.4</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.1</v>
+        <v>18.95</v>
       </c>
       <c r="EB7" t="n">
         <v>0.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>92.56</v>
+        <v>93.8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.11</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>45.22</v>
+        <v>46.1</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.78</v>
+        <v>17.4</v>
       </c>
       <c r="R8" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.78</v>
+        <v>53.6</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.11</v>
+        <v>16.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,67 +3968,67 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.210000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.11</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU8" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CB8" t="n">
         <v>3.4</v>
@@ -4043,7 +4043,7 @@
         <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG8" t="n">
         <v>2.7</v>
@@ -4052,67 +4052,67 @@
         <v>1.35</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK8" t="n">
         <v>1.77</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO8" t="n">
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CR8" t="n">
         <v>1.46</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB8" t="n">
         <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD8" t="n">
         <v>3.37</v>
@@ -4121,76 +4121,76 @@
         <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.31999999999999</v>
+        <v>92</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM8" t="n">
-        <v>41</v>
+        <v>41.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.42</v>
+        <v>13.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.16</v>
+        <v>16.05</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.16</v>
+        <v>7.3</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.42</v>
+        <v>53.35</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.47</v>
+        <v>13.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.05</v>
+        <v>10.2</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.53</v>
+        <v>16.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>93.3</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M9" t="n">
-        <v>40.2</v>
+        <v>39.18</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.8</v>
+        <v>16.18</v>
       </c>
       <c r="R9" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,25 +4266,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.9</v>
+        <v>51.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.9</v>
+        <v>11.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.3</v>
+        <v>20.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -4371,70 +4371,70 @@
         <v>2.11</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.11</v>
+        <v>4.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BZ9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CB9" t="n">
         <v>3.28</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>3.3</v>
       </c>
       <c r="CC9" t="n">
         <v>5.06</v>
@@ -4449,7 +4449,7 @@
         <v>3.32</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
@@ -4464,22 +4464,22 @@
         <v>1.69</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO9" t="n">
         <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4500,67 +4500,67 @@
         <v>2.28</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DD9" t="n">
         <v>3.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.68000000000001</v>
+        <v>86.95</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.63</v>
+        <v>34.35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.47</v>
+        <v>13.65</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.1</v>
+        <v>15.35</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.68</v>
+        <v>7.6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.74</v>
+        <v>46.6</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.37</v>
+        <v>7.2</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.84</v>
+        <v>20.25</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC9" t="n">
         <v>2.05</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="n">
-        <v>99</v>
+        <v>99.67</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="K10" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>38.88</v>
+        <v>39.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="O10" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="P10" t="n">
-        <v>16.62</v>
+        <v>16.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="R10" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.38</v>
+        <v>41.67</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.62</v>
+        <v>18.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,49 +4774,49 @@
         <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.56</v>
+        <v>8.26</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="BR10" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.96</v>
+        <v>3.87</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CC10" t="n">
         <v>6.02</v>
@@ -4846,43 +4846,43 @@
         <v>6.51</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.1</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
@@ -4897,28 +4897,28 @@
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CX10" t="n">
         <v>1.76</v>
       </c>
-      <c r="CW10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.74</v>
-      </c>
       <c r="CY10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DD10" t="n">
         <v>3.46</v>
@@ -4927,76 +4927,76 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DH10" t="n">
-        <v>92.94</v>
+        <v>93.58</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.28</v>
+        <v>36.53</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.16</v>
+        <v>16.89</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.56</v>
+        <v>7.52</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.56</v>
+        <v>39.37</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.67</v>
+        <v>11.58</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.28</v>
+        <v>7.32</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.28</v>
+        <v>19.21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>98.11</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M11" t="n">
-        <v>58.44</v>
+        <v>57.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.56</v>
+        <v>10.5</v>
       </c>
       <c r="R11" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>59.67</v>
+        <v>58.7</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.11</v>
+        <v>17.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.78</v>
+        <v>17.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5177,70 +5177,70 @@
         <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
         <v>1.11</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.67</v>
+        <v>5.53</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
       <c r="CC11" t="n">
         <v>1.87</v>
@@ -5249,157 +5249,157 @@
         <v>1.82</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK11" t="n">
         <v>1.62</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM11" t="n">
         <v>2.19</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.16</v>
+        <v>105.89</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.16</v>
+        <v>57.58</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.94</v>
+        <v>14.79</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.39</v>
+        <v>11.31</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.44</v>
+        <v>5.37</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.39</v>
+        <v>58.89</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.89</v>
+        <v>17.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>12</v>
+        <v>11.84</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.89</v>
+        <v>5.79</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.33</v>
+        <v>18.32</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="12">
@@ -5409,67 +5409,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>114.56</v>
+        <v>116.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>67.56</v>
+        <v>66.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>11.22</v>
+        <v>11.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="R12" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -5478,25 +5478,25 @@
         <v>58</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.11</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.22</v>
+        <v>11.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.89</v>
+        <v>7.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.67</v>
+        <v>19.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AF12" t="n">
         <v>0.1</v>
@@ -5580,70 +5580,70 @@
         <v>1.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.74</v>
+        <v>3.86</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.99</v>
       </c>
       <c r="CC12" t="n">
         <v>1.98</v>
@@ -5652,124 +5652,124 @@
         <v>2.04</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CT12" t="n">
         <v>2.87</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DH12" t="n">
-        <v>108.05</v>
+        <v>109.35</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>59.69</v>
+        <v>59.55</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.68</v>
+        <v>12.85</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.21</v>
+        <v>6.05</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.21</v>
+        <v>57.25</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.68</v>
+        <v>5.95</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.42</v>
+        <v>19.35</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5902,52 +5902,52 @@
         <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.33</v>
+        <v>88.7</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>34.44</v>
+        <v>34.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.22</v>
+        <v>10.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.89</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.22</v>
+        <v>6.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.11</v>
+        <v>15.7</v>
       </c>
       <c r="BE13" t="n">
         <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.79</v>
+        <v>7.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BN13" t="n">
         <v>1.05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BT13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BU13" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
@@ -6043,55 +6043,55 @@
         <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="CD13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CQ13" t="n">
         <v>3.94</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>3.85</v>
       </c>
       <c r="CR13" t="n">
         <v>1.46</v>
@@ -6106,106 +6106,106 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>88.16</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.84</v>
+        <v>36.6</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.05</v>
+        <v>10.85</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.84</v>
+        <v>16.6</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.26</v>
+        <v>50.95</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.16</v>
+        <v>7.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.89</v>
+        <v>16.15</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="H14" t="n">
-        <v>89.90000000000001</v>
+        <v>89.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M14" t="n">
-        <v>41.2</v>
+        <v>40.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>12.2</v>
+        <v>12.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.7</v>
+        <v>15.82</v>
       </c>
       <c r="R14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47</v>
+        <v>46.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.17</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="BR14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.42</v>
+        <v>4.28</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
         <v>6.22</v>
@@ -6458,13 +6458,13 @@
         <v>6.66</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CH14" t="n">
         <v>1.31</v>
@@ -6479,22 +6479,22 @@
         <v>1.54</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN14" t="n">
         <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
@@ -6527,55 +6527,55 @@
         <v>1.85</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DD14" t="n">
         <v>3.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.06</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.61</v>
+        <v>40</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.39</v>
+        <v>12.58</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.22</v>
+        <v>14.37</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.06</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.22</v>
+        <v>44.05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.17</v>
+        <v>7.27</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.67</v>
+        <v>20.79</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6708,139 +6708,139 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AI15" t="n">
-        <v>98.09999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.5</v>
+        <v>5.09</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.3</v>
+        <v>48</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.9</v>
+        <v>11.82</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>58.3</v>
+        <v>57.55</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.1</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="BD15" t="n">
         <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.44</v>
+        <v>8.26</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT15" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY15" t="n">
         <v>1.93</v>
@@ -6855,22 +6855,22 @@
         <v>3.62</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI15" t="n">
         <v>1.73</v>
@@ -6882,7 +6882,7 @@
         <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
         <v>2.18</v>
@@ -6894,19 +6894,19 @@
         <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU15" t="n">
         <v>1.35</v>
@@ -6918,16 +6918,16 @@
         <v>2.2</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB15" t="n">
         <v>1.42</v>
@@ -6939,79 +6939,79 @@
         <v>3.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
         <v>1.05</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.78</v>
+        <v>101.63</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.83</v>
+        <v>5.58</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.78</v>
+        <v>48.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.94</v>
+        <v>11.9</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13</v>
+        <v>12.95</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.55</v>
+        <v>57.16</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.39</v>
+        <v>13.05</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.56</v>
+        <v>8.32</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.83</v>
+        <v>4.73</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.72</v>
+        <v>18.68</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -7114,127 +7114,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.12</v>
+        <v>84.89</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>37</v>
+        <v>38.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>10.78</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.12</v>
+        <v>14.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.5</v>
+        <v>43.44</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.12</v>
+        <v>19.33</v>
       </c>
       <c r="BE16" t="n">
         <v>1.23</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.06</v>
+        <v>7.95</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT16" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU16" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY16" t="n">
         <v>4.06</v>
@@ -7252,25 +7252,25 @@
         <v>4.65</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.52</v>
+        <v>4.34</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.78</v>
+        <v>4.57</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7282,25 +7282,25 @@
         <v>1.97</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7315,106 +7315,106 @@
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW16" t="n">
         <v>2.04</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB16" t="n">
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD16" t="n">
         <v>3.56</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.16</v>
+        <v>85.37</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.67</v>
+        <v>38.42</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.28</v>
+        <v>10.63</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.22</v>
+        <v>14.31</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.83</v>
+        <v>8.74</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.33</v>
+        <v>43.21</v>
       </c>
       <c r="DW16" t="n">
         <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.28</v>
+        <v>11.31</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.33</v>
+        <v>8.42</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>17</v>
+        <v>17.63</v>
       </c>
       <c r="EB16" t="n">
         <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="17">
@@ -7520,7 +7520,7 @@
         <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>80.7</v>
@@ -7535,7 +7535,7 @@
         <v>3.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN17" t="n">
         <v>31.8</v>
@@ -7544,7 +7544,7 @@
         <v>0.7</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17" t="n">
         <v>13.8</v>
@@ -7622,10 +7622,10 @@
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR17" t="n">
         <v>85</v>
@@ -7751,7 +7751,7 @@
         <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DH17" t="n">
         <v>82.55</v>
@@ -7766,7 +7766,7 @@
         <v>3.65</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DM17" t="n">
         <v>37.15</v>
@@ -7775,7 +7775,7 @@
         <v>0.7</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="DP17" t="n">
         <v>13.1</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -8127,13 +8127,13 @@
         <v>2.09</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA18" t="n">
         <v>1.69</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.7</v>
+        <v>57.65</v>
       </c>
       <c r="DW18" t="n">
         <v>0.05</v>
@@ -8377,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
@@ -8530,16 +8530,16 @@
         <v>1.93</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB19" t="n">
         <v>1.37</v>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.3</v>
+        <v>45.35</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>0.1</v>
@@ -8723,139 +8723,139 @@
         <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>83.56</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>31.44</v>
+        <v>31.9</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.11</v>
+        <v>14.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.67</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>43.22</v>
+        <v>43.3</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="BD20" t="n">
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.529999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="BR20" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS20" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT20" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW20" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX20" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY20" t="n">
         <v>3.14</v>
@@ -8864,22 +8864,22 @@
         <v>3.3</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG20" t="n">
         <v>2.6</v>
@@ -8903,7 +8903,7 @@
         <v>2.09</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO20" t="n">
         <v>1.38</v>
@@ -8912,16 +8912,16 @@
         <v>2.22</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8936,97 +8936,97 @@
         <v>1.74</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DH20" t="n">
-        <v>93.42</v>
+        <v>93.7</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM20" t="n">
-        <v>38.21</v>
+        <v>38.1</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.1</v>
+        <v>14.25</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.79</v>
+        <v>10.95</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.95</v>
+        <v>44.9</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.42</v>
+        <v>12.3</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.84</v>
+        <v>7.8</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.42</v>
+        <v>17.35</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -9051,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
         <v>93.5</v>
@@ -9066,7 +9066,7 @@
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M21" t="n">
         <v>45.8</v>
@@ -9075,7 +9075,7 @@
         <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
         <v>14.2</v>
@@ -9234,10 +9234,10 @@
         <v>1.2</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9363,7 +9363,7 @@
         <v>1.1</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="DH21" t="n">
         <v>88.15000000000001</v>
@@ -9378,7 +9378,7 @@
         <v>4.5</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="DM21" t="n">
         <v>39.4</v>
@@ -9387,7 +9387,7 @@
         <v>0.8</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="DP21" t="n">
         <v>13.75</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -3634,7 +3634,7 @@
         <v>7.04</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.66</v>
+        <v>7.65</v>
       </c>
       <c r="CE7" t="n">
         <v>1.4</v>
@@ -3679,19 +3679,19 @@
         <v>1.47</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CT7" t="n">
         <v>2.78</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV7" t="n">
         <v>1.85</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX7" t="n">
         <v>1.69</v>
@@ -3712,7 +3712,7 @@
         <v>2.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE7" t="n">
         <v>0.15</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="H11" t="n">
-        <v>98.40000000000001</v>
+        <v>100.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>57.3</v>
+        <v>58.27</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P11" t="n">
-        <v>14.7</v>
+        <v>14.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.5</v>
+        <v>10.82</v>
       </c>
       <c r="R11" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58.7</v>
+        <v>59.55</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.6</v>
+        <v>17.91</v>
       </c>
       <c r="AA11" t="n">
-        <v>11</v>
+        <v>11.27</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.8</v>
+        <v>18.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5177,70 +5177,70 @@
         <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>1.43</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>1.46</v>
-      </c>
       <c r="CA11" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.74</v>
+        <v>4.91</v>
       </c>
       <c r="CC11" t="n">
         <v>1.87</v>
@@ -5249,46 +5249,46 @@
         <v>1.82</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL11" t="n">
         <v>2.12</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
         <v>2.78</v>
@@ -5300,22 +5300,22 @@
         <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY11" t="n">
         <v>2.03</v>
       </c>
-      <c r="CX11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>2.04</v>
-      </c>
       <c r="CZ11" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
@@ -5327,79 +5327,79 @@
         <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF11" t="n">
         <v>1.05</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="DH11" t="n">
-        <v>105.89</v>
+        <v>106.8</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.79</v>
+        <v>7</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.58</v>
+        <v>58.1</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.79</v>
+        <v>14.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.31</v>
+        <v>11.45</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>58.89</v>
+        <v>59.35</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.63</v>
+        <v>17.8</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.84</v>
+        <v>11.95</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.32</v>
+        <v>18.65</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -5643,7 +5643,7 @@
         <v>3.86</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC12" t="n">
         <v>1.98</v>
@@ -5694,7 +5694,7 @@
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT12" t="n">
         <v>2.87</v>
@@ -5706,7 +5706,7 @@
         <v>1.82</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX12" t="n">
         <v>1.66</v>
@@ -5727,7 +5727,7 @@
         <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6311,46 +6311,46 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>94.75</v>
+        <v>93.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AN14" t="n">
-        <v>39.88</v>
+        <v>38.33</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.880000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>40.75</v>
+        <v>39.78</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.5</v>
+        <v>19.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.949999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.79</v>
+        <v>4.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS14" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY14" t="n">
         <v>3.87</v>
@@ -6446,55 +6446,55 @@
         <v>4.28</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="CC14" t="n">
-        <v>6.22</v>
+        <v>7.53</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.66</v>
+        <v>8</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK14" t="n">
         <v>1.54</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.32</v>
+        <v>4.23</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
@@ -6509,22 +6509,22 @@
         <v>1.35</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB14" t="n">
         <v>1.45</v>
@@ -6539,43 +6539,43 @@
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.68000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>40</v>
+        <v>39.3</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.58</v>
+        <v>12.65</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.37</v>
+        <v>14.2</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.789999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>44.05</v>
+        <v>43.45</v>
       </c>
       <c r="DW14" t="n">
         <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.27</v>
+        <v>7.35</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.79</v>
+        <v>20.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G15" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="H15" t="n">
-        <v>110.88</v>
+        <v>114.78</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="K15" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>49.12</v>
+        <v>53.89</v>
       </c>
       <c r="N15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="R15" t="n">
-        <v>8.75</v>
+        <v>7.78</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.62</v>
+        <v>58</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.62</v>
+        <v>19.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6789,70 +6789,70 @@
         <v>1.27</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="CC15" t="n">
         <v>2.47</v>
@@ -6861,25 +6861,25 @@
         <v>2.61</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL15" t="n">
         <v>2.14</v>
@@ -6894,10 +6894,10 @@
         <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6912,31 +6912,31 @@
         <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB15" t="n">
         <v>1.42</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="DE15" t="n">
         <v>0.1</v>
@@ -6945,40 +6945,40 @@
         <v>1.05</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.63</v>
+        <v>103.85</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.58</v>
+        <v>5.65</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.47</v>
+        <v>50.65</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.9</v>
+        <v>11.85</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.58</v>
+        <v>7.2</v>
       </c>
       <c r="DS15" t="n">
         <v>0.15</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.16</v>
+        <v>57.75</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.05</v>
+        <v>13.2</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.32</v>
+        <v>8.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.68</v>
+        <v>18.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -7114,127 +7114,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>84.89</v>
+        <v>81</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.67</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.78</v>
+        <v>10.9</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.779999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43.44</v>
+        <v>42.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.22</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.78</v>
+        <v>7.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.33</v>
+        <v>18.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="BF16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BH16" t="n">
         <v>7.95</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BR16" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU16" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
         <v>4.06</v>
@@ -7252,34 +7252,34 @@
         <v>4.65</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.34</v>
+        <v>5</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.57</v>
+        <v>5.31</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CK16" t="n">
         <v>1.61</v>
@@ -7297,10 +7297,10 @@
         <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7315,10 +7315,10 @@
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CX16" t="n">
         <v>1.64</v>
@@ -7336,52 +7336,52 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>85.37</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.42</v>
+        <v>37.1</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.63</v>
+        <v>10.7</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.31</v>
+        <v>14.15</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.1</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.21</v>
+        <v>42.6</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.31</v>
+        <v>10.95</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.42</v>
+        <v>8.15</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.63</v>
+        <v>17.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,139 +1469,139 @@
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>91.56</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>42.78</v>
+        <v>40.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.89</v>
+        <v>10.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.44</v>
+        <v>7.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.89</v>
+        <v>49.9</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.44</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.22</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.22</v>
+        <v>15.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.32</v>
+        <v>5.45</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>1.67</v>
@@ -1610,16 +1610,16 @@
         <v>1.65</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1631,34 +1631,34 @@
         <v>2.82</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
@@ -1667,112 +1667,112 @@
         <v>3.02</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU2" t="n">
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.42</v>
+        <v>97.3</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.69</v>
+        <v>46.2</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.84</v>
+        <v>9.6</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.21</v>
+        <v>13.85</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.42</v>
+        <v>9.1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.63</v>
+        <v>17.3</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.56</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.56</v>
+        <v>46.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.67</v>
+        <v>10.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.67</v>
+        <v>56.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.22</v>
+        <v>11.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.78</v>
+        <v>19.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT3" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY3" t="n">
         <v>1.91</v>
@@ -2013,31 +2013,31 @@
         <v>1.97</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
         <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.85</v>
@@ -2049,7 +2049,7 @@
         <v>2.22</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN3" t="n">
         <v>1.73</v>
@@ -2061,7 +2061,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2079,16 +2079,16 @@
         <v>2.02</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX3" t="n">
         <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA3" t="n">
         <v>1.74</v>
@@ -2109,40 +2109,40 @@
         <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.35</v>
+        <v>104.52</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.8</v>
+        <v>5.57</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.9</v>
+        <v>50.52</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.2</v>
+        <v>6.28</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>55.95</v>
+        <v>56</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.45</v>
+        <v>14.19</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.15</v>
+        <v>9.9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.4</v>
+        <v>18.57</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.7</v>
+        <v>84.55</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.3</v>
+        <v>32.45</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP4" t="n">
         <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.4</v>
+        <v>15.27</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.3</v>
+        <v>15.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>53.9</v>
+        <v>54.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.3</v>
+        <v>10.64</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>6.73</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.6</v>
+        <v>18.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.27</v>
@@ -2416,25 +2416,25 @@
         <v>2.43</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="CE4" t="n">
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2443,16 +2443,16 @@
         <v>1.83</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
         <v>1.64</v>
@@ -2461,16 +2461,16 @@
         <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CR4" t="n">
         <v>1.48</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CT4" t="n">
         <v>2.73</v>
@@ -2485,22 +2485,22 @@
         <v>2.01</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.09</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB4" t="n">
         <v>1.41</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD4" t="n">
         <v>3.45</v>
@@ -2509,73 +2509,73 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.05</v>
+        <v>96.45</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.74</v>
+        <v>39.95</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.58</v>
+        <v>14.55</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.21</v>
+        <v>15.1</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>54.95</v>
+        <v>55.25</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.9</v>
+        <v>12.95</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.58</v>
+        <v>19.85</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
         <v>1.95</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>108.33</v>
+        <v>111.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>43.44</v>
+        <v>45.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.44</v>
+        <v>13.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.44</v>
+        <v>12.6</v>
       </c>
       <c r="R6" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61</v>
+        <v>61.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.22</v>
+        <v>14.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="AC6" t="n">
-        <v>23.11</v>
+        <v>22.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.58</v>
+        <v>7.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC6" t="n">
         <v>3.02</v>
@@ -3237,7 +3237,7 @@
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG6" t="n">
         <v>2.76</v>
@@ -3249,16 +3249,16 @@
         <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
         <v>1.6</v>
@@ -3270,7 +3270,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3297,7 +3297,7 @@
         <v>2.32</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA6" t="n">
         <v>1.61</v>
@@ -3306,52 +3306,52 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.16</v>
+        <v>103.9</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.63</v>
+        <v>45.7</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.95</v>
+        <v>14.55</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.47</v>
+        <v>12.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="DS6" t="n">
         <v>0.1</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>60.74</v>
+        <v>61.1</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.74</v>
+        <v>13.95</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.26</v>
+        <v>20.1</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H10" t="n">
-        <v>99.67</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>39.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P10" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.89</v>
-      </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.67</v>
+        <v>41.4</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.56</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.26</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC10" t="n">
         <v>6.02</v>
@@ -4852,43 +4852,43 @@
         <v>3.21</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH10" t="n">
         <v>1.32</v>
       </c>
       <c r="CI10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CK10" t="n">
         <v>1.7</v>
       </c>
-      <c r="CJ10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.69</v>
-      </c>
       <c r="CL10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM10" t="n">
         <v>2.11</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO10" t="n">
         <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CT10" t="n">
         <v>2.72</v>
@@ -4912,7 +4912,7 @@
         <v>2.11</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
@@ -4927,43 +4927,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.58</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.53</v>
+        <v>36.3</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.89</v>
+        <v>16.7</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.16</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.52</v>
+        <v>7.65</v>
       </c>
       <c r="DS10" t="n">
         <v>0.1</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.37</v>
+        <v>39.35</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.58</v>
+        <v>11.75</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.32</v>
+        <v>7.45</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.21</v>
+        <v>18.9</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="11">
@@ -5240,7 +5240,7 @@
         <v>4.6</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="CC11" t="n">
         <v>1.87</v>
@@ -5303,7 +5303,7 @@
         <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -6449,13 +6449,13 @@
         <v>3.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC14" t="n">
         <v>7.53</v>
       </c>
       <c r="CD14" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="CE14" t="n">
         <v>1.49</v>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="H17" t="n">
-        <v>84.40000000000001</v>
+        <v>85.64</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="M17" t="n">
-        <v>42.5</v>
+        <v>45.36</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="R17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>42.6</v>
+        <v>42.64</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.2</v>
+        <v>10.55</v>
       </c>
       <c r="AA17" t="n">
         <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.9</v>
+        <v>19.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AF17" t="n">
         <v>0.1</v>
@@ -7595,70 +7595,70 @@
         <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.91</v>
+        <v>5.06</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
         <v>5.73</v>
@@ -7667,13 +7667,13 @@
         <v>6.44</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7682,7 +7682,7 @@
         <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK17" t="n">
         <v>1.72</v>
@@ -7691,19 +7691,19 @@
         <v>2.27</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO17" t="n">
         <v>1.37</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
@@ -7718,106 +7718,106 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB17" t="n">
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.55</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.15</v>
+        <v>38.9</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.1</v>
+        <v>13.05</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.25</v>
+        <v>12.19</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.2</v>
+        <v>40.34</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.15</v>
+        <v>10.34</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.75</v>
+        <v>17.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="H2" t="n">
-        <v>106.5</v>
+        <v>108.73</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>52.1</v>
+        <v>53.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="P2" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.8</v>
+        <v>12.64</v>
       </c>
       <c r="R2" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.9</v>
+        <v>53.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.4</v>
+        <v>11.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.9</v>
+        <v>18.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>1.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.45</v>
+        <v>5.57</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="CC2" t="n">
         <v>2.17</v>
@@ -1625,40 +1625,40 @@
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
@@ -1667,112 +1667,112 @@
         <v>3.02</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU2" t="n">
         <v>1.4</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DC2" t="n">
         <v>2.06</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.07</v>
-      </c>
       <c r="DD2" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.3</v>
+        <v>98.91</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>46.2</v>
+        <v>47.24</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.6</v>
+        <v>9.57</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.4</v>
+        <v>6.29</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.9</v>
+        <v>51.76</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.85</v>
+        <v>14.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.1</v>
+        <v>9.34</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.3</v>
+        <v>17.19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="H4" t="n">
-        <v>111</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.89</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.11</v>
+        <v>56.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.78</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.78</v>
+        <v>20.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,64 +2356,64 @@
         <v>2.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BR4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT4" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU4" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY4" t="n">
         <v>2.27</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CA4" t="n">
         <v>3.3</v>
@@ -2431,25 +2431,25 @@
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK4" t="n">
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CM4" t="n">
         <v>2.02</v>
@@ -2461,28 +2461,28 @@
         <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CU4" t="n">
         <v>1.37</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX4" t="n">
         <v>1.77</v>
@@ -2491,94 +2491,94 @@
         <v>2.23</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DA4" t="n">
         <v>1.66</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.45</v>
+        <v>97.67</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.95</v>
+        <v>41.33</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.55</v>
+        <v>14.52</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.25</v>
+        <v>55.53</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.95</v>
+        <v>13.19</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.85</v>
+        <v>19.52</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
-        <v>73.56</v>
+        <v>69.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>33.11</v>
+        <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>16.22</v>
+        <v>16.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.56</v>
+        <v>16.1</v>
       </c>
       <c r="R5" t="n">
-        <v>8.33</v>
+        <v>9.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>47.56</v>
+        <v>45</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.22</v>
+        <v>5.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.44</v>
+        <v>19</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.95</v>
+        <v>4.38</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.19</v>
+        <v>4.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CC5" t="n">
         <v>5.81</v>
@@ -2831,13 +2831,13 @@
         <v>6.39</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF5" t="n">
         <v>3.08</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
@@ -2855,7 +2855,7 @@
         <v>2.18</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN5" t="n">
         <v>1.74</v>
@@ -2864,10 +2864,10 @@
         <v>1.37</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CR5" t="n">
         <v>1.5</v>
@@ -2876,16 +2876,16 @@
         <v>3.23</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV5" t="n">
         <v>1.77</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX5" t="n">
         <v>1.69</v>
@@ -2903,52 +2903,52 @@
         <v>1.43</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.5</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.85</v>
+        <v>29.95</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.7</v>
+        <v>15.71</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.45</v>
+        <v>15.29</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.9</v>
+        <v>9.43</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.3</v>
+        <v>45.14</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.45</v>
+        <v>10.1</v>
       </c>
       <c r="DY5" t="n">
-        <v>7</v>
+        <v>6.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.25</v>
+        <v>18.09</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="6">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
@@ -3887,139 +3887,139 @@
         <v>2.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.2</v>
+        <v>87.64</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.2</v>
+        <v>35.91</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.8</v>
+        <v>13.73</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.7</v>
+        <v>14.64</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>53.1</v>
+        <v>51.82</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.4</v>
+        <v>16.18</v>
       </c>
       <c r="BE8" t="n">
         <v>1.16</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
         <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5.24</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT8" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.6</v>
@@ -4028,40 +4028,40 @@
         <v>2.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB8" t="n">
         <v>3.4</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="CE8" t="n">
         <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK8" t="n">
         <v>1.77</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CM8" t="n">
         <v>2.01</v>
@@ -4070,31 +4070,31 @@
         <v>1.6</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX8" t="n">
         <v>1.83</v>
@@ -4109,88 +4109,88 @@
         <v>1.63</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>92</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.7</v>
+        <v>4.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.65</v>
+        <v>40.76</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.05</v>
+        <v>15.95</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.35</v>
+        <v>52.67</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.2</v>
+        <v>10.05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.2</v>
+        <v>16.09</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.33</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.44</v>
+        <v>29.2</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.11</v>
+        <v>13.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41</v>
+        <v>41.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.33</v>
+        <v>19.7</v>
       </c>
       <c r="BE9" t="n">
         <v>1.16</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BR9" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY9" t="n">
         <v>3</v>
@@ -4431,25 +4431,25 @@
         <v>3.18</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.3</v>
+        <v>5.08</v>
       </c>
       <c r="CE9" t="n">
         <v>1.51</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
@@ -4458,7 +4458,7 @@
         <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CK9" t="n">
         <v>1.69</v>
@@ -4479,7 +4479,7 @@
         <v>2.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4488,16 +4488,16 @@
         <v>3.29</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CU9" t="n">
         <v>1.33</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CX9" t="n">
         <v>1.78</v>
@@ -4521,46 +4521,46 @@
         <v>3.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.95</v>
+        <v>86.86</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.35</v>
+        <v>34.43</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.65</v>
+        <v>13.86</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.35</v>
+        <v>15.24</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.6</v>
+        <v>7.71</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4572,22 +4572,22 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.6</v>
+        <v>46.71</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.25</v>
+        <v>19.95</v>
       </c>
       <c r="EB9" t="n">
         <v>1.24</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.27</v>
@@ -5096,139 +5096,139 @@
         <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>114.22</v>
+        <v>111.9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.89</v>
+        <v>56.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.89</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.22</v>
+        <v>12.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59.11</v>
+        <v>59.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>17.67</v>
+        <v>17.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.89</v>
+        <v>18.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.6</v>
+        <v>5.48</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
         <v>1.4</v>
@@ -5237,22 +5237,22 @@
         <v>1.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG11" t="n">
         <v>3.12</v>
@@ -5273,7 +5273,7 @@
         <v>2.12</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN11" t="n">
         <v>1.77</v>
@@ -5282,19 +5282,19 @@
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU11" t="n">
         <v>1.48</v>
@@ -5303,19 +5303,19 @@
         <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
@@ -5327,79 +5327,79 @@
         <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
         <v>1.05</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.8</v>
+        <v>106.05</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.1</v>
+        <v>57.47</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO11" t="n">
         <v>2.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.6</v>
+        <v>14.43</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.45</v>
+        <v>11.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.35</v>
+        <v>59.48</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.8</v>
+        <v>17.62</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.95</v>
+        <v>11.81</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.65</v>
+        <v>18.52</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
@@ -5499,52 +5499,52 @@
         <v>0.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.4</v>
+        <v>3.27</v>
       </c>
       <c r="AI12" t="n">
-        <v>102.2</v>
+        <v>108.18</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.6</v>
+        <v>4.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>52.6</v>
+        <v>58.45</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>13.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>6.09</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>56.5</v>
+        <v>58.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.4</v>
+        <v>14.09</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.2</v>
+        <v>19.45</v>
       </c>
       <c r="BE12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.55</v>
       </c>
-      <c r="BF12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BG12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.1</v>
+        <v>9.57</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.35</v>
+        <v>5.71</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU12" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY12" t="n">
         <v>1.72</v>
@@ -5646,10 +5646,10 @@
         <v>4</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="CE12" t="n">
         <v>1.41</v>
@@ -5658,43 +5658,43 @@
         <v>2.88</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK12" t="n">
         <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM12" t="n">
         <v>2.25</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT12" t="n">
         <v>2.87</v>
@@ -5706,7 +5706,7 @@
         <v>1.82</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX12" t="n">
         <v>1.66</v>
@@ -5715,7 +5715,7 @@
         <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA12" t="n">
         <v>1.78</v>
@@ -5724,52 +5724,52 @@
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>109.35</v>
+        <v>112.14</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.9</v>
+        <v>5.52</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>59.55</v>
+        <v>62.28</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.85</v>
+        <v>12.81</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.25</v>
+        <v>10.52</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.05</v>
+        <v>5.81</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.25</v>
+        <v>58.24</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.2</v>
+        <v>16.43</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.25</v>
+        <v>10.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.35</v>
+        <v>19.47</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6311,133 +6311,133 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>93.22</v>
+        <v>92.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.33</v>
+        <v>36.9</v>
       </c>
       <c r="AO14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM14" t="n">
         <v>0.67</v>
       </c>
-      <c r="AP14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>39.78</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.7</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
         <v>3.87</v>
@@ -6446,136 +6446,136 @@
         <v>4.28</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="CC14" t="n">
-        <v>7.53</v>
+        <v>7.88</v>
       </c>
       <c r="CD14" t="n">
-        <v>8.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL14" t="n">
         <v>2.05</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN14" t="n">
         <v>1.86</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CX14" t="n">
         <v>1.59</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DD14" t="n">
         <v>3.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.15000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.3</v>
+        <v>38.57</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.65</v>
+        <v>12.57</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.2</v>
+        <v>13.95</v>
       </c>
       <c r="DR14" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.45</v>
+        <v>42.85</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.85</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.35</v>
+        <v>7.14</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>114.78</v>
+        <v>110.9</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
-        <v>53.89</v>
+        <v>51</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.78</v>
+        <v>13.5</v>
       </c>
       <c r="R15" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>58</v>
+        <v>57.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.44</v>
+        <v>13.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.67</v>
+        <v>19.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6789,70 +6789,70 @@
         <v>1.27</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.25</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BO15" t="n">
         <v>1.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="BR15" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS15" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT15" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CC15" t="n">
         <v>2.47</v>
@@ -6864,10 +6864,10 @@
         <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
@@ -6882,7 +6882,7 @@
         <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM15" t="n">
         <v>2.18</v>
@@ -6891,13 +6891,13 @@
         <v>1.73</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6912,10 +6912,10 @@
         <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CX15" t="n">
         <v>1.72</v>
@@ -6927,91 +6927,91 @@
         <v>2.16</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB15" t="n">
         <v>1.42</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.85</v>
+        <v>102.52</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="DM15" t="n">
-        <v>50.65</v>
+        <v>49.43</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.85</v>
+        <v>11.76</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.75</v>
+        <v>57.53</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.5</v>
+        <v>8.43</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.75</v>
+        <v>18.52</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>85.8</v>
+        <v>86.73</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M16" t="n">
-        <v>38.2</v>
+        <v>38.36</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.3</v>
+        <v>14.64</v>
       </c>
       <c r="R16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43</v>
+        <v>43.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.4</v>
+        <v>11.64</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.1</v>
+        <v>17.64</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,49 +7192,49 @@
         <v>2.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BT16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CC16" t="n">
         <v>5</v>
@@ -7264,13 +7264,13 @@
         <v>5.31</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7285,7 +7285,7 @@
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM16" t="n">
         <v>2.24</v>
@@ -7297,19 +7297,19 @@
         <v>1.38</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS16" t="n">
         <v>3.21</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
@@ -7324,10 +7324,10 @@
         <v>1.64</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA16" t="n">
         <v>1.8</v>
@@ -7336,7 +7336,7 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DD16" t="n">
         <v>3.53</v>
@@ -7345,76 +7345,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>84</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>1.95</v>
       </c>
-      <c r="DH16" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DK16" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.1</v>
+        <v>37.24</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.7</v>
+        <v>10.81</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.15</v>
+        <v>14.34</v>
       </c>
       <c r="DR16" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.6</v>
+        <v>43</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.95</v>
+        <v>11.1</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.15</v>
+        <v>8.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.2</v>
+        <v>17.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="AI18" t="n">
-        <v>107.8</v>
+        <v>110.64</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>48.9</v>
+        <v>49.73</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.2</v>
+        <v>15.55</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.6</v>
+        <v>14.45</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>56.3</v>
+        <v>56.91</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BN18" t="n">
         <v>0.95</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BU18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BY18" t="n">
         <v>1.87</v>
@@ -8058,22 +8058,22 @@
         <v>2.04</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="CE18" t="n">
         <v>1.44</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG18" t="n">
         <v>2.68</v>
@@ -8085,16 +8085,16 @@
         <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK18" t="n">
         <v>1.71</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN18" t="n">
         <v>1.67</v>
@@ -8124,19 +8124,19 @@
         <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY18" t="n">
         <v>2.21</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
@@ -8151,43 +8151,43 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>112.5</v>
+        <v>113.76</v>
       </c>
       <c r="DI18" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>53</v>
+        <v>53.24</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.8</v>
+        <v>14.53</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.8</v>
+        <v>14.71</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.6</v>
+        <v>6.62</v>
       </c>
       <c r="DS18" t="n">
         <v>0.05</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.65</v>
+        <v>57.91</v>
       </c>
       <c r="DW18" t="n">
         <v>0.05</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.7</v>
+        <v>13.71</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.65</v>
+        <v>20.71</v>
       </c>
       <c r="EB18" t="n">
         <v>1.59</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>81.64</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN19" t="n">
-        <v>30.7</v>
+        <v>31.09</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.4</v>
+        <v>13.18</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.9</v>
+        <v>13.55</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>42.9</v>
+        <v>43.27</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.1</v>
+        <v>10.18</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>6.18</v>
       </c>
       <c r="BC19" t="n">
         <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.2</v>
+        <v>15.55</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV19" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY19" t="n">
         <v>3.19</v>
@@ -8461,34 +8461,34 @@
         <v>3.49</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.84</v>
+        <v>5.17</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.17</v>
+        <v>5.52</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
       </c>
       <c r="CI19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ19" t="n">
         <v>1.88</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1.87</v>
       </c>
       <c r="CK19" t="n">
         <v>1.64</v>
@@ -8506,7 +8506,7 @@
         <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.58</v>
@@ -8515,7 +8515,7 @@
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT19" t="n">
         <v>2.83</v>
@@ -8524,10 +8524,10 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
         <v>1.72</v>
@@ -8539,91 +8539,91 @@
         <v>2.14</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB19" t="n">
         <v>1.37</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="DE19" t="n">
         <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.45</v>
+        <v>87</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.3</v>
+        <v>36.24</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.85</v>
+        <v>12.76</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.95</v>
+        <v>13.76</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.35</v>
+        <v>45.43</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.1</v>
+        <v>10.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.45</v>
+        <v>6.95</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.5</v>
+        <v>16.62</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="H20" t="n">
-        <v>102.3</v>
+        <v>102</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M20" t="n">
-        <v>44.3</v>
+        <v>44.64</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="P20" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
         <v>0.1</v>
@@ -8804,70 +8804,70 @@
         <v>2.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.550000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV20" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW20" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX20" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="CA20" t="n">
         <v>3.35</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>4.85</v>
@@ -8876,13 +8876,13 @@
         <v>5.26</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH20" t="n">
         <v>1.34</v>
@@ -8897,7 +8897,7 @@
         <v>1.69</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM20" t="n">
         <v>2.09</v>
@@ -8909,7 +8909,7 @@
         <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ20" t="n">
         <v>4.01</v>
@@ -8921,7 +8921,7 @@
         <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8930,103 +8930,103 @@
         <v>1.85</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX20" t="n">
         <v>1.74</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB20" t="n">
         <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD20" t="n">
         <v>3.43</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="DH20" t="n">
-        <v>93.7</v>
+        <v>93.95</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM20" t="n">
-        <v>38.1</v>
+        <v>38.57</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.25</v>
+        <v>14.19</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.95</v>
+        <v>10.85</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.050000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.9</v>
+        <v>44.53</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.8</v>
+        <v>7.62</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.35</v>
+        <v>17.71</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -9048,82 +9048,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M21" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="U21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.5</v>
+        <v>13.64</v>
       </c>
       <c r="AA21" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.3</v>
+        <v>16.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP21" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV21" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW21" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX21" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.26</v>
+        <v>3.64</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="CC21" t="n">
         <v>4.8</v>
@@ -9279,28 +9279,28 @@
         <v>5.05</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI21" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK21" t="n">
         <v>1.57</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM21" t="n">
         <v>2.34</v>
@@ -9309,25 +9309,25 @@
         <v>1.83</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV21" t="n">
         <v>1.86</v>
@@ -9336,100 +9336,100 @@
         <v>2.03</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB21" t="n">
         <v>1.42</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.15000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.4</v>
+        <v>39.24</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.75</v>
+        <v>13.9</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.15</v>
+        <v>12.09</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="DW21" t="n">
         <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.15</v>
+        <v>11.81</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="EA21" t="n">
-        <v>18</v>
+        <v>17.76</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -3081,139 +3081,139 @@
         <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>96.59999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>45.7</v>
+        <v>43.73</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.4</v>
+        <v>14.82</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.6</v>
+        <v>11.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>6.45</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.7</v>
+        <v>17.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY6" t="n">
         <v>2.01</v>
@@ -3222,55 +3222,55 @@
         <v>2.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
         <v>2</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3285,106 +3285,106 @@
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.95</v>
       </c>
-      <c r="CW6" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CX6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DD6" t="n">
         <v>3.39</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.9</v>
+        <v>102.95</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>45.7</v>
+        <v>44.67</v>
       </c>
       <c r="DN6" t="n">
         <v>0.95</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.55</v>
+        <v>14.29</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.1</v>
+        <v>12.14</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.9</v>
+        <v>5.76</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.1</v>
+        <v>61.33</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.95</v>
+        <v>13.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.1</v>
+        <v>19.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>82.11</v>
+        <v>81.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>12.78</v>
+        <v>12.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.89</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.89</v>
+        <v>47.8</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.44</v>
+        <v>19.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
         <v>0.09</v>
@@ -3565,70 +3565,70 @@
         <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.4</v>
+        <v>5.29</v>
       </c>
       <c r="BR7" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS7" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.98</v>
+        <v>3.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.57</v>
+        <v>4.36</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.06</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
         <v>7.04</v>
@@ -3637,13 +3637,13 @@
         <v>7.65</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
@@ -3661,19 +3661,19 @@
         <v>2.23</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN7" t="n">
         <v>1.69</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CR7" t="n">
         <v>1.47</v>
@@ -3700,7 +3700,7 @@
         <v>2.12</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA7" t="n">
         <v>1.75</v>
@@ -3715,37 +3715,37 @@
         <v>3.17</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.9</v>
+        <v>30.76</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DP7" t="n">
         <v>13</v>
@@ -3754,7 +3754,7 @@
         <v>12.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.25</v>
+        <v>45.76</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.95</v>
+        <v>19.15</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>88.09999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.2</v>
+        <v>34.09</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.6</v>
+        <v>17.18</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>37.3</v>
+        <v>37.91</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.8</v>
+        <v>19.36</v>
       </c>
       <c r="BE10" t="n">
         <v>1.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="BR10" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY10" t="n">
         <v>3.85</v>
@@ -4834,25 +4834,25 @@
         <v>4.28</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.02</v>
+        <v>5.73</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.51</v>
+        <v>6.22</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF10" t="n">
         <v>3.21</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH10" t="n">
         <v>1.32</v>
@@ -4864,10 +4864,10 @@
         <v>2.09</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CM10" t="n">
         <v>2.11</v>
@@ -4882,7 +4882,7 @@
         <v>2.31</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="CR10" t="n">
         <v>1.48</v>
@@ -4897,22 +4897,22 @@
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CX10" t="n">
         <v>1.76</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.11</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
@@ -4927,76 +4927,76 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="DG10" t="n">
         <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.90000000000001</v>
+        <v>94.05</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.3</v>
+        <v>36.14</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.7</v>
+        <v>16.52</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.449999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.35</v>
+        <v>39.57</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.75</v>
+        <v>11.71</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.9</v>
+        <v>18.71</v>
       </c>
       <c r="EB10" t="n">
         <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="11">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="H13" t="n">
-        <v>91.59999999999999</v>
+        <v>90.27</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>38.09</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="P13" t="n">
-        <v>10.9</v>
+        <v>11.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>17.7</v>
+        <v>16.91</v>
       </c>
       <c r="R13" t="n">
-        <v>7.2</v>
+        <v>6.82</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.4</v>
+        <v>49.82</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.7</v>
+        <v>12.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.6</v>
+        <v>16.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AF13" t="n">
         <v>0.1</v>
@@ -5983,70 +5983,70 @@
         <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BN13" t="n">
         <v>1.05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BR13" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT13" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BU13" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC13" t="n">
         <v>3.52</v>
@@ -6055,13 +6055,13 @@
         <v>3.78</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
@@ -6073,25 +6073,25 @@
         <v>1.98</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO13" t="n">
         <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="CR13" t="n">
         <v>1.46</v>
@@ -6112,100 +6112,100 @@
         <v>2.07</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.15000000000001</v>
+        <v>89.52</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.6</v>
+        <v>36.24</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.6</v>
+        <v>16.24</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.8</v>
+        <v>7.57</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.95</v>
+        <v>50.14</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.3</v>
+        <v>11.14</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.05</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.15</v>
+        <v>16.05</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G11" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="H11" t="n">
-        <v>100.73</v>
+        <v>102</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="L11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>58.27</v>
+        <v>60.92</v>
       </c>
       <c r="N11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O11" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>14.36</v>
+        <v>13.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.82</v>
+        <v>10.75</v>
       </c>
       <c r="R11" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="S11" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>59.55</v>
+        <v>60.08</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.91</v>
+        <v>19.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.27</v>
+        <v>12</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.64</v>
+        <v>7.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.45</v>
+        <v>18.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
         <v>0.3</v>
@@ -5177,70 +5177,70 @@
         <v>1.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.89</v>
+        <v>4.96</v>
       </c>
       <c r="CC11" t="n">
         <v>1.82</v>
@@ -5252,52 +5252,52 @@
         <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL11" t="n">
         <v>2.12</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CT11" t="n">
         <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
         <v>1.87</v>
@@ -5306,100 +5306,100 @@
         <v>2.04</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.3</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB11" t="n">
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DG11" t="n">
         <v>3.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.05</v>
+        <v>106.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.47</v>
+        <v>58.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
         <v>2.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.43</v>
+        <v>14.13</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.72</v>
+        <v>11.64</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.19</v>
+        <v>5.09</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.48</v>
+        <v>59.77</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>17.62</v>
+        <v>18.36</v>
       </c>
       <c r="DY11" t="n">
-        <v>11.81</v>
+        <v>12.18</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.81</v>
+        <v>6.18</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.52</v>
+        <v>18.73</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>80.7</v>
+        <v>80.36</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.8</v>
+        <v>31.27</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.8</v>
+        <v>13.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.6</v>
+        <v>11.27</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AV17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BL17" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.95</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.24</v>
+        <v>4.36</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY17" t="n">
         <v>4.41</v>
@@ -7655,67 +7655,67 @@
         <v>5.06</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.73</v>
+        <v>6.16</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.44</v>
+        <v>6.87</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI17" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.06</v>
+        <v>3.97</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="CT17" t="n">
         <v>2.76</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CV17" t="n">
         <v>1.79</v>
@@ -7724,100 +7724,100 @@
         <v>2.12</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DB17" t="n">
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.29000000000001</v>
+        <v>83</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.9</v>
+        <v>38.32</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.05</v>
+        <v>12.96</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.19</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
-        <v>9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.34</v>
+        <v>40.04</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.34</v>
+        <v>10.23</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.67</v>
+        <v>7.55</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.14</v>
+        <v>16.9</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>88.09999999999999</v>
+        <v>85.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.3</v>
+        <v>38.91</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.4</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.4</v>
+        <v>10.82</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.9</v>
+        <v>49.18</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10.45</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>6.45</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.7</v>
+        <v>15.64</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
         <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
         <v>1.63</v>
@@ -1610,43 +1610,43 @@
         <v>1.62</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN2" t="n">
         <v>1.77</v>
@@ -1655,19 +1655,19 @@
         <v>1.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU2" t="n">
         <v>1.4</v>
@@ -1676,7 +1676,7 @@
         <v>1.87</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX2" t="n">
         <v>1.66</v>
@@ -1688,91 +1688,91 @@
         <v>2.24</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD2" t="n">
         <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DH2" t="n">
-        <v>98.91</v>
+        <v>97.14</v>
       </c>
       <c r="DI2" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.24</v>
+        <v>46.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.57</v>
+        <v>11.73</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.29</v>
+        <v>6.32</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.76</v>
+        <v>51.32</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.14</v>
+        <v>13.72</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.34</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.81</v>
+        <v>4.68</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.19</v>
+        <v>17.1</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="H3" t="n">
-        <v>109.91</v>
+        <v>107.67</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="K3" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="L3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>54.45</v>
+        <v>53.83</v>
       </c>
       <c r="N3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>11.36</v>
+        <v>11.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.45</v>
+        <v>11.08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.36</v>
+        <v>6.67</v>
       </c>
       <c r="S3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55.36</v>
+        <v>54.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.27</v>
+        <v>16.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.45</v>
+        <v>11.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.82</v>
+        <v>5.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.09</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.1</v>
+        <v>10.32</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.29</v>
+        <v>5.45</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT3" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BU3" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="CC3" t="n">
         <v>2.24</v>
@@ -2031,7 +2031,7 @@
         <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
@@ -2040,19 +2040,19 @@
         <v>1.93</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2067,31 +2067,31 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
         <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,82 +2100,82 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
         <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.52</v>
+        <v>103.55</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.57</v>
+        <v>5.59</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.52</v>
+        <v>50.36</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO3" t="n">
         <v>2.95</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.38</v>
+        <v>11.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.14</v>
+        <v>10.95</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.28</v>
+        <v>6.46</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56</v>
+        <v>55.64</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.19</v>
+        <v>14.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.57</v>
+        <v>18.23</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.55</v>
+        <v>84.42</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.45</v>
+        <v>32.33</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.27</v>
+        <v>15.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.09</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="BB4" t="n">
         <v>7</v>
       </c>
-      <c r="AT4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.73</v>
-      </c>
       <c r="BC4" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.27</v>
+        <v>17.92</v>
       </c>
       <c r="BE4" t="n">
         <v>1.19</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
         <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.71</v>
+        <v>4.59</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
         <v>2.27</v>
@@ -2416,25 +2416,25 @@
         <v>2.42</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="CE4" t="n">
         <v>1.45</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2449,37 +2449,37 @@
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CM4" t="n">
         <v>2.02</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO4" t="n">
         <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS4" t="n">
         <v>3.17</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU4" t="n">
         <v>1.37</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW4" t="n">
         <v>2</v>
@@ -2500,7 +2500,7 @@
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
         <v>3.4</v>
@@ -2509,73 +2509,73 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>97.67</v>
+        <v>97</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.33</v>
+        <v>40.86</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.52</v>
+        <v>14.64</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>14.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.53</v>
+        <v>55.32</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.1</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.52</v>
+        <v>19.27</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
         <v>2</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.91</v>
+        <v>76.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>27.83</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.27</v>
+        <v>15.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.359999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.27</v>
+        <v>44</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.82</v>
+        <v>10.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.64</v>
+        <v>7.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.27</v>
+        <v>16.75</v>
       </c>
       <c r="BE5" t="n">
         <v>1.12</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>4.05</v>
@@ -2822,19 +2822,19 @@
         <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.39</v>
+        <v>6.27</v>
       </c>
       <c r="CE5" t="n">
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG5" t="n">
         <v>2.7</v>
@@ -2843,22 +2843,22 @@
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
         <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM5" t="n">
         <v>2.21</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO5" t="n">
         <v>1.37</v>
@@ -2867,7 +2867,7 @@
         <v>2.16</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CR5" t="n">
         <v>1.5</v>
@@ -2882,10 +2882,10 @@
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX5" t="n">
         <v>1.69</v>
@@ -2900,10 +2900,10 @@
         <v>1.74</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD5" t="n">
         <v>3.41</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DH5" t="n">
-        <v>74.56999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>29.95</v>
+        <v>29.27</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.71</v>
+        <v>15.77</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.29</v>
+        <v>15.09</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.43</v>
+        <v>9.59</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.14</v>
+        <v>44.45</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.76</v>
+        <v>6.63</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.09</v>
+        <v>17.77</v>
       </c>
       <c r="EB5" t="n">
         <v>1.09</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>111.2</v>
+        <v>109</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>45.7</v>
+        <v>44.91</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>13.7</v>
+        <v>13.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="R6" t="n">
         <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61.7</v>
+        <v>61.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.6</v>
+        <v>14.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.5</v>
+        <v>21.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,70 +3162,70 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.67</v>
+        <v>7.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CC6" t="n">
         <v>3</v>
@@ -3237,10 +3237,10 @@
         <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3252,25 +3252,25 @@
         <v>1.89</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN6" t="n">
         <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3306,85 +3306,85 @@
         <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.95</v>
+        <v>102.22</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.67</v>
+        <v>44.32</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.29</v>
+        <v>14.04</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.14</v>
+        <v>12.23</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.76</v>
+        <v>5.72</v>
       </c>
       <c r="DS6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="DW6" t="n">
         <v>0.09</v>
       </c>
-      <c r="DT6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>61.33</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0.1</v>
-      </c>
       <c r="DX6" t="n">
-        <v>13.81</v>
+        <v>13.96</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.09</v>
+        <v>5.18</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.71</v>
+        <v>19.27</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3484,139 +3484,139 @@
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.18000000000001</v>
+        <v>79.42</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>29.18</v>
+        <v>30.5</v>
       </c>
       <c r="AO7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.64</v>
       </c>
-      <c r="AP7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18.55</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BN7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO7" t="n">
         <v>1.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="BR7" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY7" t="n">
         <v>3.83</v>
@@ -3625,28 +3625,28 @@
         <v>4.36</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.04</v>
+        <v>6.79</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.65</v>
+        <v>7.37</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG7" t="n">
         <v>2.79</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
         <v>1.8</v>
@@ -3658,7 +3658,7 @@
         <v>1.67</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM7" t="n">
         <v>2.15</v>
@@ -3673,19 +3673,19 @@
         <v>2.08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CR7" t="n">
         <v>1.47</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
         <v>1.85</v>
@@ -3700,91 +3700,91 @@
         <v>2.12</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
         <v>1.75</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
         <v>3.17</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.23999999999999</v>
+        <v>80.37</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.76</v>
+        <v>31.41</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>13</v>
+        <v>13.05</v>
       </c>
       <c r="DQ7" t="n">
         <v>12.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.76</v>
+        <v>46.18</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.15</v>
+        <v>19.23</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
         <v>2.09</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>93.8</v>
+        <v>98</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>46.1</v>
+        <v>48</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="P8" t="n">
-        <v>12.7</v>
+        <v>12.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.4</v>
+        <v>17.36</v>
       </c>
       <c r="R8" t="n">
-        <v>7.1</v>
+        <v>6.82</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.6</v>
+        <v>55.09</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.5</v>
+        <v>16.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>16</v>
+        <v>16.55</v>
       </c>
       <c r="AD8" t="n">
         <v>1.69</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,67 +3968,67 @@
         <v>2.27</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.33</v>
+        <v>9.41</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
         <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CB8" t="n">
         <v>3.4</v>
@@ -4040,10 +4040,10 @@
         <v>3.79</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG8" t="n">
         <v>2.71</v>
@@ -4058,10 +4058,10 @@
         <v>1.88</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CM8" t="n">
         <v>2.01</v>
@@ -4073,10 +4073,10 @@
         <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CR8" t="n">
         <v>1.45</v>
@@ -4094,7 +4094,7 @@
         <v>1.96</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX8" t="n">
         <v>1.83</v>
@@ -4112,85 +4112,85 @@
         <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="DE8" t="n">
         <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.56999999999999</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.76</v>
+        <v>41.96</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.24</v>
+        <v>13.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.95</v>
+        <v>16</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.28</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.67</v>
+        <v>53.46</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.67</v>
+        <v>13.72</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.05</v>
+        <v>10.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.09</v>
+        <v>16.36</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="H9" t="n">
-        <v>93.18000000000001</v>
+        <v>92.92</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="L9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>39.18</v>
+        <v>39.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>14.09</v>
+        <v>14.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.18</v>
+        <v>16.25</v>
       </c>
       <c r="R9" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,22 +4266,22 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.18</v>
+        <v>51</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.82</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.91</v>
+        <v>7.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.18</v>
+        <v>20.58</v>
       </c>
       <c r="AD9" t="n">
         <v>1.31</v>
@@ -4371,70 +4371,70 @@
         <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY9" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC9" t="n">
         <v>4.84</v>
@@ -4443,10 +4443,10 @@
         <v>5.08</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CG9" t="n">
         <v>2.46</v>
@@ -4455,22 +4455,22 @@
         <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.12</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL9" t="n">
         <v>2.27</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO9" t="n">
         <v>1.47</v>
@@ -4479,7 +4479,7 @@
         <v>2.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4488,16 +4488,16 @@
         <v>3.29</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CU9" t="n">
         <v>1.33</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CX9" t="n">
         <v>1.78</v>
@@ -4506,13 +4506,13 @@
         <v>2.23</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA9" t="n">
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC9" t="n">
         <v>2.62</v>
@@ -4524,43 +4524,43 @@
         <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.86</v>
+        <v>87</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.43</v>
+        <v>35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DP9" t="n">
         <v>13.86</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.24</v>
+        <v>15.32</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.71</v>
+        <v>7.64</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4572,22 +4572,22 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.71</v>
+        <v>46.82</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.19</v>
+        <v>11.05</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.24</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.95</v>
+        <v>20.18</v>
       </c>
       <c r="EB9" t="n">
         <v>1.24</v>
@@ -5240,7 +5240,7 @@
         <v>4.7</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="CC11" t="n">
         <v>1.82</v>
@@ -5291,19 +5291,19 @@
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT11" t="n">
         <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5321,10 +5321,10 @@
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0.27</v>
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H12" t="n">
-        <v>116.5</v>
+        <v>115.82</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>5.82</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M12" t="n">
-        <v>66.5</v>
+        <v>64.36</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P12" t="n">
-        <v>11.7</v>
+        <v>12.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58</v>
+        <v>56.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>18.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.7</v>
+        <v>11.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.3</v>
+        <v>7.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.5</v>
+        <v>19.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5580,70 +5580,70 @@
         <v>1.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.57</v>
+        <v>9.32</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
         <v>1.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CB12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC12" t="n">
         <v>1.94</v>
@@ -5652,13 +5652,13 @@
         <v>2</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
@@ -5670,13 +5670,13 @@
         <v>2.01</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN12" t="n">
         <v>1.77</v>
@@ -5685,10 +5685,10 @@
         <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5703,10 +5703,10 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX12" t="n">
         <v>1.66</v>
@@ -5721,10 +5721,10 @@
         <v>1.78</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
         <v>3.37</v>
@@ -5733,76 +5733,76 @@
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="DH12" t="n">
-        <v>112.14</v>
+        <v>112</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.52</v>
+        <v>5.37</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>62.28</v>
+        <v>61.4</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.81</v>
+        <v>13.19</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.52</v>
+        <v>10.54</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.81</v>
+        <v>5.77</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>58.24</v>
+        <v>57.5</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.43</v>
+        <v>16.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.52</v>
+        <v>10.32</v>
       </c>
       <c r="DZ12" t="n">
         <v>5.91</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.47</v>
+        <v>19.27</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.27</v>
@@ -5902,52 +5902,52 @@
         <v>2.27</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.7</v>
+        <v>89.55</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>34.2</v>
+        <v>34.82</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.8</v>
+        <v>10.36</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.5</v>
+        <v>15.55</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>50.5</v>
+        <v>51.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.9</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.7</v>
+        <v>16.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.43</v>
+        <v>7.32</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="BR13" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BY13" t="n">
         <v>2.36</v>
@@ -6043,55 +6043,55 @@
         <v>2.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.52</v>
+        <v>3.37</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.78</v>
+        <v>3.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="CR13" t="n">
         <v>1.46</v>
@@ -6106,73 +6106,73 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.52</v>
+        <v>89.91</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.24</v>
+        <v>36.46</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.77</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.24</v>
+        <v>16.23</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.57</v>
+        <v>7.73</v>
       </c>
       <c r="DS13" t="n">
         <v>0.09</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.14</v>
+        <v>50.64</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.14</v>
+        <v>10.91</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.05</v>
+        <v>16.45</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="H14" t="n">
-        <v>89.45</v>
+        <v>90.75</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="L14" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M14" t="n">
-        <v>40.09</v>
+        <v>40.83</v>
       </c>
       <c r="N14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>12.55</v>
+        <v>12.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.82</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.45</v>
+        <v>45.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.64</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.64</v>
+        <v>8.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AC14" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>1.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.24</v>
+        <v>10</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CC14" t="n">
         <v>7.88</v>
@@ -6458,43 +6458,43 @@
         <v>8.56</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
@@ -6512,25 +6512,25 @@
         <v>1.72</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DD14" t="n">
         <v>3.4</v>
@@ -6539,43 +6539,43 @@
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.05</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.57</v>
+        <v>39.04</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.57</v>
+        <v>12.73</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.95</v>
+        <v>13.59</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.949999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42.85</v>
+        <v>42.68</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.529999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.14</v>
+        <v>7.41</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="EA14" t="n">
-        <v>20</v>
+        <v>20.23</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6708,139 +6708,139 @@
         <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>94.91</v>
+        <v>94.17</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>48</v>
+        <v>46.75</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.82</v>
+        <v>11.75</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.18</v>
+        <v>12.92</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>57.55</v>
+        <v>57.58</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.36</v>
+        <v>4.08</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.289999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY15" t="n">
         <v>1.82</v>
@@ -6849,31 +6849,31 @@
         <v>1.9</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.11</v>
@@ -6882,22 +6882,22 @@
         <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6933,52 +6933,52 @@
         <v>1.42</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD15" t="n">
         <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.52</v>
+        <v>101.77</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.62</v>
+        <v>5.45</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.43</v>
+        <v>48.68</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.76</v>
+        <v>11.73</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.81</v>
+        <v>13.18</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="DS15" t="n">
         <v>0.14</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.53</v>
+        <v>57.54</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.1</v>
+        <v>12.91</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.43</v>
+        <v>8.41</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.52</v>
+        <v>18.77</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -7114,127 +7114,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>81</v>
+        <v>82.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>36.91</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.9</v>
+        <v>10.64</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.2</v>
+        <v>43.09</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>10.91</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.3</v>
+        <v>7.82</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.3</v>
+        <v>18.27</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.050000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="BR16" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BS16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT16" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BU16" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY16" t="n">
         <v>3.95</v>
@@ -7252,28 +7252,28 @@
         <v>4.49</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="CC16" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.31</v>
+        <v>5.72</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI16" t="n">
         <v>1.8</v>
@@ -7285,7 +7285,7 @@
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM16" t="n">
         <v>2.24</v>
@@ -7294,31 +7294,31 @@
         <v>1.77</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX16" t="n">
         <v>1.64</v>
@@ -7327,7 +7327,7 @@
         <v>2.06</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA16" t="n">
         <v>1.8</v>
@@ -7336,52 +7336,52 @@
         <v>1.4</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DH16" t="n">
-        <v>84</v>
+        <v>84.55</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.24</v>
+        <v>37.64</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.81</v>
+        <v>10.68</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.34</v>
+        <v>14.32</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.949999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.09</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43</v>
+        <v>43.41</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.1</v>
+        <v>11.28</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="EA16" t="n">
         <v>17.95</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="17">
@@ -7658,13 +7658,13 @@
         <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC17" t="n">
         <v>6.16</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
       <c r="CE17" t="n">
         <v>1.45</v>
@@ -7709,13 +7709,13 @@
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT17" t="n">
         <v>2.76</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV17" t="n">
         <v>1.79</v>
@@ -7742,7 +7742,7 @@
         <v>2.24</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>117.2</v>
+        <v>118</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M18" t="n">
-        <v>57.1</v>
+        <v>59.82</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O18" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="P18" t="n">
-        <v>13.4</v>
+        <v>13.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>14.55</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59</v>
+        <v>58.91</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.6</v>
+        <v>15.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.7</v>
+        <v>10.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>21</v>
+        <v>21.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,49 +7998,49 @@
         <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BH18" t="n">
         <v>8.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BT18" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,19 +8049,19 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CC18" t="n">
         <v>2.4</v>
@@ -8082,10 +8082,10 @@
         <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK18" t="n">
         <v>1.71</v>
@@ -8106,7 +8106,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8121,19 +8121,19 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY18" t="n">
         <v>2.21</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DA18" t="n">
         <v>1.68</v>
@@ -8142,58 +8142,58 @@
         <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD18" t="n">
         <v>3.6</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.76</v>
+        <v>114.32</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DK18" t="n">
         <v>4.9</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM18" t="n">
-        <v>53.24</v>
+        <v>54.78</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.53</v>
+        <v>14.55</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.71</v>
+        <v>14.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.62</v>
+        <v>6.45</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
@@ -8202,25 +8202,25 @@
         <v>57.91</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.71</v>
+        <v>13.78</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.859999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.71</v>
+        <v>20.82</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="19">
@@ -8230,61 +8230,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="H19" t="n">
-        <v>92.90000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M19" t="n">
-        <v>41.9</v>
+        <v>41.73</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>12.3</v>
+        <v>12.36</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.8</v>
+        <v>47.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.8</v>
+        <v>18.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.27</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BH19" t="n">
         <v>8.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
         <v>5.17</v>
@@ -8476,10 +8476,10 @@
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
@@ -8491,10 +8491,10 @@
         <v>1.88</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM19" t="n">
         <v>2.19</v>
@@ -8506,22 +8506,22 @@
         <v>1.33</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
         <v>1.92</v>
@@ -8533,61 +8533,61 @@
         <v>1.72</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DC19" t="n">
         <v>2.14</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
         <v>3.34</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DH19" t="n">
-        <v>87</v>
+        <v>86.78</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.24</v>
+        <v>36.41</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.76</v>
+        <v>12.77</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.76</v>
+        <v>13.78</v>
       </c>
       <c r="DR19" t="n">
         <v>8</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.43</v>
+        <v>45.41</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.62</v>
+        <v>10.72</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>3.82</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.62</v>
+        <v>16.82</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0.09</v>
@@ -8723,139 +8723,139 @@
         <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" t="n">
-        <v>85.09999999999999</v>
+        <v>85.27</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>31.9</v>
+        <v>31.55</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="AR20" t="n">
-        <v>12.4</v>
+        <v>12.09</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>43.3</v>
+        <v>43.09</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>12.3</v>
+        <v>11.82</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.9</v>
+        <v>7.73</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>15.55</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.289999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS20" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV20" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BX20" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY20" t="n">
         <v>3.2</v>
@@ -8864,55 +8864,55 @@
         <v>3.42</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.26</v>
+        <v>5.44</v>
       </c>
       <c r="CE20" t="n">
         <v>1.46</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI20" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
@@ -8945,88 +8945,88 @@
         <v>1.68</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DE20" t="n">
         <v>0.09</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="DH20" t="n">
-        <v>93.95</v>
+        <v>93.64</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM20" t="n">
-        <v>38.57</v>
+        <v>38.1</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.19</v>
+        <v>14.22</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.85</v>
+        <v>10.77</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.53</v>
+        <v>44.36</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.1</v>
+        <v>11.86</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.62</v>
+        <v>7.55</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.48</v>
+        <v>4.32</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.71</v>
+        <v>17.41</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>99.7</v>
+        <v>100.82</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>38.4</v>
+        <v>38.09</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>15.8</v>
+        <v>15.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.4</v>
+        <v>42.45</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.3</v>
+        <v>11.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="AC10" t="n">
         <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.33</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.29</v>
+        <v>4.45</v>
       </c>
       <c r="BR10" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.28</v>
+        <v>4.17</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC10" t="n">
         <v>5.73</v>
@@ -4849,7 +4849,7 @@
         <v>1.48</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CG10" t="n">
         <v>2.55</v>
@@ -4864,34 +4864,34 @@
         <v>2.09</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN10" t="n">
         <v>1.69</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS10" t="n">
         <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4903,22 +4903,22 @@
         <v>2.16</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DD10" t="n">
         <v>3.46</v>
@@ -4927,43 +4927,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DG10" t="n">
         <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.05</v>
+        <v>94.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.14</v>
+        <v>36.09</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.52</v>
+        <v>16.14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.67</v>
+        <v>8.77</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
       <c r="DS10" t="n">
         <v>0.09</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.57</v>
+        <v>40.18</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.71</v>
+        <v>11.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.43</v>
+        <v>7.22</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.71</v>
+        <v>18.68</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="11">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.8</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="AR21" t="n">
-        <v>11.7</v>
+        <v>11.36</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44</v>
+        <v>44.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.73</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.5</v>
+        <v>7.09</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.7</v>
+        <v>18.91</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT21" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX21" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY21" t="n">
         <v>3.4</v>
@@ -9267,91 +9267,91 @@
         <v>3.64</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CC21" t="n">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="CD21" t="n">
-        <v>5.05</v>
+        <v>4.85</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI21" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS21" t="n">
         <v>3.14</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU21" t="n">
         <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DD21" t="n">
         <v>3.24</v>
@@ -9360,76 +9360,76 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DH21" t="n">
-        <v>87.23999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="DI21" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.38</v>
+        <v>4.55</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.24</v>
+        <v>39.46</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.9</v>
+        <v>13.77</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.09</v>
+        <v>11.9</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.1</v>
+        <v>46.14</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.81</v>
+        <v>12.19</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.24</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="EA21" t="n">
-        <v>17.76</v>
+        <v>17.91</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.08</v>
@@ -4290,139 +4290,139 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.90000000000001</v>
+        <v>78.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.2</v>
+        <v>28.64</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.6</v>
+        <v>13.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.8</v>
+        <v>42.09</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.7</v>
+        <v>19.18</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY9" t="n">
         <v>3.02</v>
@@ -4431,43 +4431,43 @@
         <v>3.19</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.08</v>
+        <v>4.98</v>
       </c>
       <c r="CE9" t="n">
         <v>1.52</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
         <v>2.12</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN9" t="n">
         <v>1.67</v>
@@ -4476,10 +4476,10 @@
         <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4494,7 +4494,7 @@
         <v>1.33</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CW9" t="n">
         <v>2.26</v>
@@ -4512,88 +4512,88 @@
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DD9" t="n">
         <v>3.5</v>
       </c>
       <c r="DE9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DS9" t="n">
         <v>0.09</v>
       </c>
-      <c r="DF9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>87</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>35</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.05</v>
-      </c>
       <c r="DT9" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.82</v>
+        <v>46.74</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.05</v>
+        <v>11.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.04</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.18</v>
+        <v>19.91</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="10">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>90.27</v>
+        <v>88.83</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M13" t="n">
-        <v>38.09</v>
+        <v>38.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="P13" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.91</v>
+        <v>16.33</v>
       </c>
       <c r="R13" t="n">
-        <v>6.82</v>
+        <v>6.92</v>
       </c>
       <c r="S13" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.82</v>
+        <v>50.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.27</v>
+        <v>12.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.64</v>
+        <v>7.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.36</v>
+        <v>17</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -5983,70 +5983,70 @@
         <v>1.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BN13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS13" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT13" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BU13" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX13" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
         <v>3.37</v>
@@ -6055,43 +6055,43 @@
         <v>3.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO13" t="n">
         <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="CR13" t="n">
         <v>1.46</v>
@@ -6106,10 +6106,10 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
         <v>1.72</v>
@@ -6124,85 +6124,85 @@
         <v>1.72</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DH13" t="n">
-        <v>89.91</v>
+        <v>89.17</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.46</v>
+        <v>36.65</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.77</v>
+        <v>10.82</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.23</v>
+        <v>15.96</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.64</v>
+        <v>50.82</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.91</v>
+        <v>11.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.45</v>
+        <v>16.78</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
         <v>2.04</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.2</v>
+        <v>-0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>46.2</v>
+        <v>44.91</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.7</v>
+        <v>53.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.9</v>
+        <v>11.36</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.1</v>
+        <v>18.82</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.32</v>
+        <v>10.22</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY3" t="n">
         <v>1.87</v>
@@ -2013,16 +2013,16 @@
         <v>1.92</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
@@ -2031,7 +2031,7 @@
         <v>2.79</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH3" t="n">
         <v>1.42</v>
@@ -2043,16 +2043,16 @@
         <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL3" t="n">
         <v>2.21</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2070,7 +2070,7 @@
         <v>2.9</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
         <v>1.43</v>
@@ -2082,16 +2082,16 @@
         <v>1.89</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,82 +2100,82 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.55</v>
+        <v>100.65</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.36</v>
+        <v>49.56</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.46</v>
+        <v>6.83</v>
       </c>
       <c r="DS3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="DW3" t="n">
         <v>0.09</v>
       </c>
-      <c r="DT3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.05</v>
-      </c>
       <c r="DX3" t="n">
-        <v>14.5</v>
+        <v>14.13</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.23</v>
+        <v>18.13</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="4">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>69.8</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>31</v>
+        <v>29.73</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="P5" t="n">
-        <v>16.2</v>
+        <v>15.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.1</v>
+        <v>15.91</v>
       </c>
       <c r="R5" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45</v>
+        <v>46.55</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AC5" t="n">
-        <v>19</v>
+        <v>18.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BH5" t="n">
         <v>9.09</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.36</v>
+        <v>4.48</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.52</v>
+        <v>4.32</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CC5" t="n">
         <v>5.75</v>
@@ -2834,10 +2834,10 @@
         <v>1.45</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
@@ -2852,10 +2852,10 @@
         <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN5" t="n">
         <v>1.73</v>
@@ -2864,10 +2864,10 @@
         <v>1.37</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="CR5" t="n">
         <v>1.5</v>
@@ -2876,7 +2876,7 @@
         <v>3.23</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2885,16 +2885,16 @@
         <v>1.78</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA5" t="n">
         <v>1.74</v>
@@ -2903,7 +2903,7 @@
         <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD5" t="n">
         <v>3.41</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.36</v>
+        <v>73.39</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>29.27</v>
+        <v>28.74</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
         <v>1.91</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.77</v>
+        <v>15.48</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.59</v>
+        <v>9.48</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.45</v>
+        <v>45.22</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.09</v>
+        <v>10.22</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.63</v>
+        <v>6.61</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.46</v>
+        <v>3.61</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.77</v>
+        <v>17.7</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="H6" t="n">
-        <v>109</v>
+        <v>109.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="K6" t="n">
-        <v>4.18</v>
+        <v>4.42</v>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>44.91</v>
+        <v>48.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="P6" t="n">
-        <v>13.27</v>
+        <v>12.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.73</v>
+        <v>12.5</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="S6" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>61.45</v>
+        <v>62.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.82</v>
+        <v>15.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.73</v>
+        <v>9.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,70 +3162,70 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.45</v>
+        <v>7.48</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="BQ6" t="n">
         <v>4</v>
       </c>
       <c r="BR6" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CA6" t="n">
         <v>3.46</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC6" t="n">
         <v>3</v>
@@ -3246,19 +3246,19 @@
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK6" t="n">
         <v>1.78</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
         <v>1.59</v>
@@ -3270,7 +3270,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3279,16 +3279,16 @@
         <v>3.12</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.95</v>
       </c>
       <c r="CX6" t="n">
         <v>1.84</v>
@@ -3306,52 +3306,52 @@
         <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DE6" t="n">
         <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DH6" t="n">
-        <v>102.22</v>
+        <v>102.78</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.32</v>
+        <v>46</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.04</v>
+        <v>13.83</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.72</v>
+        <v>5.65</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>61.22</v>
+        <v>62</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.96</v>
+        <v>14.57</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.779999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.18</v>
+        <v>5.34</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.27</v>
+        <v>19.39</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="H7" t="n">
-        <v>81.5</v>
+        <v>78.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>32.5</v>
+        <v>32.36</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>12.8</v>
+        <v>13.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>12.18</v>
       </c>
       <c r="R7" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.8</v>
+        <v>46.27</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.8</v>
+        <v>19.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.550000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.23</v>
+        <v>5.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS7" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.83</v>
+        <v>4.39</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.36</v>
+        <v>5.16</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="CC7" t="n">
         <v>6.79</v>
@@ -3637,19 +3637,19 @@
         <v>7.37</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.97</v>
@@ -3661,100 +3661,100 @@
         <v>2.22</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CR7" t="n">
         <v>1.47</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CT7" t="n">
         <v>2.77</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="DE7" t="n">
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.37</v>
+        <v>78.78</v>
       </c>
       <c r="DI7" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="DL7" t="n">
         <v>0.13</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.41</v>
+        <v>31.39</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.05</v>
+        <v>13.3</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.68</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.18</v>
+        <v>45.52</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.539999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.23</v>
+        <v>18.96</v>
       </c>
       <c r="EB7" t="n">
         <v>0.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,139 +3887,139 @@
         <v>2.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>87.64</v>
+        <v>87.42</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>35.91</v>
+        <v>35.17</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.73</v>
+        <v>13.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.64</v>
+        <v>15.17</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.82</v>
+        <v>51.42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.09</v>
+        <v>11.42</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.18</v>
+        <v>15.58</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.41</v>
+        <v>9.35</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU8" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.51</v>
@@ -4034,10 +4034,10 @@
         <v>3.4</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="CE8" t="n">
         <v>1.43</v>
@@ -4058,31 +4058,31 @@
         <v>1.88</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO8" t="n">
         <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT8" t="n">
         <v>2.82</v>
@@ -4094,16 +4094,16 @@
         <v>1.96</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA8" t="n">
         <v>1.63</v>
@@ -4115,49 +4115,49 @@
         <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.81999999999999</v>
+        <v>92.48</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.96</v>
+        <v>41.31</v>
       </c>
       <c r="DN8" t="n">
         <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16</v>
+        <v>16.22</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DS8" t="n">
         <v>0.22</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.46</v>
+        <v>53.18</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.72</v>
+        <v>13.78</v>
       </c>
       <c r="DY8" t="n">
         <v>10.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.36</v>
+        <v>16.04</v>
       </c>
       <c r="EB8" t="n">
         <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -4434,13 +4434,13 @@
         <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CC9" t="n">
         <v>4.75</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="CE9" t="n">
         <v>1.52</v>
@@ -4512,7 +4512,7 @@
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DC9" t="n">
         <v>2.63</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>88.91</v>
+        <v>90.58</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.09</v>
+        <v>34.17</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.18</v>
+        <v>16.92</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>37.91</v>
+        <v>37.92</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.36</v>
+        <v>19.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="BR10" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS10" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY10" t="n">
         <v>3.78</v>
@@ -4834,28 +4834,28 @@
         <v>4.17</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.22</v>
+        <v>6.03</v>
       </c>
       <c r="CE10" t="n">
         <v>1.48</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI10" t="n">
         <v>1.71</v>
@@ -4879,19 +4879,19 @@
         <v>1.42</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.26</v>
+        <v>4.28</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS10" t="n">
         <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4915,10 +4915,10 @@
         <v>1.67</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DD10" t="n">
         <v>3.46</v>
@@ -4930,73 +4930,73 @@
         <v>1.22</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.86</v>
+        <v>95.48</v>
       </c>
       <c r="DI10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="DW10" t="n">
         <v>0.04</v>
       </c>
-      <c r="DJ10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0</v>
-      </c>
       <c r="DX10" t="n">
-        <v>11.5</v>
+        <v>11.39</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.22</v>
+        <v>7.17</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.68</v>
+        <v>18.74</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>111.9</v>
+        <v>108.27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BO11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.45</v>
+        <v>5.26</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY11" t="n">
         <v>1.38</v>
@@ -5237,31 +5237,31 @@
         <v>1.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="CC11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CI11" t="n">
         <v>1.82</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>1.83</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.94</v>
@@ -5282,28 +5282,28 @@
         <v>1.23</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CT11" t="n">
         <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5312,7 +5312,7 @@
         <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA11" t="n">
         <v>1.82</v>
@@ -5321,85 +5321,85 @@
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DK11" t="n">
-        <v>6.91</v>
+        <v>6.87</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.96</v>
+        <v>59.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="DP11" t="n">
         <v>14.13</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.64</v>
+        <v>11.96</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.77</v>
+        <v>60.17</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>18.36</v>
+        <v>18.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>12.18</v>
+        <v>12.13</v>
       </c>
       <c r="DZ11" t="n">
-        <v>6.18</v>
+        <v>6.09</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.73</v>
+        <v>18.83</v>
       </c>
       <c r="EB11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.09</v>
@@ -5499,139 +5499,139 @@
         <v>0.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>108.18</v>
+        <v>106.92</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.45</v>
+        <v>57.25</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.82</v>
+        <v>13.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.45</v>
+        <v>11.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AU12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.09</v>
       </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BP12" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY12" t="n">
         <v>1.73</v>
@@ -5640,40 +5640,40 @@
         <v>1.8</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CD12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH12" t="n">
         <v>1.38</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK12" t="n">
         <v>1.61</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM12" t="n">
         <v>2.24</v>
@@ -5685,10 +5685,10 @@
         <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5724,52 +5724,52 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD12" t="n">
         <v>3.37</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>112</v>
+        <v>111.18</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.37</v>
+        <v>5.26</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM12" t="n">
-        <v>61.4</v>
+        <v>60.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.54</v>
+        <v>10.52</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="DS12" t="n">
         <v>0.09</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.5</v>
+        <v>57.66</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>16.22</v>
+        <v>16.17</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.32</v>
+        <v>10.17</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.27</v>
+        <v>18.87</v>
       </c>
       <c r="EB12" t="n">
         <v>1.88</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="13">
@@ -6124,10 +6124,10 @@
         <v>1.72</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD13" t="n">
         <v>3.42</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" t="n">
-        <v>92.8</v>
+        <v>93.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN14" t="n">
-        <v>36.9</v>
+        <v>39</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.6</v>
+        <v>12.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.9</v>
+        <v>12.09</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>38.9</v>
+        <v>40.64</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>7.09</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.9</v>
+        <v>20.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
         <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS14" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BT14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BY14" t="n">
         <v>3.93</v>
@@ -6446,25 +6446,25 @@
         <v>4.32</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CC14" t="n">
-        <v>7.88</v>
+        <v>7.55</v>
       </c>
       <c r="CD14" t="n">
-        <v>8.56</v>
+        <v>8.18</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
@@ -6479,22 +6479,22 @@
         <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
@@ -6503,7 +6503,7 @@
         <v>3.25</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
@@ -6518,10 +6518,10 @@
         <v>1.61</v>
       </c>
       <c r="CY14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA14" t="n">
         <v>1.85</v>
@@ -6530,7 +6530,7 @@
         <v>1.45</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DD14" t="n">
         <v>3.4</v>
@@ -6539,13 +6539,13 @@
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DH14" t="n">
-        <v>91.68000000000001</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>-0</v>
@@ -6554,28 +6554,28 @@
         <v>2.09</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.63</v>
+        <v>4.78</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>39.04</v>
+        <v>39.95</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.73</v>
+        <v>12.7</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.59</v>
+        <v>13.61</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.869999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42.68</v>
+        <v>43.35</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>9.77</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.41</v>
+        <v>7.61</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.23</v>
+        <v>20.78</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="H15" t="n">
-        <v>110.9</v>
+        <v>109.91</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M15" t="n">
         <v>51</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>11.7</v>
+        <v>12.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.5</v>
+        <v>13.45</v>
       </c>
       <c r="R15" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.5</v>
+        <v>57.09</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.2</v>
+        <v>13.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.1</v>
+        <v>18.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>1.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BH15" t="n">
         <v>8.09</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BO15" t="n">
         <v>1.09</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS15" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT15" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC15" t="n">
         <v>2.62</v>
@@ -6861,22 +6861,22 @@
         <v>2.81</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK15" t="n">
         <v>1.65</v>
@@ -6912,10 +6912,10 @@
         <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CX15" t="n">
         <v>1.72</v>
@@ -6945,73 +6945,73 @@
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.77</v>
+        <v>101.7</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.68</v>
+        <v>48.78</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.73</v>
+        <v>12.13</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.13</v>
+        <v>7.09</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.54</v>
+        <v>57.35</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.91</v>
+        <v>13.18</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.41</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="H16" t="n">
-        <v>86.73</v>
+        <v>87.08</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M16" t="n">
-        <v>38.36</v>
+        <v>38.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.64</v>
+        <v>14.5</v>
       </c>
       <c r="R16" t="n">
-        <v>8.73</v>
+        <v>8.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>43.73</v>
+        <v>43.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.64</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.64</v>
+        <v>17.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>1.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.55</v>
+        <v>4.39</v>
       </c>
       <c r="BR16" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BU16" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.95</v>
+        <v>4.29</v>
       </c>
       <c r="BZ16" t="n">
-        <v>4.49</v>
+        <v>4.93</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CC16" t="n">
         <v>5.18</v>
@@ -7267,25 +7267,25 @@
         <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH16" t="n">
         <v>1.36</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK16" t="n">
         <v>1.61</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM16" t="n">
         <v>2.24</v>
@@ -7297,10 +7297,10 @@
         <v>1.37</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CR16" t="n">
         <v>1.48</v>
@@ -7315,16 +7315,16 @@
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX16" t="n">
         <v>1.64</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.28</v>
@@ -7333,13 +7333,13 @@
         <v>1.8</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
@@ -7348,73 +7348,73 @@
         <v>1.09</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.55</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DK16" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.64</v>
+        <v>37.91</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.32</v>
+        <v>14.26</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.859999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.41</v>
+        <v>43.22</v>
       </c>
       <c r="DW16" t="n">
         <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.28</v>
+        <v>11.22</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.539999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.95</v>
+        <v>17.83</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7436,49 +7436,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
-        <v>85.64</v>
+        <v>87.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K17" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>45.36</v>
+        <v>44.42</v>
       </c>
       <c r="N17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O17" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>12.36</v>
+        <v>12.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.73</v>
+        <v>12.33</v>
       </c>
       <c r="R17" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>42.64</v>
+        <v>43.58</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.55</v>
+        <v>10.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.45</v>
+        <v>19.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7595,70 +7595,70 @@
         <v>1.91</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY17" t="n">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
         <v>6.16</v>
@@ -7667,13 +7667,13 @@
         <v>6.85</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
@@ -7682,7 +7682,7 @@
         <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK17" t="n">
         <v>1.71</v>
@@ -7703,16 +7703,16 @@
         <v>2.16</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
@@ -7727,19 +7727,19 @@
         <v>1.74</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DB17" t="n">
         <v>1.41</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD17" t="n">
         <v>3.18</v>
@@ -7748,43 +7748,43 @@
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DH17" t="n">
-        <v>83</v>
+        <v>84.09</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.32</v>
+        <v>38.13</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DP17" t="n">
         <v>12.96</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12</v>
+        <v>11.82</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.960000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DS17" t="n">
         <v>0.22</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.04</v>
+        <v>40.65</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.23</v>
+        <v>10.44</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.55</v>
+        <v>7.61</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.9</v>
+        <v>16.91</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="18">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.27</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>81.64</v>
+        <v>83.58</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.09</v>
+        <v>32.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.18</v>
+        <v>12.75</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.55</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.27</v>
+        <v>43.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.18</v>
+        <v>11.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.18</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.55</v>
+        <v>15.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS19" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY19" t="n">
         <v>3.09</v>
@@ -8461,25 +8461,25 @@
         <v>3.36</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>5.17</v>
+        <v>4.95</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.52</v>
+        <v>5.28</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH19" t="n">
         <v>1.38</v>
@@ -8494,7 +8494,7 @@
         <v>1.65</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CM19" t="n">
         <v>2.19</v>
@@ -8503,22 +8503,22 @@
         <v>1.74</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CR19" t="n">
         <v>1.45</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
@@ -8527,70 +8527,70 @@
         <v>1.92</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
         <v>1.72</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB19" t="n">
         <v>1.38</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DD19" t="n">
         <v>3.34</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.78</v>
+        <v>87.56</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.41</v>
+        <v>37</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.77</v>
+        <v>12.56</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.78</v>
+        <v>13.74</v>
       </c>
       <c r="DR19" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.41</v>
+        <v>45.44</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.72</v>
+        <v>11.17</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.91</v>
+        <v>7.31</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.82</v>
+        <v>16.65</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H20" t="n">
-        <v>102</v>
+        <v>99.08</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="K20" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M20" t="n">
-        <v>44.64</v>
+        <v>43.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="P20" t="n">
         <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.449999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="R20" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>45.64</v>
+        <v>45.33</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>11.91</v>
+        <v>12.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.36</v>
+        <v>7.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.27</v>
+        <v>18.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF20" t="n">
         <v>0.09</v>
@@ -8804,70 +8804,70 @@
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.050000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT20" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU20" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV20" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW20" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BZ20" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>4.95</v>
@@ -8876,43 +8876,43 @@
         <v>5.44</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI20" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK20" t="n">
         <v>1.7</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN20" t="n">
         <v>1.67</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
@@ -8921,7 +8921,7 @@
         <v>3.18</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU20" t="n">
         <v>1.37</v>
@@ -8930,40 +8930,40 @@
         <v>1.85</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX20" t="n">
         <v>1.74</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD20" t="n">
         <v>3.41</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DH20" t="n">
-        <v>93.64</v>
+        <v>92.48</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.04</v>
@@ -8972,28 +8972,28 @@
         <v>1.78</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM20" t="n">
-        <v>38.1</v>
+        <v>37.92</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="DP20" t="n">
         <v>14.22</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.77</v>
+        <v>10.83</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.359999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS20" t="n">
         <v>0.13</v>
@@ -9005,25 +9005,25 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.36</v>
+        <v>44.26</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>11.86</v>
+        <v>12.09</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.55</v>
+        <v>7.74</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.41</v>
+        <v>17.26</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC20" t="n">
         <v>1.78</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.55</v>
+        <v>84</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.91</v>
+        <v>37.58</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.09</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.18</v>
+        <v>48.92</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.45</v>
+        <v>10.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.45</v>
+        <v>6.17</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.64</v>
+        <v>15.83</v>
       </c>
       <c r="BE2" t="n">
         <v>1.23</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY2" t="n">
         <v>1.63</v>
@@ -1610,16 +1610,16 @@
         <v>1.62</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1628,7 +1628,7 @@
         <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH2" t="n">
         <v>1.39</v>
@@ -1637,7 +1637,7 @@
         <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
         <v>1.6</v>
@@ -1652,7 +1652,7 @@
         <v>1.77</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
         <v>2.02</v>
@@ -1661,19 +1661,19 @@
         <v>3.42</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
         <v>2.04</v>
@@ -1682,13 +1682,13 @@
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
         <v>1.35</v>
@@ -1697,82 +1697,82 @@
         <v>2.07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.14</v>
+        <v>95.83</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.91</v>
+        <v>4.69</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>46.23</v>
+        <v>45.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.73</v>
+        <v>11.78</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.32</v>
+        <v>6.66</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.32</v>
+        <v>51.09</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.72</v>
+        <v>13.57</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.1</v>
+        <v>17.13</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="H4" t="n">
-        <v>112.1</v>
+        <v>115.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>51.1</v>
+        <v>51.18</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="P4" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.9</v>
+        <v>14.45</v>
       </c>
       <c r="R4" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.6</v>
+        <v>56.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>15.73</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.7</v>
+        <v>11.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.9</v>
+        <v>20.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.949999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC4" t="n">
         <v>3.25</v>
@@ -2428,13 +2428,13 @@
         <v>3.45</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2449,13 +2449,13 @@
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO4" t="n">
         <v>1.36</v>
@@ -2464,10 +2464,10 @@
         <v>2.21</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
         <v>3.17</v>
@@ -2479,10 +2479,10 @@
         <v>1.37</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX4" t="n">
         <v>1.77</v>
@@ -2500,52 +2500,52 @@
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DH4" t="n">
-        <v>97</v>
+        <v>99.17</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.86</v>
+        <v>41.35</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.64</v>
+        <v>14.61</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.95</v>
+        <v>14.74</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="DS4" t="n">
         <v>0.13</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.32</v>
+        <v>55.26</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.27</v>
+        <v>19.31</v>
       </c>
       <c r="EB4" t="n">
         <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5">
@@ -5703,10 +5703,10 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX12" t="n">
         <v>1.66</v>
@@ -5727,7 +5727,7 @@
         <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
@@ -7303,13 +7303,13 @@
         <v>3.83</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7336,10 +7336,10 @@
         <v>1.39</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>110.64</v>
+        <v>109.92</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>49.73</v>
+        <v>49.58</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.55</v>
+        <v>15.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.45</v>
+        <v>14.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.91</v>
+        <v>7.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,73 +7974,73 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>56.91</v>
+        <v>57.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.45</v>
+        <v>20.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN18" t="n">
         <v>1</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BT18" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV18" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BY18" t="n">
         <v>1.95</v>
@@ -8058,37 +8058,37 @@
         <v>2.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL18" t="n">
         <v>2.25</v>
@@ -8097,52 +8097,52 @@
         <v>2.09</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU18" t="n">
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB18" t="n">
         <v>1.41</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DD18" t="n">
         <v>3.6</v>
@@ -8151,43 +8151,43 @@
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.32</v>
+        <v>113.78</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>54.78</v>
+        <v>54.48</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.55</v>
+        <v>14.66</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.5</v>
+        <v>14.65</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="DS18" t="n">
         <v>0.09</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.91</v>
+        <v>58.17</v>
       </c>
       <c r="DW18" t="n">
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.78</v>
+        <v>13.61</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.82</v>
+        <v>8.74</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.82</v>
+        <v>20.69</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="19">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -9048,82 +9048,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>91.27</v>
+        <v>91</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="K21" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="L21" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M21" t="n">
-        <v>44.91</v>
+        <v>43.42</v>
       </c>
       <c r="N21" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="O21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>14.45</v>
+        <v>14.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.45</v>
+        <v>12.83</v>
       </c>
       <c r="R21" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="S21" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.64</v>
+        <v>13.08</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.82</v>
+        <v>9.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AC21" t="n">
-        <v>16.91</v>
+        <v>17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.050000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU21" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX21" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC21" t="n">
         <v>4.61</v>
@@ -9279,52 +9279,52 @@
         <v>4.85</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH21" t="n">
         <v>1.34</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO21" t="n">
         <v>1.38</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="CR21" t="n">
         <v>1.49</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU21" t="n">
         <v>1.38</v>
@@ -9333,25 +9333,25 @@
         <v>1.85</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB21" t="n">
         <v>1.43</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD21" t="n">
         <v>3.24</v>
@@ -9360,43 +9360,43 @@
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.14</v>
+        <v>88.13</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.46</v>
+        <v>38.91</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.77</v>
+        <v>13.96</v>
       </c>
       <c r="DQ21" t="n">
-        <v>11.9</v>
+        <v>12.13</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.54</v>
+        <v>7.52</v>
       </c>
       <c r="DS21" t="n">
         <v>0.13</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.14</v>
+        <v>45.69</v>
       </c>
       <c r="DW21" t="n">
         <v>0.04</v>
       </c>
       <c r="DX21" t="n">
-        <v>12.19</v>
+        <v>11.96</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.460000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="EA21" t="n">
         <v>17.91</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1661,16 +1661,16 @@
         <v>3.42</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV2" t="n">
         <v>1.88</v>
@@ -1694,7 +1694,7 @@
         <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD2" t="n">
         <v>3.48</v>
@@ -2413,7 +2413,7 @@
         <v>2.33</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CA4" t="n">
         <v>3.28</v>
@@ -2467,7 +2467,7 @@
         <v>3.85</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS4" t="n">
         <v>3.17</v>

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="H8" t="n">
-        <v>98</v>
+        <v>100.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="L8" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O8" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="P8" t="n">
-        <v>12.55</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.36</v>
+        <v>17.83</v>
       </c>
       <c r="R8" t="n">
-        <v>6.82</v>
+        <v>6.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.09</v>
+        <v>55.08</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.36</v>
+        <v>16.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.91</v>
+        <v>12.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.55</v>
+        <v>16.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.35</v>
+        <v>9.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.26</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT8" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CC8" t="n">
         <v>3.49</v>
@@ -4043,16 +4043,16 @@
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH8" t="n">
         <v>1.36</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.88</v>
@@ -4073,13 +4073,13 @@
         <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS8" t="n">
         <v>3.16</v>
@@ -4091,10 +4091,10 @@
         <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX8" t="n">
         <v>1.82</v>
@@ -4112,85 +4112,85 @@
         <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.48</v>
+        <v>93.84</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.65</v>
+        <v>4.84</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.31</v>
+        <v>41.34</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.13</v>
+        <v>12.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.22</v>
+        <v>16.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.13</v>
+        <v>6.96</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.18</v>
+        <v>53.25</v>
       </c>
       <c r="DW8" t="n">
         <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.78</v>
+        <v>14.08</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.13</v>
+        <v>10.38</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="EA8" t="n">
-        <v>16.04</v>
+        <v>15.92</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -4200,88 +4200,88 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M9" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U9" t="n">
         <v>0.08</v>
       </c>
-      <c r="F9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H9" t="n">
-        <v>92.92</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P9" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51</v>
+        <v>50.15</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.42</v>
+        <v>7.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.58</v>
+        <v>19.77</v>
       </c>
       <c r="AD9" t="n">
         <v>1.31</v>
@@ -4371,70 +4371,70 @@
         <v>2.18</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.65</v>
+        <v>8.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BP9" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT9" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
       <c r="CA9" t="n">
         <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CC9" t="n">
         <v>4.75</v>
@@ -4443,10 +4443,10 @@
         <v>4.97</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CG9" t="n">
         <v>2.45</v>
@@ -4458,28 +4458,28 @@
         <v>1.67</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CK9" t="n">
         <v>1.71</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CM9" t="n">
         <v>2.1</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO9" t="n">
         <v>1.47</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="CR9" t="n">
         <v>1.56</v>
@@ -4512,7 +4512,7 @@
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DC9" t="n">
         <v>2.63</v>
@@ -4521,79 +4521,79 @@
         <v>3.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.95999999999999</v>
+        <v>86.88</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.48</v>
+        <v>35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.78</v>
+        <v>13.87</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.13</v>
+        <v>14.96</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.74</v>
+        <v>46.46</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.22</v>
+        <v>7.29</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.91</v>
+        <v>19.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -4618,79 +4618,79 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>100.82</v>
+        <v>102.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.36</v>
+        <v>4.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>38.09</v>
+        <v>37.42</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="P10" t="n">
-        <v>15.09</v>
+        <v>14.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>6.91</v>
+        <v>6.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.45</v>
+        <v>44</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.82</v>
+        <v>11.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.82</v>
+        <v>4.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="BR10" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC10" t="n">
         <v>5.58</v>
@@ -4849,25 +4849,25 @@
         <v>1.48</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH10" t="n">
         <v>1.31</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK10" t="n">
         <v>1.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM10" t="n">
         <v>2.1</v>
@@ -4879,7 +4879,7 @@
         <v>1.42</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ10" t="n">
         <v>4.28</v>
@@ -4891,7 +4891,7 @@
         <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4909,10 +4909,10 @@
         <v>2.23</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB10" t="n">
         <v>1.45</v>
@@ -4927,43 +4927,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>95.48</v>
+        <v>96.33</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.04</v>
+        <v>35.8</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="DP10" t="n">
-        <v>16.04</v>
+        <v>15.92</v>
       </c>
       <c r="DQ10" t="n">
-        <v>8.779999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.48</v>
+        <v>7.34</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.09</v>
+        <v>40.96</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.39</v>
+        <v>11.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.74</v>
+        <v>19.08</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.18</v>
@@ -6711,136 +6711,136 @@
         <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AI15" t="n">
-        <v>94.17</v>
+        <v>93.23</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.83</v>
+        <v>4.69</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.75</v>
+        <v>44.85</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.75</v>
+        <v>11.77</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AU15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO15" t="n">
         <v>1.17</v>
       </c>
-      <c r="AV15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BP15" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY15" t="n">
         <v>1.84</v>
@@ -6849,55 +6849,55 @@
         <v>1.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CG15" t="n">
         <v>2.62</v>
       </c>
-      <c r="CD15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>2.63</v>
-      </c>
       <c r="CH15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI15" t="n">
         <v>1.72</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN15" t="n">
         <v>1.72</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="CR15" t="n">
         <v>1.47</v>
@@ -6912,10 +6912,10 @@
         <v>1.35</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CX15" t="n">
         <v>1.72</v>
@@ -6933,7 +6933,7 @@
         <v>1.42</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DD15" t="n">
         <v>3.61</v>
@@ -6942,76 +6942,76 @@
         <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG15" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.7</v>
+        <v>100.88</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.78</v>
+        <v>47.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DP15" t="n">
         <v>12.13</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.17</v>
+        <v>13.25</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.35</v>
+        <v>57.46</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.18</v>
+        <v>13.21</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.609999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.57</v>
+        <v>18.46</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="16">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7514,139 +7514,139 @@
         <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI17" t="n">
-        <v>80.36</v>
+        <v>80.75</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.27</v>
+        <v>31.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.55</v>
+        <v>13.75</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.27</v>
+        <v>8.92</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>37.45</v>
+        <v>37.58</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.36</v>
+        <v>15.58</v>
       </c>
       <c r="BE17" t="n">
         <v>1.06</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.960000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.26</v>
+        <v>4.42</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY17" t="n">
         <v>4.29</v>
@@ -7655,40 +7655,40 @@
         <v>4.9</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.16</v>
+        <v>5.89</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.85</v>
+        <v>6.55</v>
       </c>
       <c r="CE17" t="n">
         <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CM17" t="n">
         <v>2.08</v>
@@ -7700,10 +7700,10 @@
         <v>1.36</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7712,7 +7712,7 @@
         <v>3.12</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
@@ -7724,13 +7724,13 @@
         <v>2.12</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA17" t="n">
         <v>1.68</v>
@@ -7748,76 +7748,76 @@
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.09</v>
+        <v>84.12</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="DM17" t="n">
-        <v>38.13</v>
+        <v>37.96</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO17" t="n">
         <v>2.04</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.96</v>
+        <v>13.08</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.82</v>
+        <v>11.88</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>40.65</v>
+        <v>40.58</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.44</v>
+        <v>10.46</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.61</v>
+        <v>7.62</v>
       </c>
       <c r="DZ17" t="n">
         <v>2.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.91</v>
+        <v>17.42</v>
       </c>
       <c r="EB17" t="n">
         <v>1.14</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="18">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
         <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
         <v>0.08</v>
@@ -8723,139 +8723,139 @@
         <v>1.58</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>85.27</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>15.55</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BF20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.39</v>
+        <v>3.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT20" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU20" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV20" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW20" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY20" t="n">
         <v>3.12</v>
@@ -8864,25 +8864,25 @@
         <v>3.32</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH20" t="n">
         <v>1.34</v>
@@ -8909,10 +8909,10 @@
         <v>1.38</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CR20" t="n">
         <v>1.48</v>
@@ -8927,10 +8927,10 @@
         <v>1.37</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX20" t="n">
         <v>1.74</v>
@@ -8945,88 +8945,88 @@
         <v>1.69</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DH20" t="n">
-        <v>92.48</v>
+        <v>91.83</v>
       </c>
       <c r="DI20" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="DK20" t="n">
         <v>4</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DM20" t="n">
-        <v>37.92</v>
+        <v>37.84</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.22</v>
+        <v>14.58</v>
       </c>
       <c r="DQ20" t="n">
-        <v>10.83</v>
+        <v>10.62</v>
       </c>
       <c r="DR20" t="n">
-        <v>8.390000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>44.26</v>
+        <v>44.29</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="DY20" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.26</v>
+        <v>17.04</v>
       </c>
       <c r="EB20" t="n">
         <v>1.34</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Italy_Serie_A_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,49 +1794,49 @@
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G3" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>107.67</v>
+        <v>107.23</v>
       </c>
       <c r="I3" t="n">
         <v>-0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="K3" t="n">
-        <v>6.42</v>
+        <v>6.92</v>
       </c>
       <c r="L3" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>53.83</v>
+        <v>53.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>11.58</v>
+        <v>11.54</v>
       </c>
       <c r="Q3" t="n">
         <v>11.08</v>
       </c>
       <c r="R3" t="n">
-        <v>6.67</v>
+        <v>6.69</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
         <v>0.08</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.75</v>
+        <v>54.85</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.67</v>
+        <v>17.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.5</v>
+        <v>12.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.17</v>
+        <v>5.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.5</v>
+        <v>17.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.22</v>
+        <v>10.42</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.39</v>
+        <v>5.62</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="CC3" t="n">
         <v>2.34</v>
@@ -2028,118 +2028,118 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.86</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
         <v>1.43</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.65</v>
+        <v>100.71</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.39</v>
+        <v>5.71</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.56</v>
+        <v>49.75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>10.87</v>
+        <v>10.88</v>
       </c>
       <c r="DR3" t="n">
         <v>6.83</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.13</v>
+        <v>54.21</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.13</v>
+        <v>14.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.74</v>
+        <v>10.17</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.4</v>
+        <v>4.58</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.13</v>
+        <v>17.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="H4" t="n">
-        <v>115.27</v>
+        <v>114.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="L4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>51.18</v>
+        <v>52.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O4" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="P4" t="n">
-        <v>13.73</v>
+        <v>13.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.45</v>
+        <v>14.42</v>
       </c>
       <c r="R4" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>56.36</v>
+        <v>56</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.73</v>
+        <v>15.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.64</v>
+        <v>11.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.82</v>
+        <v>20.17</v>
       </c>
       <c r="AD4" t="n">
         <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.26</v>
+        <v>4.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CC4" t="n">
         <v>3.25</v>
@@ -2428,13 +2428,13 @@
         <v>3.45</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF4" t="n">
         <v>3.09</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2446,7 +2446,7 @@
         <v>1.92</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
         <v>2.41</v>
@@ -2461,19 +2461,19 @@
         <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU4" t="n">
         <v>1.37</v>
@@ -2485,13 +2485,13 @@
         <v>1.99</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA4" t="n">
         <v>1.66</v>
@@ -2500,85 +2500,85 @@
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>99.17</v>
+        <v>99.3</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.35</v>
+        <v>42.29</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.61</v>
+        <v>14.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.74</v>
+        <v>14.71</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.7</v>
+        <v>5.58</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>55.26</v>
+        <v>55.12</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.17</v>
+        <v>13.29</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.31</v>
+        <v>19.05</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2684,46 +2684,46 @@
         <v>1.92</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>76.33</v>
+        <v>74.92</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>27.83</v>
+        <v>27.85</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.42</v>
+        <v>15.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.25</v>
+        <v>14.54</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
         <v>0.08</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44</v>
+        <v>44.23</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.75</v>
+        <v>10.15</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.33</v>
+        <v>6.92</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.75</v>
+        <v>16.54</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL5" t="n">
         <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>3.88</v>
@@ -2819,16 +2819,16 @@
         <v>4.32</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.27</v>
+        <v>6.41</v>
       </c>
       <c r="CE5" t="n">
         <v>1.45</v>
@@ -2843,10 +2843,10 @@
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK5" t="n">
         <v>1.63</v>
@@ -2873,40 +2873,40 @@
         <v>1.5</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX5" t="n">
         <v>1.7</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB5" t="n">
         <v>1.42</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2915,40 +2915,40 @@
         <v>1.79</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.39</v>
+        <v>72.75</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.74</v>
+        <v>28.71</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.48</v>
+        <v>15.42</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.04</v>
+        <v>15.17</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.48</v>
+        <v>9.42</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.22</v>
+        <v>45.29</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.22</v>
+        <v>9.92</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.61</v>
+        <v>6.42</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.7</v>
+        <v>17.54</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3487,49 +3487,49 @@
         <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
         <v>1.92</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.42</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AM7" t="n">
         <v>0.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>30.5</v>
+        <v>31.85</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.5</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>44.83</v>
+        <v>44.77</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.33</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.43</v>
+        <v>9.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.04</v>
+        <v>5.29</v>
       </c>
       <c r="BR7" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY7" t="n">
         <v>4.39</v>
@@ -3625,64 +3625,64 @@
         <v>5.16</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.79</v>
+        <v>6.9</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.37</v>
+        <v>7.5</v>
       </c>
       <c r="CE7" t="n">
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.97</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CU7" t="n">
         <v>1.42</v>
@@ -3697,97 +3697,97 @@
         <v>1.68</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB7" t="n">
         <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="DE7" t="n">
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DH7" t="n">
-        <v>78.78</v>
+        <v>79.58</v>
       </c>
       <c r="DI7" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DL7" t="n">
         <v>0.13</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.39</v>
+        <v>32.08</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.3</v>
+        <v>13.21</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.52</v>
+        <v>45.46</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.56</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.48</v>
+        <v>5.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.96</v>
+        <v>19.08</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>108.27</v>
+        <v>108.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08<